--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADE4CD5-5A34-1E42-93C1-20ADB7C2A07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8116E4D5-FE75-5645-874B-C55C16ED3ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -78,10 +78,6 @@
 Dra Juanita Reina</t>
   </si>
   <si>
-    <t>Palabras de Calusura
-Presentación musical CEMID</t>
-  </si>
-  <si>
     <t>Educación para todos desde la perspectiva de garantía de derechos y la educación para todos.  
 CEMID 
 Slendy Caterin Malpica Orjuela 
@@ -231,10 +227,6 @@
   </si>
   <si>
     <t>Soacha</t>
-  </si>
-  <si>
-    <t>Acto Inagural
-Grupo de Danza Foloklórica Maguaré</t>
   </si>
   <si>
     <t>Conferencia Principal
@@ -962,6 +954,15 @@
     <t xml:space="preserve">CUIDALAB 
  William Romero - Pedro Nel Urrea
  Julio Pinzon y colegio Kimmy pernia </t>
+  </si>
+  <si>
+    <t>Acto Inagural
+Oración
+Grupo de Danza Foloklórica Maguaré</t>
+  </si>
+  <si>
+    <t>Palabras de Clausura
+Presentación musical CEMID</t>
   </si>
 </sst>
 </file>
@@ -1466,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>3</v>
@@ -1481,13 +1482,13 @@
         <v>2</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>46314</v>
       </c>
@@ -1498,7 +1499,7 @@
         <v>0.375</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
@@ -1507,10 +1508,10 @@
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1533,10 +1534,10 @@
         <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1550,7 +1551,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
@@ -1559,10 +1560,10 @@
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1576,7 +1577,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>
@@ -1585,10 +1586,10 @@
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1631,10 +1632,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1657,10 +1658,10 @@
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1674,7 +1675,7 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>4</v>
@@ -1683,10 +1684,10 @@
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1700,7 +1701,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="E10" t="s">
         <v>4</v>
@@ -1709,10 +1710,10 @@
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1742,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>3</v>
@@ -1757,10 +1758,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1774,19 +1775,19 @@
         <v>0.34375</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1800,19 +1801,19 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1826,19 +1827,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1853,7 +1854,7 @@
         <v>0.4375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
@@ -1870,19 +1871,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1896,7 +1897,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -1913,19 +1914,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1939,19 +1940,19 @@
         <v>0.625</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1965,19 +1966,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1991,19 +1992,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2017,19 +2018,19 @@
         <v>0.6875</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2043,19 +2044,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2069,16 +2070,16 @@
         <v>0.8125</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2092,19 +2093,19 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2118,19 +2119,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2144,19 +2145,19 @@
         <v>0.375</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2170,19 +2171,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2196,7 +2197,7 @@
         <v>0.4375</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
@@ -2213,19 +2214,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -2236,19 +2237,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2259,19 +2260,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2285,7 +2286,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
@@ -2302,19 +2303,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2328,19 +2329,19 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2354,19 +2355,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.2">
@@ -2380,19 +2381,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2406,19 +2407,19 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2432,19 +2433,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="238" x14ac:dyDescent="0.2">
@@ -2455,19 +2456,19 @@
         <v>0.375</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" t="s">
         <v>23</v>
       </c>
-      <c r="E30" t="s">
-        <v>24</v>
-      </c>
       <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="35" x14ac:dyDescent="0.25">
@@ -2481,19 +2482,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I31" s="21"/>
     </row>
@@ -2508,7 +2509,7 @@
         <v>0.4375</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
@@ -2525,19 +2526,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H33" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2551,19 +2552,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="102" x14ac:dyDescent="0.2">
@@ -2577,19 +2578,19 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2603,19 +2604,19 @@
         <v>0.375</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2626,19 +2627,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2652,10 +2653,10 @@
         <v>0.4375</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
@@ -2672,19 +2673,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2698,19 +2699,19 @@
         <v>0.5</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>5</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2724,7 +2725,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
@@ -2741,19 +2742,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>5</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H42" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2767,7 +2768,7 @@
         <v>0.4375</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
@@ -2784,19 +2785,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H44" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I44" s="14"/>
     </row>
@@ -2811,19 +2812,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="102" x14ac:dyDescent="0.2">
@@ -2837,19 +2838,19 @@
         <v>0.5</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
         <v>5</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H46" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2863,19 +2864,19 @@
         <v>0.375</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H47" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2889,19 +2890,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
         <v>5</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H48" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -2915,19 +2916,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" t="s">
         <v>41</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>42</v>
       </c>
-      <c r="F49" t="s">
-        <v>43</v>
-      </c>
       <c r="G49" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -2941,19 +2942,19 @@
         <v>0.5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s">
+        <v>41</v>
+      </c>
+      <c r="F50" t="s">
         <v>42</v>
       </c>
-      <c r="F50" t="s">
-        <v>43</v>
-      </c>
       <c r="G50" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2967,19 +2968,19 @@
         <v>0.375</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F51" t="s">
         <v>5</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H51" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -2993,16 +2994,16 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E52" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3016,10 +3017,10 @@
         <v>0.4375</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F53" t="s">
         <v>5</v>
@@ -3036,19 +3037,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F54" t="s">
         <v>5</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H54" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3062,19 +3063,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E55" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F55" t="s">
         <v>5</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H55" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3088,19 +3089,19 @@
         <v>0.5</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F56" t="s">
         <v>5</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H56" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3114,19 +3115,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F57" t="s">
         <v>5</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H57" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3154,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>3</v>
@@ -3169,10 +3170,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3186,19 +3187,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3212,19 +3213,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3238,7 +3239,7 @@
         <v>0.4375</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
@@ -3255,19 +3256,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3281,19 +3282,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3307,7 +3308,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -3324,19 +3325,19 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3350,19 +3351,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3376,19 +3377,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3402,19 +3403,19 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3428,19 +3429,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3454,19 +3455,19 @@
         <v>0.375</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3480,19 +3481,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3506,16 +3507,16 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3529,7 +3530,7 @@
         <v>0.4375</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
@@ -3546,19 +3547,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3572,19 +3573,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3598,19 +3599,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3624,19 +3625,19 @@
         <v>0.375</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3650,16 +3651,16 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3673,7 +3674,7 @@
         <v>0.4375</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
@@ -3690,19 +3691,19 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3716,19 +3717,19 @@
         <v>0.46875</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3742,19 +3743,19 @@
         <v>0.5</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H25" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3768,7 +3769,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
@@ -3785,19 +3786,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3811,19 +3812,19 @@
         <v>0.625</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3837,19 +3838,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3863,19 +3864,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H30" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3889,19 +3890,19 @@
         <v>0.6875</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3915,19 +3916,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3941,19 +3942,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H33" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3967,19 +3968,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3993,19 +3994,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4016,7 +4017,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
@@ -4033,19 +4034,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="204" x14ac:dyDescent="0.2">
@@ -4059,19 +4060,19 @@
         <v>0.625</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H38" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -4085,19 +4086,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -4111,19 +4112,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>5</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -4137,19 +4138,19 @@
         <v>0.6875</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H41" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -4163,19 +4164,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
         <v>5</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H42" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4189,16 +4190,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="153" x14ac:dyDescent="0.2">
@@ -4212,16 +4213,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4235,19 +4236,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4261,19 +4262,19 @@
         <v>0.375</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
         <v>5</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H46" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -4287,19 +4288,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H47" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -4313,19 +4314,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
         <v>5</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H48" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4339,7 +4340,7 @@
         <v>0.4375</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F49" t="s">
         <v>5</v>
@@ -4356,19 +4357,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
         <v>5</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4382,19 +4383,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F51" t="s">
         <v>5</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H51" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4408,19 +4409,19 @@
         <v>0.375</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" t="s">
+        <v>103</v>
+      </c>
+      <c r="F52" t="s">
         <v>104</v>
       </c>
-      <c r="E52" t="s">
-        <v>105</v>
-      </c>
-      <c r="F52" t="s">
-        <v>106</v>
-      </c>
       <c r="G52" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4434,19 +4435,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E53" t="s">
+        <v>41</v>
+      </c>
+      <c r="F53" t="s">
         <v>42</v>
       </c>
-      <c r="F53" t="s">
-        <v>43</v>
-      </c>
       <c r="G53" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H53" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4474,10 +4475,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>3</v>
@@ -4489,10 +4490,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4506,19 +4507,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4532,19 +4533,19 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4558,19 +4559,19 @@
         <v>0.40625</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4584,19 +4585,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4610,7 +4611,7 @@
         <v>0.4375</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -4627,19 +4628,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4653,14 +4654,14 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E8" s="16"/>
       <c r="G8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4674,19 +4675,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4700,7 +4701,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -4717,19 +4718,19 @@
         <v>0.625</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4743,19 +4744,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4769,19 +4770,19 @@
         <v>0.5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4795,19 +4796,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4821,19 +4822,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4847,19 +4848,19 @@
         <v>0.375</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4873,19 +4874,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -4899,19 +4900,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4922,7 +4923,7 @@
         <v>0.4375</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
@@ -4939,19 +4940,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4965,19 +4966,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4991,19 +4992,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5017,19 +5018,19 @@
         <v>0.375</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="339" customHeight="1" x14ac:dyDescent="0.2">
@@ -5043,19 +5044,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5069,7 +5070,7 @@
         <v>0.4375</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
@@ -5086,19 +5087,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5112,19 +5113,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5138,19 +5139,19 @@
         <v>0.375</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H28" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5164,19 +5165,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5190,7 +5191,7 @@
         <v>0.4375</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
@@ -5207,19 +5208,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5233,19 +5234,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H32" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5259,7 +5260,7 @@
         <v>0.4375</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
@@ -5276,19 +5277,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5302,19 +5303,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5328,19 +5329,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5354,19 +5355,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5380,16 +5381,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -5403,19 +5404,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5429,13 +5430,13 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="D40" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" t="s">
         <v>140</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5449,19 +5450,19 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="D41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H41" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5475,19 +5476,19 @@
         <v>0.1875</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H42" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5501,19 +5502,19 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F43" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -5539,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>30</v>
       </c>
       <c r="D1" s="27" t="s">
         <v>3</v>
@@ -5554,10 +5555,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5571,19 +5572,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5597,16 +5598,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5620,19 +5621,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5646,19 +5647,19 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5672,19 +5673,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5698,19 +5699,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5724,19 +5725,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5750,7 +5751,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" t="s">
@@ -5768,16 +5769,16 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5791,19 +5792,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5817,19 +5818,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5843,19 +5844,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5869,19 +5870,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5895,19 +5896,19 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5921,19 +5922,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5947,19 +5948,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -5989,10 +5990,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>30</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>3</v>
@@ -6004,10 +6005,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -6021,19 +6022,19 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -6047,19 +6048,19 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6073,19 +6074,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6099,11 +6100,11 @@
         <v>0.4375</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6117,19 +6118,19 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -6143,19 +6144,19 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -6169,19 +6170,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6195,10 +6196,10 @@
         <v>0.4375</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -6212,19 +6213,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -6238,19 +6239,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6264,7 +6265,7 @@
         <v>0.375</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -6278,19 +6279,19 @@
         <v>0.40625</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6304,10 +6305,10 @@
         <v>0.4375</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6321,19 +6322,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6347,19 +6348,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6373,19 +6374,19 @@
         <v>0.5</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -6399,19 +6400,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F078449-A8B7-F845-AAAE-ECF79F5334F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B4EAB6-B566-2743-8251-795E08693F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="5" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="207">
   <si>
     <t>DÍA</t>
   </si>
@@ -231,12 +231,6 @@
 Diego Fernando Barragán
 Decano facultad de Educación
 Universidad de la Salle</t>
-  </si>
-  <si>
-    <t>Conversatorio: Corporalidad y Aprendizaje Experiencial
-    Miguel Diaz (Perú) Alicia López (México)
-Eliana Monroy, Gonzalo Amaya, German Preciado,  (Colombia) 
- Modera: Pedro Nel Urrea Roa</t>
   </si>
   <si>
     <t>Auditorio B206</t>
@@ -844,11 +838,6 @@
   </si>
   <si>
     <t>CONGRESO IDRM - REDI EDUFISICA
-Diagnóstico morfofuncional del perfil de fuerza-velocidad horizontal en el contexto del deporte escolar regional
-Yohandis Abad Camejo, Francisco Freyre Vazquez, Abel Emilio Campaña Garzon(</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM - REDI EDUFISICA
 Implementación de la Plataforma de Educación física (PEF)
 Pablo Paúl Almeyda Torres, Susana Elizabeth Saravia Tasayco, Jimmy Alexandre Vergara Blas. Perú</t>
   </si>
@@ -963,6 +952,17 @@
   </si>
   <si>
     <t>CENTRO UNIVERSITARIO</t>
+  </si>
+  <si>
+    <t>Conversatorio: Corporalidad y Aprendizaje Experiencial
+   Miguel Diaz (Perú) Alicia López (México)
+Eliana Monroy, Gonzalo Amaya, German Preciado,  (Colombia) 
+ Modera: Pedro Nel Urrea Roa</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM - REDI EDUFISICA
+Diagnóstico morfofuncional del perfil de fuerza-velocidad horizontal en el contexto del deporte escolar regional
+Yohandis Abad Camejo, Francisco Freyre Vazquez, Abel Emilio Campaña Garzon</t>
   </si>
 </sst>
 </file>
@@ -1483,13 +1483,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G1" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -1503,7 +1503,7 @@
         <v>0.375</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -1512,10 +1512,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1538,10 +1538,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1564,10 +1564,10 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1581,7 +1581,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -1590,10 +1590,10 @@
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1636,10 +1636,10 @@
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1662,10 +1662,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1679,7 +1679,7 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
@@ -1688,10 +1688,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1705,7 +1705,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
@@ -1714,10 +1714,10 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1759,13 +1759,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G1" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1782,16 +1782,16 @@
         <v>9</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1808,16 +1808,16 @@
         <v>10</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1834,16 +1834,16 @@
         <v>20</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1878,19 +1878,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1922,19 +1922,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1948,19 +1948,19 @@
         <v>0.625</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1974,19 +1974,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -2000,19 +2000,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2026,19 +2026,19 @@
         <v>0.6875</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2052,19 +2052,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2078,16 +2078,16 @@
         <v>0.8125</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H14" s="25"/>
     </row>
@@ -2111,7 +2111,7 @@
         <v>17</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H15" s="25" t="s">
         <v>17</v>
@@ -2137,7 +2137,7 @@
         <v>17</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H16" s="25" t="s">
         <v>17</v>
@@ -2163,10 +2163,10 @@
         <v>4</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2180,7 +2180,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>16</v>
@@ -2189,10 +2189,10 @@
         <v>4</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -2206,7 +2206,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>16</v>
@@ -2215,10 +2215,10 @@
         <v>4</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -2230,7 +2230,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>16</v>
@@ -2239,10 +2239,10 @@
         <v>4</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2263,10 +2263,10 @@
         <v>4</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2280,7 +2280,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>16</v>
@@ -2289,10 +2289,10 @@
         <v>4</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2306,7 +2306,7 @@
         <v>0.625</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>16</v>
@@ -2315,10 +2315,10 @@
         <v>4</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2332,7 +2332,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>16</v>
@@ -2341,10 +2341,10 @@
         <v>4</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.2">
@@ -2358,7 +2358,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>16</v>
@@ -2367,10 +2367,10 @@
         <v>4</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2384,7 +2384,7 @@
         <v>0.6875</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>16</v>
@@ -2393,10 +2393,10 @@
         <v>4</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2410,7 +2410,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>16</v>
@@ -2419,10 +2419,10 @@
         <v>4</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="238" x14ac:dyDescent="0.2">
@@ -2443,10 +2443,10 @@
         <v>4</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="35" x14ac:dyDescent="0.25">
@@ -2469,10 +2469,10 @@
         <v>4</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I29" s="14"/>
     </row>
@@ -2496,10 +2496,10 @@
         <v>4</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2522,10 +2522,10 @@
         <v>4</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="102" x14ac:dyDescent="0.2">
@@ -2542,16 +2542,16 @@
         <v>26</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F32" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2565,7 +2565,7 @@
         <v>0.375</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E33" s="25" t="s">
         <v>29</v>
@@ -2574,10 +2574,10 @@
         <v>4</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2589,7 +2589,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>29</v>
@@ -2598,10 +2598,10 @@
         <v>4</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H34" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2624,10 +2624,10 @@
         <v>4</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2650,10 +2650,10 @@
         <v>4</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H36" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2667,7 +2667,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>32</v>
@@ -2676,10 +2676,10 @@
         <v>4</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H37" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2702,10 +2702,10 @@
         <v>4</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I38" s="10"/>
     </row>
@@ -2729,10 +2729,10 @@
         <v>4</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H39" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="102" x14ac:dyDescent="0.2">
@@ -2755,10 +2755,10 @@
         <v>4</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2781,10 +2781,10 @@
         <v>4</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H41" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2807,10 +2807,10 @@
         <v>4</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H42" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2833,10 +2833,10 @@
         <v>41</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H43" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="102" x14ac:dyDescent="0.2">
@@ -2850,7 +2850,7 @@
         <v>0.5</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="25" t="s">
         <v>40</v>
@@ -2859,10 +2859,10 @@
         <v>41</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2876,19 +2876,19 @@
         <v>0.375</v>
       </c>
       <c r="D45" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="25" t="s">
-        <v>61</v>
-      </c>
       <c r="F45" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2902,17 +2902,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>4</v>
+      </c>
       <c r="G46" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2929,16 +2931,16 @@
         <v>18</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F47" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2955,16 +2957,16 @@
         <v>18</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F48" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -2981,16 +2983,16 @@
         <v>18</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F49" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H49" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3007,16 +3009,16 @@
         <v>18</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F50" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H50" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3056,13 +3058,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G1" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3076,7 +3078,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>16</v>
@@ -3085,10 +3087,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3102,7 +3104,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>16</v>
@@ -3111,10 +3113,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3148,7 +3150,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>16</v>
@@ -3157,10 +3159,10 @@
         <v>4</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3174,7 +3176,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>16</v>
@@ -3183,10 +3185,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3218,7 +3220,7 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>16</v>
@@ -3227,10 +3229,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3244,7 +3246,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>16</v>
@@ -3253,10 +3255,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3270,7 +3272,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>16</v>
@@ -3279,10 +3281,10 @@
         <v>4</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3296,7 +3298,7 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>16</v>
@@ -3305,10 +3307,10 @@
         <v>4</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3322,7 +3324,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>16</v>
@@ -3331,10 +3333,10 @@
         <v>4</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3348,19 +3350,19 @@
         <v>0.375</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3374,19 +3376,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3400,17 +3402,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="25"/>
+        <v>71</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>4</v>
+      </c>
       <c r="G15" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3424,19 +3428,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3450,19 +3454,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3476,19 +3480,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3502,19 +3506,19 @@
         <v>0.375</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3528,17 +3532,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="25"/>
+        <v>43</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>4</v>
+      </c>
       <c r="G20" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3552,19 +3558,19 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3578,19 +3584,19 @@
         <v>0.46875</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F22" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3604,19 +3610,19 @@
         <v>0.5</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F23" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3630,19 +3636,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F24" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3656,19 +3662,19 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3682,19 +3688,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3708,19 +3714,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F27" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3734,19 +3740,19 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F28" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3760,19 +3766,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F29" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3786,7 +3792,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="25" t="s">
         <v>22</v>
@@ -3795,10 +3801,10 @@
         <v>4</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3812,7 +3818,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="25" t="s">
         <v>22</v>
@@ -3821,10 +3827,10 @@
         <v>4</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3838,7 +3844,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>29</v>
@@ -3847,10 +3853,10 @@
         <v>4</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3864,7 +3870,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E33" s="25" t="s">
         <v>29</v>
@@ -3873,10 +3879,10 @@
         <v>4</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="204" x14ac:dyDescent="0.2">
@@ -3890,7 +3896,7 @@
         <v>0.625</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>29</v>
@@ -3899,10 +3905,10 @@
         <v>4</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H34" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -3916,7 +3922,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>29</v>
@@ -3925,10 +3931,10 @@
         <v>4</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3942,7 +3948,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36" s="25" t="s">
         <v>29</v>
@@ -3951,10 +3957,10 @@
         <v>4</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H36" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3968,7 +3974,7 @@
         <v>0.6875</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>29</v>
@@ -3977,10 +3983,10 @@
         <v>4</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H37" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -3994,7 +4000,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E38" s="25" t="s">
         <v>29</v>
@@ -4003,10 +4009,10 @@
         <v>4</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4020,14 +4026,14 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E39" s="25" t="s">
         <v>17</v>
       </c>
       <c r="F39" s="25"/>
       <c r="G39" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H39" s="25" t="s">
         <v>17</v>
@@ -4044,14 +4050,14 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E40" s="25" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="25"/>
       <c r="G40" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H40" s="25" t="s">
         <v>17</v>
@@ -4068,7 +4074,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E41" s="25" t="s">
         <v>32</v>
@@ -4077,10 +4083,10 @@
         <v>4</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H41" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4094,7 +4100,7 @@
         <v>0.375</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E42" s="25" t="s">
         <v>32</v>
@@ -4103,10 +4109,10 @@
         <v>4</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H42" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -4120,7 +4126,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E43" s="25" t="s">
         <v>32</v>
@@ -4129,10 +4135,10 @@
         <v>4</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H43" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -4146,7 +4152,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E44" s="25" t="s">
         <v>32</v>
@@ -4155,10 +4161,10 @@
         <v>4</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4172,7 +4178,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>32</v>
@@ -4181,10 +4187,10 @@
         <v>4</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4198,7 +4204,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E46" s="25" t="s">
         <v>36</v>
@@ -4207,10 +4213,10 @@
         <v>4</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4224,19 +4230,19 @@
         <v>0.375</v>
       </c>
       <c r="D47" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="E47" s="25" t="s">
+      <c r="F47" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="F47" s="25" t="s">
-        <v>103</v>
-      </c>
       <c r="G47" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4250,7 +4256,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>40</v>
@@ -4259,10 +4265,10 @@
         <v>41</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -4302,13 +4308,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G1" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4322,7 +4328,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>16</v>
@@ -4331,10 +4337,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4348,7 +4354,7 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>16</v>
@@ -4357,10 +4363,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4374,7 +4380,7 @@
         <v>0.40625</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>16</v>
@@ -4383,10 +4389,10 @@
         <v>4</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4400,7 +4406,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>16</v>
@@ -4409,10 +4415,10 @@
         <v>4</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4446,7 +4452,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>16</v>
@@ -4455,10 +4461,10 @@
         <v>4</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4472,15 +4478,19 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="25"/>
+        <v>112</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>4</v>
+      </c>
       <c r="G8" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4494,7 +4504,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" s="29" t="s">
         <v>16</v>
@@ -4503,10 +4513,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4538,7 +4548,7 @@
         <v>0.625</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>16</v>
@@ -4547,10 +4557,10 @@
         <v>4</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4564,19 +4574,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4590,19 +4600,19 @@
         <v>0.5</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4616,19 +4626,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4642,19 +4652,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4668,19 +4678,19 @@
         <v>0.375</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4694,19 +4704,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -4720,19 +4730,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4746,19 +4756,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4772,19 +4782,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4798,7 +4808,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" s="29" t="s">
         <v>22</v>
@@ -4807,10 +4817,10 @@
         <v>4</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4824,7 +4834,7 @@
         <v>0.375</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E22" s="29" t="s">
         <v>22</v>
@@ -4833,10 +4843,10 @@
         <v>4</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="339" customHeight="1" x14ac:dyDescent="0.2">
@@ -4850,7 +4860,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E23" s="29" t="s">
         <v>22</v>
@@ -4859,10 +4869,10 @@
         <v>4</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4876,7 +4886,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E24" s="29" t="s">
         <v>22</v>
@@ -4885,10 +4895,10 @@
         <v>4</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4902,7 +4912,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E25" s="29" t="s">
         <v>22</v>
@@ -4911,10 +4921,10 @@
         <v>4</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4928,7 +4938,7 @@
         <v>0.375</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E26" s="29" t="s">
         <v>29</v>
@@ -4937,10 +4947,10 @@
         <v>4</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4954,7 +4964,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" s="29" t="s">
         <v>29</v>
@@ -4963,10 +4973,10 @@
         <v>4</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4980,7 +4990,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E28" s="29" t="s">
         <v>29</v>
@@ -4989,10 +4999,10 @@
         <v>4</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5006,19 +5016,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F29" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5032,19 +5042,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F30" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5058,19 +5068,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5084,7 +5094,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E32" s="29" t="s">
         <v>36</v>
@@ -5093,10 +5103,10 @@
         <v>4</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5110,7 +5120,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E33" s="29" t="s">
         <v>36</v>
@@ -5119,10 +5129,10 @@
         <v>4</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5136,14 +5146,14 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>17</v>
       </c>
       <c r="F34" s="25"/>
       <c r="G34" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H34" s="25" t="s">
         <v>17</v>
@@ -5160,19 +5170,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5186,13 +5196,13 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>40</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G36" s="24"/>
       <c r="H36" s="25"/>
@@ -5208,19 +5218,19 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E37" s="24" t="s">
         <v>40</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H37" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5234,19 +5244,19 @@
         <v>0.1875</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>40</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5260,19 +5270,19 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>40</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H39" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -5310,13 +5320,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G1" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5330,16 +5340,16 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H2" s="25" t="s">
         <v>17</v>
@@ -5356,14 +5366,14 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H3" s="25" t="s">
         <v>17</v>
@@ -5380,7 +5390,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>16</v>
@@ -5389,10 +5399,10 @@
         <v>4</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5406,7 +5416,7 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>16</v>
@@ -5415,10 +5425,10 @@
         <v>4</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5432,7 +5442,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>16</v>
@@ -5441,10 +5451,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5458,7 +5468,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>16</v>
@@ -5467,10 +5477,10 @@
         <v>4</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5484,7 +5494,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>16</v>
@@ -5493,10 +5503,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -5510,14 +5520,14 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H9" s="25" t="s">
         <v>17</v>
@@ -5534,19 +5544,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5560,7 +5570,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>22</v>
@@ -5569,10 +5579,10 @@
         <v>4</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5586,7 +5596,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>22</v>
@@ -5595,10 +5605,10 @@
         <v>4</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5612,7 +5622,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>22</v>
@@ -5621,10 +5631,10 @@
         <v>4</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5638,7 +5648,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>22</v>
@@ -5647,10 +5657,10 @@
         <v>4</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5664,19 +5674,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E15" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="F15" s="25" t="s">
-        <v>153</v>
-      </c>
       <c r="G15" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5690,19 +5700,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5777,13 +5787,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G1" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5797,19 +5807,19 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>156</v>
-      </c>
       <c r="F2" s="23" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5823,19 +5833,19 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>158</v>
-      </c>
       <c r="F3" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5849,19 +5859,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5879,7 +5889,7 @@
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="25"/>
@@ -5895,19 +5905,19 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5921,19 +5931,19 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5947,19 +5957,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5973,19 +5983,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5999,19 +6009,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6025,7 +6035,7 @@
         <v>0.375</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
@@ -6043,19 +6053,19 @@
         <v>0.40625</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6069,19 +6079,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6095,19 +6105,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6121,19 +6131,19 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -6147,19 +6157,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E86858-E1A6-194F-8354-FA4887B700FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A77176A-BC69-9247-BEDD-BA81F9DDD514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -791,11 +791,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
-¿Qué puede llegar a ser una persona? Capacidades humanas como horizonte para la Educación Física 
-Yammir López Brito, Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
-  </si>
-  <si>
     <t>CONGRESO IDRM -REDDI EDUFISICA
 Caracterización de la fuerza en miembros inferiores en futbolistas prejuveniles de la Escuela Nueva Era de Sogamoso como apoyo a la educación física escolar.
 Nataly Alejandra Velandia Naranjo</t>
@@ -967,6 +962,11 @@
     <t>CONGRESO IDRM -REDDI EDUFISICA
 Juegos Electrónicos
 Alexander Ospina Bolaños - Presidente PAMESCO - Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+¿Qué puede llegar a ser una persona? Capacidades humanas como horizonte para la Educación Física 
+Yammir López Brito (España), Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1899,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
         <v>43</v>
@@ -1925,7 +1925,7 @@
         <v>0.625</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E9" t="s">
         <v>43</v>
@@ -1951,7 +1951,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E10" t="s">
         <v>43</v>
@@ -1977,7 +1977,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
         <v>43</v>
@@ -2003,7 +2003,7 @@
         <v>0.6875</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E12" t="s">
         <v>43</v>
@@ -2029,7 +2029,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
         <v>43</v>
@@ -2254,7 +2254,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E22" t="s">
         <v>16</v>
@@ -2280,7 +2280,7 @@
         <v>0.625</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -2306,7 +2306,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
@@ -2332,7 +2332,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
@@ -2358,7 +2358,7 @@
         <v>0.6875</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E26" t="s">
         <v>16</v>
@@ -2384,7 +2384,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
         <v>16</v>
@@ -2639,7 +2639,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
@@ -3050,7 +3050,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -3145,7 +3145,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
@@ -3185,7 +3185,7 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
@@ -3211,7 +3211,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -3237,7 +3237,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -3263,7 +3263,7 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
@@ -3289,7 +3289,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -3601,7 +3601,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E24" t="s">
         <v>43</v>
@@ -3627,7 +3627,7 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
         <v>43</v>
@@ -3653,7 +3653,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E26" t="s">
         <v>43</v>
@@ -3679,7 +3679,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E27" t="s">
         <v>43</v>
@@ -3705,7 +3705,7 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E28" t="s">
         <v>43</v>
@@ -3731,7 +3731,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E29" t="s">
         <v>43</v>
@@ -3835,7 +3835,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E33" t="s">
         <v>29</v>
@@ -3861,7 +3861,7 @@
         <v>0.625</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E34" t="s">
         <v>29</v>
@@ -3887,7 +3887,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E35" t="s">
         <v>29</v>
@@ -3913,7 +3913,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E36" t="s">
         <v>29</v>
@@ -3939,7 +3939,7 @@
         <v>0.6875</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E37" t="s">
         <v>29</v>
@@ -3965,7 +3965,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" t="s">
         <v>29</v>
@@ -4587,7 +4587,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>56</v>

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A77176A-BC69-9247-BEDD-BA81F9DDD514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324B95D4-2A30-1A45-81A2-D7A745C33657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="3740" yWindow="2280" windowWidth="53000" windowHeight="35040" activeTab="5" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="213">
   <si>
     <t>DÍA</t>
   </si>
@@ -95,10 +95,6 @@
   </si>
   <si>
     <t>Almuerzo</t>
-  </si>
-  <si>
-    <t>Diálogos científicos
-Carlos Pacheco</t>
   </si>
   <si>
     <t>CHARLAS WEBINAR MAFB-LFDD
@@ -126,21 +122,6 @@
 Briyith Tatiana Ramírez Villanueva </t>
   </si>
   <si>
-    <t>PEMA - Proyecto estación meteorológica 
-Nelson Eduardo Bejarano Morales
-Edwin Javier Rozo Carrasquilla 
-María Erika Castro Díaz
-Gloria Yomaira Tovar 
-Jazmín Parra Umba
-Semillero de investigación Phobos, proyecto Belt Vision
-CEMID - Edwin Javier Rozo Carrasquilla 
- Colorado Torres David Santiago
- Cotrino Rojas Manuel Alejandro
- Mei Mendoza Dayana Sofía
- Pinilla Martínez Fabian Esteban
- Rodriguez Artiza Nicolás</t>
-  </si>
-  <si>
     <t>Living Lab B201</t>
   </si>
   <si>
@@ -157,13 +138,6 @@
 Maira Alejandra Pulgarín Rodríguez</t>
   </si>
   <si>
-    <t>Retos y posibilidades de la inteligencia artificial en la formación de docentes
-Formato: conferencia
-Saúl Antonio Reyes
-Celebración renovación alta calidad Lic. Informática
-Red de Innovación Educativa, STEM y Nuevas Tecnologías- Carlos Pacheco</t>
-  </si>
-  <si>
     <t>HORA INCIO</t>
   </si>
   <si>
@@ -171,11 +145,6 @@
   </si>
   <si>
     <t>Creative Lab C504</t>
-  </si>
-  <si>
-    <t>Ecoeducación Sonora de la
-Licenciatura en Ciencias Naturales y Educación Ambiental
-Carlos Pacheco</t>
   </si>
   <si>
     <t>Del sofá al mundo: aprender lenguas a través del cine
@@ -183,10 +152,6 @@
   </si>
   <si>
     <t>Salón C508</t>
-  </si>
-  <si>
-    <t>Impacto de la IA en la escuela – Docentes y Estudiantes
-CEMID: DISA</t>
   </si>
   <si>
     <t xml:space="preserve">Proyecto ATS - Todos juntos - Ibagué - virtual
@@ -281,10 +246,6 @@
     <t>Diálogos de Semilleros Ciprés</t>
   </si>
   <si>
-    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
-Carlos Pacheco</t>
-  </si>
-  <si>
     <t>Taller Experiencial con presentación de Caso:Educación con Propósito: Laboratorio de Innovacón Pedagogíca para Transformar Comunidades 
 EDULAB</t>
   </si>
@@ -320,10 +281,6 @@
   </si>
   <si>
     <t>Ciudadanía digital en los Colegios Minuto de Dios
-José Argenis Mendoza</t>
-  </si>
-  <si>
-    <t>Iniciativas de IA para la protección del Medio Ambiente 
 José Argenis Mendoza</t>
   </si>
   <si>
@@ -450,9 +407,6 @@
 Semillero Educación Infantil</t>
   </si>
   <si>
-    <t>CEMID - Sobre convivencia escolar y la prevención del acoso escolar</t>
-  </si>
-  <si>
     <t>Educomunicación, pensamiento crítico y lenguaje desde las experiencias audiovisuales en la CEMID
 Valerie Sophia Prado Velásquez -Evolet Blue Pabón Gómez</t>
   </si>
@@ -517,29 +471,6 @@
 Natalia Martínez - Johana Rodríguez </t>
   </si>
   <si>
-    <t>Taller: Arqueología de la confianza: recuperar el pasado para innovar en educación
-James Ricardo Zorro Monroy, Frendy González y Sandra Patricia Pachón Monsalve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poster Expandido - CEMID
-Arquitectura autosostenible
-1. Ospina Galeano Jorge Esteban 
-2. Parra Moya Julián David
-3. Rodriguez Giraldo Mariana
-4. Torres Díaz Mariana 
-AlgaeX Lab: Huerta Escolar Inteligente.
-1. Lauren Fiallo Mendoza
-2. Sara Valentina Velez Mena
-3. María José Zambrano García
-4. Juliana Ramírez Angulo
-App de las emociones
-1. - Samuel Alejandro García Cuervo 
-2. Nikol Mariana Buitrago Jaramillo 
-3. Laura Sofia Tobar García 
-4. Mariana Quiroga Sánchez 
-</t>
-  </si>
-  <si>
     <t>Taller de Graffiti
 Daniel Núñez, UNIARTES</t>
   </si>
@@ -764,11 +695,6 @@
     <t xml:space="preserve">CUIDALAB 
  William Romero - Pedro Nel Urrea
  Julio Pinzon y colegio Kimmy pernia </t>
-  </si>
-  <si>
-    <t>Acto Inagural
-Oración
-Grupo de Danza Foloklórica Maguaré</t>
   </si>
   <si>
     <t>Palabras de Clausura
@@ -967,6 +893,92 @@
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
 ¿Qué puede llegar a ser una persona? Capacidades humanas como horizonte para la Educación Física 
 Yammir López Brito (España), Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
+  </si>
+  <si>
+    <t>PEMA - Proyecto estación meteorológica 
+Nelson Eduardo Bejarano Morales
+Edwin Javier Rozo Carrasquilla 
+María Erika Castro Díaz
+Gloria Yomaira Tovar 
+Jazmín Parra Umba</t>
+  </si>
+  <si>
+    <t>Semillero de investigación Phobos, proyecto Belt Vision
+CEMID - Edwin Javier Rozo Carrasquilla 
+ Colorado Torres David Santiago
+ Cotrino Rojas Manuel Alejandro
+ Mei Mendoza Dayana Sofía
+ Pinilla Martínez Fabian Esteban
+ Rodriguez Artiza Nicolás</t>
+  </si>
+  <si>
+    <t>Impacto de la IA en la escuela – Docentes y Estudiantes
+Paul Cubillos + 1 Estudinate
+CEMID</t>
+  </si>
+  <si>
+    <t>Acto Inaugural
+Oración
+Grupo de Danza Foloklórica Maguaré</t>
+  </si>
+  <si>
+    <t>Ecoeducación Sonora de la Licenciatura en Ciencias Naturales y Educación Ambiental
+Carlos Pacheco</t>
+  </si>
+  <si>
+    <t>Auditorio C204</t>
+  </si>
+  <si>
+    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
+Andrés Camilo Pérez Rodríguez, Cristian Camilo Ladino Marín</t>
+  </si>
+  <si>
+    <t>Iniciativas de IA para la protección del Medio Ambiente 
+María José Villa Moreno, Danna Valentina Rincon Loaiza</t>
+  </si>
+  <si>
+    <t>El desarrollo humano desde el acondicionamiento físico y el bienestar
+Invitado: Diego Fernando Villamizar Gómez
+Moderadora: Dalis Nury Molina Bustamante</t>
+  </si>
+  <si>
+    <t>Sobre convivencia escolar y la prevención del acoso escolar
+José Argenis Mendoza Suárez
+CEMID</t>
+  </si>
+  <si>
+    <t>AlgaeX Lab: Huerta Escolar Inteligente.
+1. Lauren Fiallo Mendoza
+2. Sara Valentina Velez Mena
+3. María José Zambrano García
+4. Juliana Ramírez Angulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App de las emociones
+1. - Samuel Alejandro García Cuervo 
+2. Nikol Mariana Buitrago Jaramillo 
+3. Laura Sofia Tobar García 
+4. Mariana Quiroga Sánchez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arquitectura autosostenible
+1. Ospina Galeano Jorge Esteban 
+2. Parra Moya Julián David
+3. Rodriguez Giraldo Mariana
+4. Torres Díaz Mariana 
+</t>
+  </si>
+  <si>
+    <t>9:!5</t>
+  </si>
+  <si>
+    <t>Arqueología de la confianza: recuperar el pasado para innovar en educación
+James Ricardo Zorro Monroy, Frendy González y Sandra Patricia Pachón Monsalve</t>
+  </si>
+  <si>
+    <t>¿Cómo se construyen las nociones de violencia en la infancia? Una experiencia de investigación en educación
+Invitado: John Jairo García Díaz
+Moderadora: Nadia Johanna Hernández Ordoñez</t>
   </si>
 </sst>
 </file>
@@ -1455,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -1467,13 +1479,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -1487,7 +1499,7 @@
         <v>0.375</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -1496,10 +1508,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1522,10 +1534,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1539,7 +1551,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
@@ -1548,10 +1560,10 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1565,7 +1577,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -1574,10 +1586,10 @@
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1620,10 +1632,10 @@
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1646,10 +1658,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1663,7 +1675,7 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
@@ -1672,10 +1684,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1689,7 +1701,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
@@ -1698,10 +1710,10 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1715,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0435A0A-E8EE-B24A-B2EA-F66A17D967D3}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="12" customWidth="1"/>
@@ -1731,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -1743,13 +1755,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1766,16 +1778,16 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1792,16 +1804,16 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1815,19 +1827,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1844,9 +1856,6 @@
       <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
@@ -1859,19 +1868,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1899,19 +1908,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1925,19 +1934,19 @@
         <v>0.625</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1951,19 +1960,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1977,19 +1986,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H11" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2003,19 +2012,19 @@
         <v>0.6875</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2029,19 +2038,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2055,16 +2064,16 @@
         <v>0.8125</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2078,45 +2087,45 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46315</v>
       </c>
       <c r="B16" s="18">
-        <v>0.79166666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C16" s="18">
-        <v>0.85416666666666663</v>
+        <v>0.375</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2124,51 +2133,51 @@
         <v>46315</v>
       </c>
       <c r="B17" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C17" s="18">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H17" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46315</v>
       </c>
       <c r="B18" s="18">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="C18" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H18" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -2176,71 +2185,77 @@
         <v>46315</v>
       </c>
       <c r="B19" s="18">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C19" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="12">
+        <v>46315</v>
+      </c>
       <c r="B20" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C20" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+      <c r="A21" s="12">
+        <v>46315</v>
+      </c>
       <c r="B21" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C21" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2248,103 +2263,103 @@
         <v>46315</v>
       </c>
       <c r="B22" s="18">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C22" s="18">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46315</v>
       </c>
       <c r="B23" s="18">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="C23" s="18">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H23" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46315</v>
       </c>
       <c r="B24" s="18">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C24" s="18">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>180</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>170</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46315</v>
       </c>
       <c r="B25" s="18">
-        <v>0.64583333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C25" s="18">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>181</v>
+        <v>0.6875</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2352,74 +2367,77 @@
         <v>46315</v>
       </c>
       <c r="B26" s="18">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="C26" s="18">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H26" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46315</v>
       </c>
       <c r="B27" s="18">
-        <v>0.6875</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C27" s="18">
-        <v>0.70833333333333337</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F27" t="s">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="238" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="119" x14ac:dyDescent="0.2">
+      <c r="A28" s="12">
+        <v>46315</v>
+      </c>
       <c r="B28" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C28" s="18">
         <v>0.375</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H28" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="35" x14ac:dyDescent="0.25">
@@ -2433,19 +2451,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I29" s="14"/>
     </row>
@@ -2460,19 +2478,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F30" t="s">
         <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2486,45 +2504,45 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F31" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46315</v>
       </c>
       <c r="B32" s="18">
-        <v>0.77083333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C32" s="18">
-        <v>0.83333333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" t="s">
         <v>26</v>
       </c>
-      <c r="E32" t="s">
-        <v>43</v>
-      </c>
       <c r="F32" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2532,205 +2550,208 @@
         <v>46315</v>
       </c>
       <c r="B33" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C33" s="18">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>168</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
         <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H33" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="12">
+        <v>46315</v>
+      </c>
       <c r="B34" s="18">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="C34" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46315</v>
       </c>
       <c r="B35" s="18">
-        <v>0.4375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C35" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
         <v>4</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46315</v>
       </c>
       <c r="B36" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C36" s="18">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>31</v>
+        <v>173</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F36" t="s">
         <v>4</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H36" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46315</v>
       </c>
       <c r="B37" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C37" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F37" t="s">
         <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="H37" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="1:9" ht="85" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46315</v>
       </c>
       <c r="B38" s="18">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C38" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F38" t="s">
         <v>4</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="H38" t="s">
-        <v>147</v>
-      </c>
-      <c r="I38" s="10"/>
-    </row>
-    <row r="39" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46315</v>
       </c>
       <c r="B39" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C39" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F39" t="s">
         <v>4</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46315</v>
       </c>
       <c r="B40" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C40" s="18">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F40" t="s">
         <v>4</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H40" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2738,155 +2759,155 @@
         <v>46315</v>
       </c>
       <c r="B41" s="18">
-        <v>0.35416666666666669</v>
+        <v>0.44374999999999998</v>
       </c>
       <c r="C41" s="18">
-        <v>0.375</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
         <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H41" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46315</v>
       </c>
       <c r="B42" s="18">
-        <v>0.44374999999999998</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C42" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" t="s">
         <v>36</v>
       </c>
-      <c r="F42" t="s">
-        <v>4</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="H42" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46315</v>
       </c>
       <c r="B43" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C43" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F43" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H43" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46315</v>
       </c>
       <c r="B44" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C44" s="18">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F44" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H44" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46315</v>
       </c>
       <c r="B45" s="18">
-        <v>0.35416666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="C45" s="18">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F45" t="s">
         <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46315</v>
       </c>
       <c r="B46" s="18">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="C46" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F46" t="s">
         <v>4</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="H46" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2894,25 +2915,25 @@
         <v>46315</v>
       </c>
       <c r="B47" s="18">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C47" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F47" t="s">
         <v>4</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H47" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2920,25 +2941,25 @@
         <v>46315</v>
       </c>
       <c r="B48" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C48" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F48" t="s">
         <v>4</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H48" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -2946,51 +2967,25 @@
         <v>46315</v>
       </c>
       <c r="B49" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="C49" s="18">
-        <v>0.5</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F49" t="s">
         <v>4</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H49" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="12">
-        <v>46315</v>
-      </c>
-      <c r="B50" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="C50" s="18">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" t="s">
-        <v>4</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H50" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3018,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -3030,13 +3025,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3050,22 +3045,22 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46316</v>
       </c>
@@ -3076,19 +3071,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>203</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3104,9 +3099,6 @@
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
@@ -3119,19 +3111,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3145,19 +3137,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3185,19 +3177,19 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3211,19 +3203,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3237,19 +3229,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3263,19 +3255,19 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3289,19 +3281,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3315,19 +3307,19 @@
         <v>0.375</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3341,19 +3333,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3367,19 +3359,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3393,19 +3385,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H16" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3419,19 +3411,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3445,19 +3437,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H18" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3471,19 +3463,19 @@
         <v>0.375</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3497,19 +3489,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H20" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3523,19 +3515,19 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F21" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3549,19 +3541,19 @@
         <v>0.46875</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="E22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F22" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="H22" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3575,19 +3567,19 @@
         <v>0.5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3601,19 +3593,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3627,19 +3619,19 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3653,19 +3645,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3679,19 +3671,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H27" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3705,19 +3697,19 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H28" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3731,19 +3723,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H29" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3757,19 +3749,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F30" t="s">
         <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3783,19 +3775,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F31" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3809,19 +3801,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3835,19 +3827,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
         <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H33" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="204" x14ac:dyDescent="0.2">
@@ -3861,19 +3853,19 @@
         <v>0.625</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H34" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -3887,19 +3879,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
         <v>4</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3913,19 +3905,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
         <v>4</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H36" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3939,19 +3931,19 @@
         <v>0.6875</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
         <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -3965,42 +3957,42 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
         <v>4</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H38" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46316</v>
       </c>
       <c r="B39" s="18">
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C39" s="18">
         <v>0.85416666666666663</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="153" x14ac:dyDescent="0.2">
@@ -4014,16 +4006,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4037,19 +4029,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F41" t="s">
         <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H41" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4063,19 +4055,19 @@
         <v>0.375</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F42" t="s">
         <v>4</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H42" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -4089,19 +4081,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F43" t="s">
         <v>4</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H43" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -4115,19 +4107,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F44" t="s">
         <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H44" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4141,19 +4133,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F45" t="s">
         <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H45" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4167,19 +4159,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F46" t="s">
         <v>4</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H46" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4193,19 +4185,19 @@
         <v>0.375</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F47" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H47" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4219,19 +4211,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F48" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H48" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4245,24 +4237,24 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E49" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
         <v>4</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H49" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E52" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -4272,7 +4264,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{610C11C2-B771-9D44-A689-56619F68B052}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="12"/>
@@ -4290,10 +4282,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -4302,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4322,19 +4314,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4348,19 +4340,19 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4374,19 +4366,19 @@
         <v>0.40625</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4400,19 +4392,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4428,9 +4420,6 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
@@ -4443,19 +4432,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4469,19 +4458,19 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4495,19 +4484,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4535,19 +4524,19 @@
         <v>0.625</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4561,19 +4550,19 @@
         <v>0.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4587,22 +4576,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46317</v>
       </c>
@@ -4613,19 +4602,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4639,19 +4628,19 @@
         <v>0.375</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4665,19 +4654,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H16" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -4691,19 +4680,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4717,19 +4706,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H18" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4743,19 +4732,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4769,19 +4758,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4795,204 +4784,204 @@
         <v>0.375</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="339" customHeight="1" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="119" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46317</v>
       </c>
       <c r="B22" s="18">
         <v>0.375</v>
       </c>
-      <c r="C22" s="18">
-        <v>0.41666666666666669</v>
+      <c r="C22" s="18" t="s">
+        <v>210</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F22" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46317</v>
       </c>
       <c r="B23" s="18">
-        <v>0.4375</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C23" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.39930555555555558</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46317</v>
       </c>
       <c r="B24" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="C24" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46317</v>
       </c>
       <c r="B25" s="18">
-        <v>0.35416666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="C25" s="18">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46317</v>
       </c>
       <c r="B26" s="18">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C26" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46317</v>
       </c>
       <c r="B27" s="18">
-        <v>0.4375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C27" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46317</v>
       </c>
       <c r="B28" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C28" s="18">
         <v>0.41666666666666669</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46317</v>
       </c>
@@ -5003,36 +4992,36 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46317</v>
       </c>
       <c r="B30" s="18">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C30" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s">
         <v>4</v>
@@ -5041,33 +5030,33 @@
         <v>144</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46317</v>
       </c>
       <c r="B31" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C31" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5075,51 +5064,54 @@
         <v>46317</v>
       </c>
       <c r="B32" s="18">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="C32" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F32" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46317</v>
       </c>
       <c r="B33" s="18">
-        <v>0.79166666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C33" s="18">
-        <v>0.85416666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" t="s">
-        <v>17</v>
+        <v>98</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46317</v>
       </c>
@@ -5127,94 +5119,91 @@
         <v>0.4375</v>
       </c>
       <c r="C34" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>17</v>
+        <v>211</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+      <c r="H34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46317</v>
       </c>
       <c r="B35" s="18">
-        <v>8.3333333333333329E-2</v>
+        <v>0.8125</v>
       </c>
       <c r="C35" s="18">
-        <v>0.10416666666666667</v>
-      </c>
-      <c r="D35" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46317</v>
       </c>
       <c r="B36" s="18">
-        <v>0.10416666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="C36" s="18">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="D36" t="s">
-        <v>115</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46317</v>
       </c>
       <c r="B37" s="18">
-        <v>0.15625</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="C37" s="18">
-        <v>0.1875</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H37" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5222,25 +5211,77 @@
         <v>46317</v>
       </c>
       <c r="B38" s="18">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="C38" s="18">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="D38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" t="s">
+        <v>103</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A39" s="12">
+        <v>46317</v>
+      </c>
+      <c r="B39" s="18">
+        <v>0.15625</v>
+      </c>
+      <c r="C39" s="18">
         <v>0.1875</v>
       </c>
-      <c r="C38" s="18">
+      <c r="D39" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" t="s">
+        <v>103</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="12">
+        <v>46317</v>
+      </c>
+      <c r="B40" s="18">
+        <v>0.1875</v>
+      </c>
+      <c r="C40" s="18">
         <v>0.20833333333333334</v>
       </c>
-      <c r="D38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" t="s">
-        <v>113</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H38" t="s">
-        <v>148</v>
+      <c r="D40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>103</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -5266,10 +5307,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -5278,13 +5319,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5298,19 +5339,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5324,16 +5365,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5347,19 +5388,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5373,19 +5414,19 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5399,19 +5440,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5425,19 +5466,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5451,19 +5492,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -5477,16 +5518,16 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5500,19 +5541,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5526,19 +5567,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5552,19 +5593,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5578,19 +5619,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5604,19 +5645,19 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5630,19 +5671,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F15" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5656,19 +5697,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5723,10 +5764,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>2</v>
@@ -5735,13 +5776,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5749,25 +5790,25 @@
         <v>46319</v>
       </c>
       <c r="B2" s="18">
-        <v>0.1875</v>
+        <v>0.6875</v>
       </c>
       <c r="C2" s="18">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5781,19 +5822,19 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5807,19 +5848,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5836,9 +5877,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
@@ -5851,19 +5890,19 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5877,19 +5916,19 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H7" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5903,19 +5942,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5929,19 +5968,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5955,22 +5994,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46319</v>
       </c>
@@ -5981,7 +6020,19 @@
         <v>0.375</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>136</v>
+        <v>126</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -5995,19 +6046,19 @@
         <v>0.40625</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6021,19 +6072,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6047,19 +6098,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6073,19 +6124,19 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -6099,19 +6150,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A77176A-BC69-9247-BEDD-BA81F9DDD514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2926FABB-2215-F14B-99E4-75215772A68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="20760" yWindow="2940" windowWidth="53000" windowHeight="35040" activeTab="3" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="211">
   <si>
     <t>DÍA</t>
   </si>
@@ -95,10 +95,6 @@
   </si>
   <si>
     <t>Almuerzo</t>
-  </si>
-  <si>
-    <t>Diálogos científicos
-Carlos Pacheco</t>
   </si>
   <si>
     <t>CHARLAS WEBINAR MAFB-LFDD
@@ -126,21 +122,6 @@
 Briyith Tatiana Ramírez Villanueva </t>
   </si>
   <si>
-    <t>PEMA - Proyecto estación meteorológica 
-Nelson Eduardo Bejarano Morales
-Edwin Javier Rozo Carrasquilla 
-María Erika Castro Díaz
-Gloria Yomaira Tovar 
-Jazmín Parra Umba
-Semillero de investigación Phobos, proyecto Belt Vision
-CEMID - Edwin Javier Rozo Carrasquilla 
- Colorado Torres David Santiago
- Cotrino Rojas Manuel Alejandro
- Mei Mendoza Dayana Sofía
- Pinilla Martínez Fabian Esteban
- Rodriguez Artiza Nicolás</t>
-  </si>
-  <si>
     <t>Living Lab B201</t>
   </si>
   <si>
@@ -157,13 +138,6 @@
 Maira Alejandra Pulgarín Rodríguez</t>
   </si>
   <si>
-    <t>Retos y posibilidades de la inteligencia artificial en la formación de docentes
-Formato: conferencia
-Saúl Antonio Reyes
-Celebración renovación alta calidad Lic. Informática
-Red de Innovación Educativa, STEM y Nuevas Tecnologías- Carlos Pacheco</t>
-  </si>
-  <si>
     <t>HORA INCIO</t>
   </si>
   <si>
@@ -171,11 +145,6 @@
   </si>
   <si>
     <t>Creative Lab C504</t>
-  </si>
-  <si>
-    <t>Ecoeducación Sonora de la
-Licenciatura en Ciencias Naturales y Educación Ambiental
-Carlos Pacheco</t>
   </si>
   <si>
     <t>Del sofá al mundo: aprender lenguas a través del cine
@@ -183,10 +152,6 @@
   </si>
   <si>
     <t>Salón C508</t>
-  </si>
-  <si>
-    <t>Impacto de la IA en la escuela – Docentes y Estudiantes
-CEMID: DISA</t>
   </si>
   <si>
     <t xml:space="preserve">Proyecto ATS - Todos juntos - Ibagué - virtual
@@ -211,10 +176,6 @@
 Fredy Torres, </t>
   </si>
   <si>
-    <t>Taller de Grafiti
-Daniel Núñez</t>
-  </si>
-  <si>
     <t>Estrategias pedagógicas para la enseñanza de niños y niñas con discapacidad
 Ana María Abella Perdomo
 Invitada por confirmar</t>
@@ -271,18 +232,10 @@
 Arley Camilo Torres Veloza</t>
   </si>
   <si>
-    <t>Voces del Barrio
-Daniel Nuñez</t>
-  </si>
-  <si>
     <t>Audiorio C205</t>
   </si>
   <si>
     <t>Diálogos de Semilleros Ciprés</t>
-  </si>
-  <si>
-    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
-Carlos Pacheco</t>
   </si>
   <si>
     <t>Taller Experiencial con presentación de Caso:Educación con Propósito: Laboratorio de Innovacón Pedagogíca para Transformar Comunidades 
@@ -320,10 +273,6 @@
   </si>
   <si>
     <t>Ciudadanía digital en los Colegios Minuto de Dios
-José Argenis Mendoza</t>
-  </si>
-  <si>
-    <t>Iniciativas de IA para la protección del Medio Ambiente 
 José Argenis Mendoza</t>
   </si>
   <si>
@@ -450,9 +399,6 @@
 Semillero Educación Infantil</t>
   </si>
   <si>
-    <t>CEMID - Sobre convivencia escolar y la prevención del acoso escolar</t>
-  </si>
-  <si>
     <t>Educomunicación, pensamiento crítico y lenguaje desde las experiencias audiovisuales en la CEMID
 Valerie Sophia Prado Velásquez -Evolet Blue Pabón Gómez</t>
   </si>
@@ -517,29 +463,6 @@
 Natalia Martínez - Johana Rodríguez </t>
   </si>
   <si>
-    <t>Taller: Arqueología de la confianza: recuperar el pasado para innovar en educación
-James Ricardo Zorro Monroy, Frendy González y Sandra Patricia Pachón Monsalve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poster Expandido - CEMID
-Arquitectura autosostenible
-1. Ospina Galeano Jorge Esteban 
-2. Parra Moya Julián David
-3. Rodriguez Giraldo Mariana
-4. Torres Díaz Mariana 
-AlgaeX Lab: Huerta Escolar Inteligente.
-1. Lauren Fiallo Mendoza
-2. Sara Valentina Velez Mena
-3. María José Zambrano García
-4. Juliana Ramírez Angulo
-App de las emociones
-1. - Samuel Alejandro García Cuervo 
-2. Nikol Mariana Buitrago Jaramillo 
-3. Laura Sofia Tobar García 
-4. Mariana Quiroga Sánchez 
-</t>
-  </si>
-  <si>
     <t>Taller de Graffiti
 Daniel Núñez, UNIARTES</t>
   </si>
@@ -764,11 +687,6 @@
     <t xml:space="preserve">CUIDALAB 
  William Romero - Pedro Nel Urrea
  Julio Pinzon y colegio Kimmy pernia </t>
-  </si>
-  <si>
-    <t>Acto Inagural
-Oración
-Grupo de Danza Foloklórica Maguaré</t>
   </si>
   <si>
     <t>Palabras de Clausura
@@ -967,6 +885,92 @@
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
 ¿Qué puede llegar a ser una persona? Capacidades humanas como horizonte para la Educación Física 
 Yammir López Brito (España), Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
+  </si>
+  <si>
+    <t>PEMA - Proyecto estación meteorológica 
+Nelson Eduardo Bejarano Morales
+Edwin Javier Rozo Carrasquilla 
+María Erika Castro Díaz
+Gloria Yomaira Tovar 
+Jazmín Parra Umba</t>
+  </si>
+  <si>
+    <t>Semillero de investigación Phobos, proyecto Belt Vision
+CEMID - Edwin Javier Rozo Carrasquilla 
+ Colorado Torres David Santiago
+ Cotrino Rojas Manuel Alejandro
+ Mei Mendoza Dayana Sofía
+ Pinilla Martínez Fabian Esteban
+ Rodriguez Artiza Nicolás</t>
+  </si>
+  <si>
+    <t>Impacto de la IA en la escuela – Docentes y Estudiantes
+Paul Cubillos + 1 Estudinate
+CEMID</t>
+  </si>
+  <si>
+    <t>Acto Inaugural
+Oración
+Grupo de Danza Foloklórica Maguaré</t>
+  </si>
+  <si>
+    <t>Ecoeducación Sonora de la Licenciatura en Ciencias Naturales y Educación Ambiental
+Carlos Pacheco</t>
+  </si>
+  <si>
+    <t>Auditorio C204</t>
+  </si>
+  <si>
+    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
+Andrés Camilo Pérez Rodríguez, Cristian Camilo Ladino Marín</t>
+  </si>
+  <si>
+    <t>Iniciativas de IA para la protección del Medio Ambiente 
+María José Villa Moreno, Danna Valentina Rincon Loaiza</t>
+  </si>
+  <si>
+    <t>El desarrollo humano desde el acondicionamiento físico y el bienestar
+Invitado: Diego Fernando Villamizar Gómez
+Moderadora: Dalis Nury Molina Bustamante</t>
+  </si>
+  <si>
+    <t>Sobre convivencia escolar y la prevención del acoso escolar
+José Argenis Mendoza Suárez
+CEMID</t>
+  </si>
+  <si>
+    <t>AlgaeX Lab: Huerta Escolar Inteligente.
+1. Lauren Fiallo Mendoza
+2. Sara Valentina Velez Mena
+3. María José Zambrano García
+4. Juliana Ramírez Angulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App de las emociones
+1. - Samuel Alejandro García Cuervo 
+2. Nikol Mariana Buitrago Jaramillo 
+3. Laura Sofia Tobar García 
+4. Mariana Quiroga Sánchez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arquitectura autosostenible
+1. Ospina Galeano Jorge Esteban 
+2. Parra Moya Julián David
+3. Rodriguez Giraldo Mariana
+4. Torres Díaz Mariana 
+</t>
+  </si>
+  <si>
+    <t>9:!5</t>
+  </si>
+  <si>
+    <t>Arqueología de la confianza: recuperar el pasado para innovar en educación
+James Ricardo Zorro Monroy, Frendy González y Sandra Patricia Pachón Monsalve</t>
+  </si>
+  <si>
+    <t>¿Cómo se construyen las nociones de violencia en la infancia? Una experiencia de investigación en educación
+Invitado: John Jairo García Díaz
+Moderadora: Nadia Johanna Hernández Ordoñez</t>
   </si>
 </sst>
 </file>
@@ -1455,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -1467,13 +1471,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -1487,7 +1491,7 @@
         <v>0.375</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -1496,10 +1500,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1522,10 +1526,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1539,7 +1543,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
@@ -1548,10 +1552,10 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1565,7 +1569,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -1574,10 +1578,10 @@
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1620,10 +1624,10 @@
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1646,10 +1650,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -1663,7 +1667,7 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
@@ -1672,10 +1676,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1689,7 +1693,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
@@ -1698,10 +1702,10 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1715,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0435A0A-E8EE-B24A-B2EA-F66A17D967D3}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="12" customWidth="1"/>
@@ -1731,10 +1735,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -1743,13 +1747,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1766,16 +1770,16 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1792,16 +1796,16 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1815,19 +1819,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1844,9 +1848,6 @@
       <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
@@ -1859,19 +1860,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1899,19 +1900,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -1925,19 +1926,19 @@
         <v>0.625</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1951,19 +1952,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H10" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -1977,19 +1978,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H11" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2003,19 +2004,19 @@
         <v>0.6875</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H12" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2029,19 +2030,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2055,16 +2056,16 @@
         <v>0.8125</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2078,45 +2079,45 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46315</v>
       </c>
       <c r="B16" s="18">
-        <v>0.79166666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C16" s="18">
-        <v>0.85416666666666663</v>
+        <v>0.375</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2124,51 +2125,51 @@
         <v>46315</v>
       </c>
       <c r="B17" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C17" s="18">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H17" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46315</v>
       </c>
       <c r="B18" s="18">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="C18" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H18" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="85" x14ac:dyDescent="0.2">
@@ -2176,71 +2177,77 @@
         <v>46315</v>
       </c>
       <c r="B19" s="18">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C19" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="12">
+        <v>46315</v>
+      </c>
       <c r="B20" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C20" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+      <c r="A21" s="12">
+        <v>46315</v>
+      </c>
       <c r="B21" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C21" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2248,103 +2255,103 @@
         <v>46315</v>
       </c>
       <c r="B22" s="18">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C22" s="18">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46315</v>
       </c>
       <c r="B23" s="18">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="C23" s="18">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H23" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46315</v>
       </c>
       <c r="B24" s="18">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C24" s="18">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>180</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>168</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46315</v>
       </c>
       <c r="B25" s="18">
-        <v>0.64583333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C25" s="18">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>181</v>
+        <v>0.6875</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="68" x14ac:dyDescent="0.2">
@@ -2352,74 +2359,77 @@
         <v>46315</v>
       </c>
       <c r="B26" s="18">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="C26" s="18">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H26" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46315</v>
       </c>
       <c r="B27" s="18">
-        <v>0.6875</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C27" s="18">
-        <v>0.70833333333333337</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F27" t="s">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="238" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="119" x14ac:dyDescent="0.2">
+      <c r="A28" s="12">
+        <v>46315</v>
+      </c>
       <c r="B28" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C28" s="18">
         <v>0.375</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="E28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H28" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="35" x14ac:dyDescent="0.25">
@@ -2433,19 +2443,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="I29" s="14"/>
     </row>
@@ -2460,19 +2470,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F30" t="s">
         <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2486,45 +2496,45 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F31" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46315</v>
       </c>
       <c r="B32" s="18">
-        <v>0.77083333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C32" s="18">
-        <v>0.83333333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E32" t="s">
         <v>26</v>
       </c>
-      <c r="E32" t="s">
-        <v>43</v>
-      </c>
       <c r="F32" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -2532,361 +2542,343 @@
         <v>46315</v>
       </c>
       <c r="B33" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C33" s="18">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
         <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H33" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="12">
+        <v>46315</v>
+      </c>
       <c r="B34" s="18">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="C34" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="H34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46315</v>
       </c>
       <c r="B35" s="18">
-        <v>0.4375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C35" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
         <v>4</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46315</v>
       </c>
       <c r="B36" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C36" s="18">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F36" t="s">
         <v>4</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H36" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46315</v>
       </c>
       <c r="B37" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C37" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F37" t="s">
         <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="1:9" ht="85" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46315</v>
       </c>
       <c r="B38" s="18">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C38" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F38" t="s">
         <v>4</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
-        <v>147</v>
-      </c>
-      <c r="I38" s="10"/>
-    </row>
-    <row r="39" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46315</v>
       </c>
       <c r="B39" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C39" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F39" t="s">
         <v>4</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H39" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46315</v>
       </c>
       <c r="B40" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C40" s="18">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F40" t="s">
         <v>4</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="H40" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="12">
-        <v>46315</v>
-      </c>
-      <c r="B41" s="18">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C41" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H41" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46315</v>
       </c>
       <c r="B42" s="18">
-        <v>0.44374999999999998</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C42" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F42" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="H42" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46315</v>
       </c>
       <c r="B43" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C43" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F43" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H43" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46315</v>
       </c>
       <c r="B44" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C44" s="18">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F44" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H44" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46315</v>
       </c>
       <c r="B45" s="18">
-        <v>0.35416666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="C45" s="18">
-        <v>0.375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F45" t="s">
         <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="H45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46315</v>
       </c>
       <c r="B46" s="18">
-        <v>0.375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C46" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F46" t="s">
         <v>4</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="H46" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2894,25 +2886,25 @@
         <v>46315</v>
       </c>
       <c r="B47" s="18">
-        <v>0.4375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C47" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F47" t="s">
         <v>4</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H47" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2920,77 +2912,25 @@
         <v>46315</v>
       </c>
       <c r="B48" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="C48" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F48" t="s">
         <v>4</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H48" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="12">
-        <v>46315</v>
-      </c>
-      <c r="B49" s="18">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C49" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" t="s">
-        <v>52</v>
-      </c>
-      <c r="F49" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H49" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="12">
-        <v>46315</v>
-      </c>
-      <c r="B50" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="C50" s="18">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" t="s">
-        <v>4</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H50" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3018,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -3030,13 +2970,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3050,22 +2990,22 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46316</v>
       </c>
@@ -3076,19 +3016,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3104,9 +3044,6 @@
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
@@ -3119,19 +3056,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3145,19 +3082,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -3185,19 +3122,19 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3211,19 +3148,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3237,19 +3174,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3263,19 +3200,19 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3289,19 +3226,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3315,19 +3252,19 @@
         <v>0.375</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3341,19 +3278,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3367,19 +3304,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3393,19 +3330,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H16" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3419,19 +3356,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3445,19 +3382,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H18" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3471,19 +3408,19 @@
         <v>0.375</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3497,19 +3434,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H20" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3523,19 +3460,19 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3549,19 +3486,19 @@
         <v>0.46875</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3575,19 +3512,19 @@
         <v>0.5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3601,19 +3538,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3627,19 +3564,19 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H25" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3653,19 +3590,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -3679,19 +3616,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H27" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3705,19 +3642,19 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H28" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -3731,19 +3668,19 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H29" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3757,19 +3694,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F30" t="s">
         <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -3783,19 +3720,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F31" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -3809,19 +3746,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -3835,19 +3772,19 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
         <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H33" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="204" x14ac:dyDescent="0.2">
@@ -3861,19 +3798,19 @@
         <v>0.625</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H34" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -3887,19 +3824,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
         <v>4</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3913,19 +3850,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
         <v>4</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H36" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -3939,19 +3876,19 @@
         <v>0.6875</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
         <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H37" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="136" x14ac:dyDescent="0.2">
@@ -3965,42 +3902,42 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
         <v>4</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H38" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46316</v>
       </c>
       <c r="B39" s="18">
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C39" s="18">
         <v>0.85416666666666663</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>68</v>
+        <v>203</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="153" x14ac:dyDescent="0.2">
@@ -4014,16 +3951,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4037,19 +3974,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F41" t="s">
         <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4063,19 +4000,19 @@
         <v>0.375</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F42" t="s">
         <v>4</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H42" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="119" x14ac:dyDescent="0.2">
@@ -4089,19 +4026,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F43" t="s">
         <v>4</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H43" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -4115,19 +4052,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F44" t="s">
         <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H44" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4141,19 +4078,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F45" t="s">
         <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="H45" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4167,19 +4104,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F46" t="s">
         <v>4</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="H46" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4193,19 +4130,19 @@
         <v>0.375</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F47" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="H47" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4219,19 +4156,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F48" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H48" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4245,24 +4182,24 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E49" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
         <v>4</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H49" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E52" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -4272,7 +4209,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{610C11C2-B771-9D44-A689-56619F68B052}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="12"/>
@@ -4290,10 +4227,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -4302,13 +4239,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4322,19 +4259,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4348,19 +4285,19 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="H3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4374,19 +4311,19 @@
         <v>0.40625</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4400,19 +4337,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4428,9 +4365,6 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
@@ -4443,19 +4377,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4469,19 +4403,19 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4495,19 +4429,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -4535,19 +4469,19 @@
         <v>0.625</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4561,19 +4495,19 @@
         <v>0.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H12" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -4587,22 +4521,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46317</v>
       </c>
@@ -4613,19 +4547,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -4639,19 +4573,19 @@
         <v>0.375</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4665,19 +4599,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H16" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -4691,19 +4625,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4717,19 +4651,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H18" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4743,19 +4677,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4769,19 +4703,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -4795,204 +4729,204 @@
         <v>0.375</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="339" customHeight="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="119" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46317</v>
       </c>
       <c r="B22" s="18">
         <v>0.375</v>
       </c>
-      <c r="C22" s="18">
-        <v>0.41666666666666669</v>
+      <c r="C22" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F22" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46317</v>
       </c>
       <c r="B23" s="18">
-        <v>0.4375</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C23" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.39930555555555558</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46317</v>
       </c>
       <c r="B24" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="C24" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46317</v>
       </c>
       <c r="B25" s="18">
-        <v>0.35416666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="C25" s="18">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46317</v>
       </c>
       <c r="B26" s="18">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C26" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46317</v>
       </c>
       <c r="B27" s="18">
-        <v>0.4375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C27" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46317</v>
       </c>
       <c r="B28" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C28" s="18">
         <v>0.41666666666666669</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46317</v>
       </c>
@@ -5003,71 +4937,71 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46317</v>
       </c>
       <c r="B30" s="18">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C30" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
         <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46317</v>
       </c>
       <c r="B31" s="18">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C31" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5075,51 +5009,54 @@
         <v>46317</v>
       </c>
       <c r="B32" s="18">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="C32" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46317</v>
       </c>
       <c r="B33" s="18">
-        <v>0.79166666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C33" s="18">
-        <v>0.85416666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" t="s">
-        <v>17</v>
+        <v>96</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46317</v>
       </c>
@@ -5127,94 +5064,91 @@
         <v>0.4375</v>
       </c>
       <c r="C34" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>17</v>
+        <v>209</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="H34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46317</v>
       </c>
       <c r="B35" s="18">
-        <v>8.3333333333333329E-2</v>
+        <v>0.8125</v>
       </c>
       <c r="C35" s="18">
-        <v>0.10416666666666667</v>
-      </c>
-      <c r="D35" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46317</v>
       </c>
       <c r="B36" s="18">
-        <v>0.10416666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="C36" s="18">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="D36" t="s">
-        <v>115</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46317</v>
       </c>
       <c r="B37" s="18">
-        <v>0.15625</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="C37" s="18">
-        <v>0.1875</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H37" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5222,25 +5156,77 @@
         <v>46317</v>
       </c>
       <c r="B38" s="18">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="C38" s="18">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="D38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A39" s="12">
+        <v>46317</v>
+      </c>
+      <c r="B39" s="18">
+        <v>0.15625</v>
+      </c>
+      <c r="C39" s="18">
         <v>0.1875</v>
       </c>
-      <c r="C38" s="18">
+      <c r="D39" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="12">
+        <v>46317</v>
+      </c>
+      <c r="B40" s="18">
+        <v>0.1875</v>
+      </c>
+      <c r="C40" s="18">
         <v>0.20833333333333334</v>
       </c>
-      <c r="D38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" t="s">
-        <v>113</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H38" t="s">
-        <v>148</v>
+      <c r="D40" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H40" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -5266,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -5278,13 +5264,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5298,19 +5284,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5324,16 +5310,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5347,19 +5333,19 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5373,19 +5359,19 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5399,19 +5385,19 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5425,19 +5411,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5451,19 +5437,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -5477,16 +5463,16 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5500,19 +5486,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5526,19 +5512,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5552,19 +5538,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5578,19 +5564,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5604,19 +5590,19 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -5630,19 +5616,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5656,19 +5642,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5723,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>2</v>
@@ -5735,13 +5721,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5749,25 +5735,25 @@
         <v>46319</v>
       </c>
       <c r="B2" s="18">
-        <v>0.1875</v>
+        <v>0.6875</v>
       </c>
       <c r="C2" s="18">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -5781,19 +5767,19 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -5807,19 +5793,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -5836,9 +5822,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
@@ -5851,19 +5835,19 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5877,19 +5861,19 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H7" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5903,19 +5887,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5929,19 +5913,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="102" x14ac:dyDescent="0.2">
@@ -5955,22 +5939,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46319</v>
       </c>
@@ -5981,7 +5965,19 @@
         <v>0.375</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>136</v>
+        <v>124</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="85" x14ac:dyDescent="0.2">
@@ -5995,19 +5991,19 @@
         <v>0.40625</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -6021,19 +6017,19 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6047,19 +6043,19 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -6073,19 +6069,19 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -6099,19 +6095,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2926FABB-2215-F14B-99E4-75215772A68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61CB33F7-557D-489E-A545-1079DBA8762B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20760" yWindow="2940" windowWidth="53000" windowHeight="35040" activeTab="3" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="2" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Viernes 23 de octubre" sheetId="7" r:id="rId5"/>
     <sheet name="Sabado 24 de octubre" sheetId="8" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,21 +44,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="212">
   <si>
     <t>DÍA</t>
   </si>
   <si>
+    <t>HORA INCIO</t>
+  </si>
+  <si>
+    <t>HORA FINAL</t>
+  </si>
+  <si>
+    <t>EVENTO</t>
+  </si>
+  <si>
     <t>LUGAR</t>
   </si>
   <si>
-    <t>EVENTO</t>
+    <t>CENTRO UNIVERSITARIO</t>
+  </si>
+  <si>
+    <t>FORMATO</t>
+  </si>
+  <si>
+    <t>MODALIDAD</t>
+  </si>
+  <si>
+    <t>LINK</t>
+  </si>
+  <si>
+    <t>Acto Inaugural
+Oración
+Grupo de Danza Foloklórica Maguaré</t>
   </si>
   <si>
     <t>Teatro Minuto de Dios</t>
   </si>
   <si>
     <t>Calle 80</t>
+  </si>
+  <si>
+    <t>Presentación cultural</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Palabras de bienvenida
+Dra Juanita Reina</t>
+  </si>
+  <si>
+    <t>Fire Pitch</t>
+  </si>
+  <si>
+    <t>Conferencia Principal
+Condición digital y residuos analógicos necesarios
+Diego Fernando Barragán
+Decano facultad de Educación
+Universidad de la Salle</t>
+  </si>
+  <si>
+    <t>Conferencia</t>
+  </si>
+  <si>
+    <t>Hackear el futuro de la Educación
+María Fernanda González Velasco, Directora ejecutiva Ascofae..  Diego Escallón, Subsecretario de calidad y pertinencia SED y Oscar Yesid Aparicio, Presidente Academia Hispanoamericana de docotores.
+Modera: Juanita Reina Zambrano</t>
+  </si>
+  <si>
+    <t>Conversatorio</t>
   </si>
   <si>
     <t>Receso</t>
@@ -71,8 +125,17 @@
 Laura Chingate, Andrei Morales y Marcela Chávez</t>
   </si>
   <si>
-    <t>Palabras de bienvenida
-Dra Juanita Reina</t>
+    <t>Flipped Talk</t>
+  </si>
+  <si>
+    <t>Conversatorio: Corporalidad y Aprendizaje Experiencial
+   Miguel Diaz (Perú) Alicia López (México)
+Eliana Monroy, Gonzalo Amaya, German Preciado,  (Colombia) 
+ Modera: Pedro Nel Urrea Roa</t>
+  </si>
+  <si>
+    <t>Palabras de Clausura
+Presentación musical CEMID</t>
   </si>
   <si>
     <t>Educación para todos desde la perspectiva de garantía de derechos y la educación para todos.  
@@ -81,38 +144,13 @@
 Kathery Yessenia Mendoza Vargas</t>
   </si>
   <si>
+    <t>Auditorio B206</t>
+  </si>
+  <si>
     <t>El DUA desde la neurociencia.
 CEMID 
 Judy Andrea Rueda Gómez 
 Lina María Castañeda Cisneros</t>
-  </si>
-  <si>
-    <t>De la categoría C al corazón: el viaje de Praxis Pedagógica
-Benjamín Barón, Centro de Investigación CIIDE</t>
-  </si>
-  <si>
-    <t>Coffee Break &amp; Networiking</t>
-  </si>
-  <si>
-    <t>Almuerzo</t>
-  </si>
-  <si>
-    <t>CHARLAS WEBINAR MAFB-LFDD
-Dalis Molina</t>
-  </si>
-  <si>
-    <t>Auditorio B205</t>
-  </si>
-  <si>
-    <t>Virtual</t>
-  </si>
-  <si>
-    <t>Encuentro de Prácticas Pedagógicas Emergentes y Creativas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Old dogs, new tricks: Life long learning through exercise for older adults"
-Virtual sincrónico
-Miranda Foyster </t>
   </si>
   <si>
     <t xml:space="preserve">Batukids  – ATS
@@ -122,7 +160,147 @@
 Briyith Tatiana Ramírez Villanueva </t>
   </si>
   <si>
+    <t>Conferencia performática</t>
+  </si>
+  <si>
+    <t>Híbrido</t>
+  </si>
+  <si>
+    <t>Coffee Break &amp; Networiking</t>
+  </si>
+  <si>
+    <t>Diálogos de Semilleros Ciprés</t>
+  </si>
+  <si>
+    <t>Poster expandido</t>
+  </si>
+  <si>
+    <t>Almuerzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+¿Qué puede llegar a ser una persona? Capacidades humanas como horizonte para la Educación Física 
+Yammir López Brito (España), Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA 
+Actividad física adaptada: Educación para la salud y prescripción del ejercicio físico. 
+ Luciana Brito - Argentina</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Diagnóstico morfofuncional del perfil de fuerza-velocidad horizontal en el contexto del deporte escolar regional
+Yohandis Abad Camejo, Francisco Freyre Vazquez, Abel Emilio Campaña Garzon - Cuba</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Caracterización de la fuerza en miembros inferiores en futbolistas prejuveniles de la Escuela Nueva Era de Sogamoso como apoyo a la educación física escolar.
+Nataly Alejandra Velandia Naranjo</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Implementación de la Plataforma de Educación física (PEF)
+Pablo Paúl Almeyda Torres, Susana Elizabeth Saravia Tasayco, Jimmy Alexandre Vergara Blas. Perú</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Educación Física, deporte y enseñanza: un análisis de la política curricular de Educación Física en Argentina
+Emiliozzi M. Valeria, Tocco Cecilia, Goldsworthy Jeremías Jesús</t>
+  </si>
+  <si>
+    <t>Retos y posibilidades de la inteligencia artificial en la formación de docentes
+Saúl Antonio Reyes
+Celebración renovación alta calidad Lic. Informática</t>
+  </si>
+  <si>
+    <t>Auditorio C204</t>
+  </si>
+  <si>
+    <t>CHARLAS WEBINAR MAFB-LFDD
+Dalis Molina</t>
+  </si>
+  <si>
+    <t>Virtual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Old dogs, new tricks: Life long learning through exercise for older adults"
+Virtual sincrónico
+Miranda Foyster </t>
+  </si>
+  <si>
+    <t>Auditorio B205</t>
+  </si>
+  <si>
+    <t>Co-crear lo común: Wikimedia, laboratorios ciudadanos y apropiacion social del conocimiento.
+Bernardo Caycedo</t>
+  </si>
+  <si>
+    <t>Experiencia en la construcción de textos infantiles en primaria, para participar en el VI encuentro de escritores
+Jennifer Corredor Merchán
+Nancy Edith Sierra Murillo  
+(+ 2 estudiantes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"El Código Deontológico y Ético del Entrenador Deportivo en Colombia y otras consideraciones"
+Colegio Colombiano de Entrenamiento Deportivo
+Aldover Alexander Colorado Castaño </t>
+  </si>
+  <si>
+    <t>De la categoría C al corazón: el viaje de Praxis Pedagógica
+Benjamín Barón, Centro de Investigación CIIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+ Enfoque de género y el lenguaje no sexista en la Educación Física primaria en el marco de la Nueva Escuela Mexicana
+Alicia López     (México)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+Evaluar el proceso y no solo el producto: el portafolio digital en la formación del profesorado de Educación Física 
+Josep Campos-Rius </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+ El Aprendizaje Servicio y Formación Docente en Educación Física
+Miguel Aquilino Diaz Barboza (Perú) </t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Gerencia curricular dialógica pentadimensional y formación de competencias investigativas en educación física universitaria: revisión integrativa.                                          
+Jorge Daniel Miranda Guzmán(Colombia)</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA 
+Diagnóstico de competencias genéricas en estudiantes universitarios como base para una estrategia con LEGO Serious Play                         
+Melissa Andrea Laiton Garnica(Colombia)</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+De la teoría a la praxis profesional: legislación, TIC e inclusión como ejes de transformación en la Educación Física escolar
+Yeison José Becerra Ariza (Colombia)</t>
+  </si>
+  <si>
+    <t>PEMA - Proyecto estación meteorológica 
+Nelson Eduardo Bejarano Morales
+Edwin Javier Rozo Carrasquilla 
+María Erika Castro Díaz
+Gloria Yomaira Tovar 
+Jazmín Parra Umba</t>
+  </si>
+  <si>
     <t>Living Lab B201</t>
+  </si>
+  <si>
+    <t>Kids Untalk</t>
+  </si>
+  <si>
+    <t>Semillero de investigación Phobos, proyecto Belt Vision
+CEMID - Edwin Javier Rozo Carrasquilla 
+ Colorado Torres David Santiago
+ Cotrino Rojas Manuel Alejandro
+ Mei Mendoza Dayana Sofía
+ Pinilla Martínez Fabian Esteban
+ Rodriguez Artiza Nicolás</t>
   </si>
   <si>
     <t>Aula Inmersiva Maestría en Ambientes de Aprendizaje
@@ -138,20 +316,39 @@
 Maira Alejandra Pulgarín Rodríguez</t>
   </si>
   <si>
-    <t>HORA INCIO</t>
-  </si>
-  <si>
-    <t>HORA FINAL</t>
+    <t xml:space="preserve">CUIDALAB 
+ William Romero - Pedro Nel Urrea
+ Julio Pinzon y colegio Kimmy pernia </t>
   </si>
   <si>
     <t>Creative Lab C504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUIDALAB 
+Taller Corpoemoción 
+Pedro Nel Urrea, Julio Pinzon y colegio Kimmy Pernia </t>
+  </si>
+  <si>
+    <t>Ecoeducación Sonora de la Licenciatura en Ciencias Naturales y Educación Ambiental
+Carlos Pacheco</t>
   </si>
   <si>
     <t>Del sofá al mundo: aprender lenguas a través del cine
 Andrea Carolina Rodríguez Salazar</t>
   </si>
   <si>
+    <t xml:space="preserve">Relacionamiento de redes   docentes CONGRESO IDRM -REDDI EDUFISICA </t>
+  </si>
+  <si>
     <t>Salón C508</t>
+  </si>
+  <si>
+    <t>Impacto de la IA en la escuela – Docentes y Estudiantes
+Paul Cubillos + 1 Estudinate
+CEMID</t>
+  </si>
+  <si>
+    <t>Pistacho Talk</t>
   </si>
   <si>
     <t xml:space="preserve">Proyecto ATS - Todos juntos - Ibagué - virtual
@@ -169,11 +366,11 @@
  Vásquez Casallas, Johan Samuel</t>
   </si>
   <si>
-    <t>Plazoleta Rafael García Herreros</t>
-  </si>
-  <si>
     <t xml:space="preserve">Presentación Artes Escénicas 
 Fredy Torres, </t>
+  </si>
+  <si>
+    <t>Plazoleta Rafael García Herreros</t>
   </si>
   <si>
     <t>Estrategias pedagógicas para la enseñanza de niños y niñas con discapacidad
@@ -185,44 +382,6 @@
   </si>
   <si>
     <t>Soacha</t>
-  </si>
-  <si>
-    <t>Conferencia Principal
-Condición digital y residuos analógicos necesarios
-Diego Fernando Barragán
-Decano facultad de Educación
-Universidad de la Salle</t>
-  </si>
-  <si>
-    <t>Auditorio B206</t>
-  </si>
-  <si>
-    <t>Retos y posibilidades de la inteligencia artificial en la formación de docentes
-Saúl Antonio Reyes
-Celebración renovación alta calidad Lic. Informática</t>
-  </si>
-  <si>
-    <t>Co-crear lo común: Wikimedia, laboratorios ciudadanos y apropiacion social del conocimiento.
-Bernardo Caycedo</t>
-  </si>
-  <si>
-    <t>Experiencia en la construcción de textos infantiles en primaria, para participar en el VI encuentro de escritores
-Jennifer Corredor Merchán
-Nancy Edith Sierra Murillo  
-(+ 2 estudiantes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"El Código Deontológico y Ético del Entrenador Deportivo en Colombia y otras consideraciones"
-Colegio Colombiano de Entrenamiento Deportivo
-Aldover Alexander Colorado Castaño </t>
-  </si>
-  <si>
-    <t>Pistacho Talk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUIDALAB 
-Taller Corpoemoción 
-Pedro Nel Urrea, Julio Pinzon y colegio Kimmy Pernia </t>
   </si>
   <si>
     <t>FISIOLAB, una estrategia didáctica interdisciplinar fundamentada en el enfoque STEAM
@@ -232,38 +391,100 @@
 Arley Camilo Torres Veloza</t>
   </si>
   <si>
+    <t>Concierto didáctico: Contrapunto Latino-Barroco para mentes inquietas
+Johan Corrales
+Bélgica-Colombia</t>
+  </si>
+  <si>
     <t>Audiorio C205</t>
   </si>
   <si>
-    <t>Diálogos de Semilleros Ciprés</t>
+    <t>Encuentro de Prácticas Pedagógicas Emergentes y Creativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA  
+Gerente Gonzalo Amaya 8:00 a 8:30am
+Estrategia Cundinamarca deporte incluyente
+Danny Quiñones
+ </t>
+  </si>
+  <si>
+    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
+Andrés Camilo Pérez Rodríguez, Cristian Camilo Ladino Marín</t>
   </si>
   <si>
     <t>Taller Experiencial con presentación de Caso:Educación con Propósito: Laboratorio de Innovacón Pedagogíca para Transformar Comunidades 
 EDULAB</t>
   </si>
   <si>
-    <t>Auditorio C205</t>
+    <t>Taller</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA 
+RUTA STEM EN EDUCACIÓN FÍSICA  
+Pedro Nel Urrea Roa</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Juegos Electrónicos
+Alexander Ospina Bolaños - Presidente PAMESCO - Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+ Presentación Libro Evaluación y Capacidades Físicas Básicas: Una visión desde la interdisciplinariedad
+Eliana Sofía Monroy Muñoz(Colombia) </t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Actividad física y regulación emocional en estudiantes universitarios 
+Deiby Alexander Lara Garzón &amp; Nayelly Tatiana Barragán Cañón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+Desarrollo de Habilidades Blandas en Educación Básica y Media
+Luis Uriel Méndez Solano - IED Alfonso Reyes Echandía. 
+ </t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Cuerpos que piensan, mentes que juegan: Estrategias sociomotrices para la formación de sujetos críticos en el siglo XXI.
+John Edwin Valencia Moreno y Oscar Javier Quintero  - Secretaria de Educación Bogotá</t>
   </si>
   <si>
     <t>Habitar el miedo y la incertidumbre en la práctica educativa 
 Laura Hurtado</t>
   </si>
   <si>
+    <t>Auditorio C205</t>
+  </si>
+  <si>
     <t>Más allá del clic: Cómo medir la calidad pedagógica real de un RED musical
-Jorge Alvarado - UNAD</t>
-  </si>
-  <si>
-    <t>Interpretaciones arqueomusicoĺogicas: Hacia una lectura ecosistemática del objeto sonoro prehispánico Taitona, Sinú y Muisca
+Jorge Alvarado 
+UNAD</t>
+  </si>
+  <si>
+    <t>El sonido de lo sagrado: Interpretaciones iconográficas y acústicas de los objetos sonoros Tairona
 Luisa Fernanda Arias
 UNAD</t>
   </si>
   <si>
+    <t xml:space="preserve">
+Enfoques y metodologías actuales para la formación Universitaria en entrenamiento auditivo y solfeo
+Ana María Moreno 
+Universidad de Cundinamarca</t>
+  </si>
+  <si>
+    <t>Divulgación social del conocimiento: posibilidades de participación académica
+Jonathan Caicedo Girón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferencia Magistral: "Apego y desarrollo del lenguaje en la primera infancia", abordando el apego como componente biológico y neurológico.
+Dr. Fernando Eli Ledesma Pérez
+UCV - Lima Perú </t>
+  </si>
+  <si>
     <t xml:space="preserve">Taller vivencial: "Leer con el cuerpo y la voz", una experiencia práctica orientada a docentes y agentes educativos sobre lectura en voz alta, narración corporal y mediación afectiva como estrategias de literacidad emergente en la primera infancia.
 Dra. Dora Tamariz  UCV - Lima  - Perú  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presentación memoria biocultural y pedagogías para la ruralidad
-Licencitura en Humanidades </t>
   </si>
   <si>
     <t>Uso de la Inteligencia Artificial en el Aprendizaje  de niños y niñas en los colegios (Alfabetización para la docencia escolar)
@@ -274,6 +495,10 @@
   <si>
     <t>Ciudadanía digital en los Colegios Minuto de Dios
 José Argenis Mendoza</t>
+  </si>
+  <si>
+    <t>Iniciativas de IA para la protección del Medio Ambiente 
+María José Villa Moreno, Danna Valentina Rincon Loaiza</t>
   </si>
   <si>
     <t xml:space="preserve">Proyecto ATS ECO - Ibagué
@@ -284,512 +509,6 @@
 4. Diego Alejandro Saray Moreno  </t>
   </si>
   <si>
-    <t xml:space="preserve">El Viaje de Nogai: Guardianes de la Diversidad
-Living Lab UNIMINUTO  360
-Andrés Rico, Maryuri Agudelo y Zaily García </t>
-  </si>
-  <si>
-    <t>Didáctica del Contagio
-Andrés Rojas</t>
-  </si>
-  <si>
-    <t>Diálogos científicos
-Virtual
-Carlos Pacheco</t>
-  </si>
-  <si>
-    <t>Del prompt a la experiencia de aprendizaje: inteligencia artificial y diseño instruccional con sentido pedagógico 
-Karla Beatriz Gómez Santana
-Kenia Viridiana Ocampo Vera, 
-Universidad de Guadalajara
-Enlace: https://teams.microsoft.com/meet/277921384618913?p=RKSqlSnDTLi83MwWvY</t>
-  </si>
-  <si>
-    <t>Estrategia tejer calidad 
-Paul Brayan Cubillos Cabrera
-José Luis Gaitán Mendoza 
-SED - CEMID</t>
-  </si>
-  <si>
-    <t>Proyecto ruta emprender, Territorializar la escuela escolarizar el territorio
-Diana Guadalupe Garnica Jiménez.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estrategias del siglo XXI para competir ante la desigualdad educativa entre zonas rurales y urbanas.
-Samuel Andrés Camargo González, 
-Samuel David Siado Aguilar, 
-María Paula Amaya Betancourt, 
-Andrés Beltrán Moreno, 
-Samuel López Jiménez, </t>
-  </si>
-  <si>
-    <t>Semillero Café sentipensante 
-Juan Esteban Carreño González
-Isaac David Fuentes Durán 
-Linda Saray Martinez Ortiz
-Melany Sareth Rueda Lea</t>
-  </si>
-  <si>
-    <t>Taller  "Inventario de pérdidas"
-Juliana Jaramillo Pabón</t>
-  </si>
-  <si>
-    <t>"Recital Poético por los caminos de Colombia
-Conferencia performática
-Cesar Julio Martinez Gil y Hector Cadena
-Encargado: red pedagogías emergentes y creativas"</t>
-  </si>
-  <si>
-    <t>Conversatorio Pensamiento de la Educación Física
-Julio Pinzón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auditorio Principal </t>
-  </si>
-  <si>
-    <t>San Camilo</t>
-  </si>
-  <si>
-    <t>Prácticas reflexivas
-Óscar Andrés Mosquera</t>
-  </si>
-  <si>
-    <t>Performance British Culture and Literature: Shakespeare in Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xeropan - Effective and fun language learning for the dedicated. 
-Ákos Huszár- Budapest, Hungary  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pearson education: international English exams </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oiga Profe Venga le Cuento....La Ruta del Reto 
-Claudia Avila-Edgar Zambrano </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La memoria biocultural en la resignificación del cuidado de la vida y la sostenibilidad de la biodiversidad del Municipio de El Rosal en Cundinamarca
-Laidy Valentina Prieto - Mónica Paola Díaz Oliveros </t>
-  </si>
-  <si>
-    <t>Divulgación social del conocimiento: posibilidades de participación académica
-Jonathan Caicedo Girón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conferencia Magistral: "Apego y desarrollo del lenguaje en la primera infancia", abordando el apego como componente biológico y neurológico.
-Dr. Fernando Eli Ledesma Pérez
-UCV - Lima Perú </t>
-  </si>
-  <si>
-    <t>Lanzamientos editoriales 
-Licenciatura en Humanidades y lengua Castellana</t>
-  </si>
-  <si>
-    <t>Presentación libro "Semillero en Lliteratura Infantil" Licenciatura en humanidades y lengua castellana
- Jonathan Caicedo Grión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pais Invitado: Mexico Singit
-Innovacion Educativa para el aprendizaje
-Guillermo Nuchowich </t>
-  </si>
-  <si>
-    <t>Construcción de la identidad en la primera infancia a través de prácticas pedagógicas  basadas en el juego, la participación y la diversidad en el aula
-Briyeth Michelle Mogollón Ascanio y Karen Daniela Álvarez Carranza 
-Semillero Educación Infantil</t>
-  </si>
-  <si>
-    <t>Educomunicación, pensamiento crítico y lenguaje desde las experiencias audiovisuales en la CEMID
-Valerie Sophia Prado Velásquez -Evolet Blue Pabón Gómez</t>
-  </si>
-  <si>
-    <t>PensArte
-Javier Maury (CoordAcadémico) - Katherine Rojas (DGC)
-Rodríguez Ruíz Isabella
-Jiménez Castillo Sara Michell
-Fonseca Chávez Ana Sofía
-Rodríguez Perilla Ana María</t>
-  </si>
-  <si>
-    <t>Investigación Cualitativa 
-Prof. Miguel Valdivia Pinto
-Universidad César Vallejo. Perú. (virtual)</t>
-  </si>
-  <si>
-    <t>Ecología de la retención estudiantil en la Educación Superior. 
-Profesora Asociada, Pilar Mendoza
-Universidad de Missouri y Directora CIIDE</t>
-  </si>
-  <si>
-    <t>Innovando desde la primera capa hasta el núcleo
-Nelson Orellano Llinás
-CEMID</t>
-  </si>
-  <si>
-    <t>Modelo de implementación STEM - MD
-Diana Marcela Valencia
-CEMID</t>
-  </si>
-  <si>
-    <t>Taller Vendaje Neuro Muscular y Kinesiotype
-Brayan García</t>
-  </si>
-  <si>
-    <t>CEMID - El Cuerpo que nos Une
-William Martínez Lievano
-Eric Guerra Charris</t>
-  </si>
-  <si>
-    <t>Desafiar Para Pensar: Experiencias Formativas para Desarrollar el Pensamiento Computacional
-Daniela Paola Urrea Diaz ,Liced Katerin Gómez Vega, Sandra Milena Bermúdez Bermúdez ,Miguel Alexander Vergara Mendoza y Nelson Enrique Orellano Llínas</t>
-  </si>
-  <si>
-    <t>Conversatorio Escenario Pedagógico Pensamiento de la Educación Física
-Anderson David Garzón Sichaca</t>
-  </si>
-  <si>
-    <t>Salòn C508</t>
-  </si>
-  <si>
-    <t>Encuentro de Estudiantes
-IDRM-REDDI
- Universidad Autonoma del Estado de Mexico, Universidad popular  del cesar de Colombia,  Universidad Atlantico y UniminutO</t>
-  </si>
-  <si>
-    <t>Conversatorio Docentes Educación Física-SENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EcoFinanzas
-Natalia Martínez - Johana Rodríguez </t>
-  </si>
-  <si>
-    <t>Taller de Graffiti
-Daniel Núñez, UNIARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presentación investigación LILEX Madrid
-Ana María Rocha Tamayo, Marisela Niño Monsalve, Norma Clemencia Rodríguez Arroyave, Claudia Alejandra Pineda Silva.
-Link de conexión: https://teams.microsoft.com/meet/241575852914896?p=8CM4487YPTL7uBv9Q5   </t>
-  </si>
-  <si>
-    <t>Madrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGISTRO </t>
-  </si>
-  <si>
-    <t>Mural de la experiencia</t>
-  </si>
-  <si>
-    <t>Zipaquirá</t>
-  </si>
-  <si>
-    <t>Muévete sin Barreras: Unplugged Pedagógico por la Inclusión</t>
-  </si>
-  <si>
-    <t>Charla con invitado paralimpico</t>
-  </si>
-  <si>
-    <t>Teaching English in Colombia: Paradigms, People &amp; Practice
-Alejandro Tabares
-CU- Girardot</t>
-  </si>
-  <si>
-    <t>Girardot</t>
-  </si>
-  <si>
-    <t>Cuidado Integral de las Personas con Discapacidad: Experiencias en el Contexto Australiano
-Virtual sincrónico
-Yara De Jesus Correia E Silva (Australia)</t>
-  </si>
-  <si>
-    <t>MINDEPORTES - Juegos Ancestrales y Tradicionales en los Territorios de Colombia
-Cristian Castellanos 
-(Presencial- virtual )</t>
-  </si>
-  <si>
-    <t>Más allá de los subtítulos: cómo el cine nos ayuda a aprender lenguas y cruzar fronteras 
-Andrea Carolina Rodríguez Salazar 
-LLEI Madrid</t>
-  </si>
-  <si>
-    <t>La literatura una ventana al mundo y una herramienta para la inclusión global  
-Laura Viviana Sechagua Sechagua 
-LLEI Madrid</t>
-  </si>
-  <si>
-    <t>El desafío de enseñar tecnología aplicada al arte en la era de la inteligencia artificial
-Emiliano Causa, Universidad Nacional de La Plata y Universidad Nacional del Arte
-Argentina</t>
-  </si>
-  <si>
-    <t>Sabio Mutis Inmersion  proposal workshop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aventura gamificada en el living lab
-Master Daniel Diaz
-Licenciatura en Lenguas Extranjeras Bogota Presencial
-Red de multilinguismo y pensamiento glocal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Viaje de Nogai: Guardianes de la Diversidad
-Living Lab UNIMINUTO  360, Andrés Rico, Maryuri Agudelo y Zaily García </t>
-  </si>
-  <si>
-    <t>CRAII 3 Piso</t>
-  </si>
-  <si>
-    <t>Perdomo</t>
-  </si>
-  <si>
-    <t>Conversatorio Pensamiento de la Educación Física
-Omar Cantor &amp; Jorge Rodríguez</t>
-  </si>
-  <si>
-    <t>Inclusive meeting for the design of Educational materials
-Karina Garcia
-LLEID</t>
-  </si>
-  <si>
-    <t>Cabina de sonido y
-plazoleta primer piso (edificio A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres en la Cima 
-Egnan Yesid Alvarez Cruz
-Dalis Nury Molina Bustamante
-</t>
-  </si>
-  <si>
-    <t>Por Confirmar</t>
-  </si>
-  <si>
-    <t>Two languages, one voice: Sign language and English
-PhD Jhon Farfan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movimiento que incluye, infancias que transforman 
-CU Madrid- instalaciones Zoraida Cadavid de Sierra 
-Carlos Fuentes Rios, José David Peralta, Claudia Alejandra Pineda </t>
-  </si>
-  <si>
-    <t>"Movimiento que incluye, infancias que transforman 
-CU Madrid- instalaciones Zoraida Cadavid de Sierra 
-Carlos Fuentes Rios, José David Peralta, Claudia Alejandra Pineda</t>
-  </si>
-  <si>
-    <t>Taller Arte, inclusión y sensibilidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flipped Talk - Construcción colaborativa </t>
-  </si>
-  <si>
-    <t>Fire Pitch -  Innovación en acción: 7 Cuatrimestre (3 grupos) 8 Cuatrimestre (2 grupos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Pitch -  Innovación en acción: 9 Cuatrimestre (2 grupos)  - 10 Cuatrimestre  (2 grupos) </t>
-  </si>
-  <si>
-    <t>Centro Nacional de las Artes - Delia Zapata</t>
-  </si>
-  <si>
-    <t>Conferencia</t>
-  </si>
-  <si>
-    <t>Conferencia performática</t>
-  </si>
-  <si>
-    <t>Poster expandido</t>
-  </si>
-  <si>
-    <t>Flipped Talk</t>
-  </si>
-  <si>
-    <t>FORMATO</t>
-  </si>
-  <si>
-    <t>MODALIDAD</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Híbrido</t>
-  </si>
-  <si>
-    <t>Kids Untalk</t>
-  </si>
-  <si>
-    <t>Fire Pitch</t>
-  </si>
-  <si>
-    <t>Presentación cultural</t>
-  </si>
-  <si>
-    <t>Taller</t>
-  </si>
-  <si>
-    <t>Concierto didáctico: Contrapunto Latino-Barroco para mentes inquietas
-Johan Corrales
-Bélgica-Colombia</t>
-  </si>
-  <si>
-    <t>Experiencia</t>
-  </si>
-  <si>
-    <t>Conferencia Performática</t>
-  </si>
-  <si>
-    <t>Unplugged pedagógico</t>
-  </si>
-  <si>
-    <t>Narrativas de infancias para el reconocimiento intercultural
-Edgar Zambrano, Diana Reyes, Ángel Téllez y David Garzón)</t>
-  </si>
-  <si>
-    <t>Poster Expandido</t>
-  </si>
-  <si>
-    <t>Técnicas de Rehabilitación y Recuperación Muscular
-Stiff García</t>
-  </si>
-  <si>
-    <t>Cuidado Integral de la Persona Mayor: Experiencias en el Contexto Australiano
-Lina María Sierra (Australia)</t>
-  </si>
-  <si>
-    <t>Proyecto de Investigación Creación
-Las Formas del Vacío - Artes  Expandidas: Circo, Danza, Audiovisual, Música, Tecnología.
-Diego Felipe Gaitán, Alejandro Andrade</t>
-  </si>
-  <si>
-    <t>Cl. 11 #5 - 60, Bogotá</t>
-  </si>
-  <si>
-    <t>Unplugged Pedagógico</t>
-  </si>
-  <si>
-    <t>Aprendiendo a través del lenguaje visual vernaculo 
-Christian Briceño</t>
-  </si>
-  <si>
-    <t>Pistacho Talk - Ideas que transforman (1. Dra. Yohana González Bohórquez) 2. Dra. Martha González Castañeda 3. Mg. Martha Muñoz Gutierrez   Ciclo de Investigación potenciado  a través de la IA:  Retos, métodos y  herramientas.</t>
-  </si>
-  <si>
-    <t>Hackear el futuro de la Educación -  Ascofade
-Cecilia DImaté, Decana Facultad de Educacién Universidad Externado.  Diego Escallón, Subsecretario de calidad y pertinencia SED y Oscar Yesid Aparicio, Presidente Academia Hispanoamericana de docotores.
-Modera: Juanita Reina Zambrano</t>
-  </si>
-  <si>
-    <t>Conversatorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUIDALAB 
- William Romero - Pedro Nel Urrea
- Julio Pinzon y colegio Kimmy pernia </t>
-  </si>
-  <si>
-    <t>Palabras de Clausura
-Presentación musical CEMID</t>
-  </si>
-  <si>
-    <t>CENTRO UNIVERSITARIO</t>
-  </si>
-  <si>
-    <t>Conversatorio: Corporalidad y Aprendizaje Experiencial
-   Miguel Diaz (Perú) Alicia López (México)
-Eliana Monroy, Gonzalo Amaya, German Preciado,  (Colombia) 
- Modera: Pedro Nel Urrea Roa</t>
-  </si>
-  <si>
-    <t>Voces del barrio
-Daniel Núñez</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Caracterización de la fuerza en miembros inferiores en futbolistas prejuveniles de la Escuela Nueva Era de Sogamoso como apoyo a la educación física escolar.
-Nataly Alejandra Velandia Naranjo</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Implementación de la Plataforma de Educación física (PEF)
-Pablo Paúl Almeyda Torres, Susana Elizabeth Saravia Tasayco, Jimmy Alexandre Vergara Blas. Perú</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Educación Física, deporte y enseñanza: un análisis de la política curricular de Educación Física en Argentina
-Emiliozzi M. Valeria, Tocco Cecilia, Goldsworthy Jeremías Jesús</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
- Enfoque de género y el lenguaje no sexista en la Educación Física primaria en el marco de la Nueva Escuela Mexicana
-Alicia López     (México)   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
-Evaluar el proceso y no solo el producto: el portafolio digital en la formación del profesorado de Educación Física 
-Josep Campos-Rius </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
- El Aprendizaje Servicio y Formación Docente en Educación Física
-Miguel Aquilino Diaz Barboza (Perú) </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Gerencia curricular dialógica pentadimensional y formación de competencias investigativas en educación física universitaria: revisión integrativa.                                          
-Jorge Daniel Miranda Guzmán(Colombia)</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA 
-Diagnóstico de competencias genéricas en estudiantes universitarios como base para una estrategia con LEGO Serious Play                         
-Melissa Andrea Laiton Garnica(Colombia)</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-De la teoría a la praxis profesional: legislación, TIC e inclusión como ejes de transformación en la Educación Física escolar
-Yeison José Becerra Ariza (Colombia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relacionamiento de redes   docentes CONGRESO IDRM -REDDI EDUFISICA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA  
-Gerente Gonzalo Amaya 8:00 a 8:30am
-Estrategia Cundinamarca deporte incluyente
-Danny Quiñones
- </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA 
-RUTA STEM EN EDUCACIÓN FÍSICA  
-Pedro Nel Urrea Roa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
- Presentación Libro Evaluación y Capacidades Físicas Básicas: Una visión desde la interdisciplinariedad
-Eliana Sofía Monroy Muñoz(Colombia) </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Actividad física y regulación emocional en estudiantes universitarios 
-Deiby Alexander Lara Garzón &amp; Nayelly Tatiana Barragán Cañón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
-Desarrollo de Habilidades Blandas en Educación Básica y Media
-Luis Uriel Méndez Solano - IED Alfonso Reyes Echandía. 
- </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Cuerpos que piensan, mentes que juegan: Estrategias sociomotrices para la formación de sujetos críticos en el siglo XXI.
-John Edwin Valencia Moreno y Oscar Javier Quintero  - Secretaria de Educación Bogotá</t>
-  </si>
-  <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
 Neffar Abdul Arboleda Ortega, Joseph David Fiquitiva Carrillo,Jeisson Miguel Urrego Gonzales  UPN EstudiantesTitulo : Estrategias de motivación extrínseca y retroalimentación en el aprendizaje del drive en jóvenes tenistas: estudio cualitativo longitudinal </t>
   </si>
@@ -818,6 +537,18 @@
     <t>CONGRESO IDRM -REDDI EDUFISICA
 Educación física como alternativa para mejorar la calidad de vida de los jóvenes de malambo Atlántico
 José Francisco Mora Núñez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Viaje de Nogai: Guardianes de la Diversidad
+Living Lab UNIMINUTO  360
+Andrés Rico, Maryuri Agudelo y Zaily García </t>
+  </si>
+  <si>
+    <t>Experiencia</t>
+  </si>
+  <si>
+    <t>Didáctica del Contagio
+Andrés Rojas</t>
   </si>
   <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA 
@@ -861,96 +592,164 @@
 Tutor Juan Pablo Reyes</t>
   </si>
   <si>
+    <t>El desarrollo humano desde el acondicionamiento físico y el bienestar
+Invitado: Diego Fernando Villamizar Gómez
+Moderadora: Dalis Nury Molina Bustamante</t>
+  </si>
+  <si>
+    <t>Del prompt a la experiencia de aprendizaje: inteligencia artificial y diseño instruccional con sentido pedagógico 
+Karla Beatriz Gómez Santana
+Kenia Viridiana Ocampo Vera, 
+Universidad de Guadalajara
+Enlace: https://teams.microsoft.com/meet/277921384618913?p=RKSqlSnDTLi83MwWvY</t>
+  </si>
+  <si>
+    <t>Estrategia tejer calidad 
+Paul Brayan Cubillos Cabrera
+José Luis Gaitán Mendoza 
+SED - CEMID</t>
+  </si>
+  <si>
+    <t>Proyecto ruta emprender, Territorializar la escuela escolarizar el territorio
+Diana Guadalupe Garnica Jiménez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estrategias del siglo XXI para competir ante la desigualdad educativa entre zonas rurales y urbanas.
+Samuel Andrés Camargo González, 
+Samuel David Siado Aguilar, 
+María Paula Amaya Betancourt, 
+Andrés Beltrán Moreno, 
+Samuel López Jiménez, </t>
+  </si>
+  <si>
+    <t>Semillero Café sentipensante 
+Juan Esteban Carreño González
+Isaac David Fuentes Durán 
+Linda Saray Martinez Ortiz
+Melany Sareth Rueda Lea</t>
+  </si>
+  <si>
+    <t>Taller  "Inventario de pérdidas"
+Juliana Jaramillo Pabón</t>
+  </si>
+  <si>
+    <t>"Recital Poético por los caminos de Colombia
+Conferencia performática
+Cesar Julio Martinez Gil y Hector Cadena
+Encargado: red pedagogías emergentes y creativas"</t>
+  </si>
+  <si>
+    <t>Conversatorio Pensamiento de la Educación Física
+Julio Pinzón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditorio Principal </t>
+  </si>
+  <si>
+    <t>San Camilo</t>
+  </si>
+  <si>
+    <t>Prácticas reflexivas
+Óscar Andrés Mosquera</t>
+  </si>
+  <si>
+    <t>Voces del barrio
+Daniel Núñez</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Performance British Culture and Literature: Shakespeare in Love</t>
+  </si>
+  <si>
+    <t>Conferencia Performática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xeropan - Effective and fun language learning for the dedicated. 
+Ákos Huszár- Budapest, Hungary  </t>
+  </si>
+  <si>
+    <t>Unplugged pedagógico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pais Invitado: Mexico Singit
+Innovacion Educativa para el aprendizaje
+Guillermo Nuchowich </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pearson education: international English exams </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oiga Profe Venga le Cuento....La Ruta del Reto 
+Claudia Avila-Edgar Zambrano </t>
+  </si>
+  <si>
+    <t>Presentación libro "Semillero en Lliteratura Infantil" Licenciatura en humanidades y lengua castellana
+ Jonathan Caicedo Grión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La memoria biocultural en la resignificación del cuidado de la vida y la sostenibilidad de la biodiversidad del Municipio de El Rosal en Cundinamarca
+Laidy Valentina Prieto - Mónica Paola Díaz Oliveros </t>
+  </si>
+  <si>
+    <t>Lanzamientos editoriales 
+Licenciatura en Humanidades y lengua Castellana</t>
+  </si>
+  <si>
+    <t>Construcción de la identidad en la primera infancia a través de prácticas pedagógicas  basadas en el juego, la participación y la diversidad en el aula
+Briyeth Michelle Mogollón Ascanio y Karen Daniela Álvarez Carranza 
+Semillero Educación Infantil</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
 Pachon:  Resolución de conflictos por medio del juego    
 Juan Esteban Caceres García 
 Daniel Felipe Castiblanco  </t>
   </si>
   <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA 
-Actividad física adaptada: Educación para la salud y prescripción del ejercicio físico. 
- Luciana Brito - Argentina</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Diagnóstico morfofuncional del perfil de fuerza-velocidad horizontal en el contexto del deporte escolar regional
-Yohandis Abad Camejo, Francisco Freyre Vazquez, Abel Emilio Campaña Garzon - Cuba</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Juegos Electrónicos
-Alexander Ospina Bolaños - Presidente PAMESCO - Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
-¿Qué puede llegar a ser una persona? Capacidades humanas como horizonte para la Educación Física 
-Yammir López Brito (España), Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
-  </si>
-  <si>
-    <t>PEMA - Proyecto estación meteorológica 
-Nelson Eduardo Bejarano Morales
-Edwin Javier Rozo Carrasquilla 
-María Erika Castro Díaz
-Gloria Yomaira Tovar 
-Jazmín Parra Umba</t>
-  </si>
-  <si>
-    <t>Semillero de investigación Phobos, proyecto Belt Vision
-CEMID - Edwin Javier Rozo Carrasquilla 
- Colorado Torres David Santiago
- Cotrino Rojas Manuel Alejandro
- Mei Mendoza Dayana Sofía
- Pinilla Martínez Fabian Esteban
- Rodriguez Artiza Nicolás</t>
-  </si>
-  <si>
-    <t>Impacto de la IA en la escuela – Docentes y Estudiantes
-Paul Cubillos + 1 Estudinate
-CEMID</t>
-  </si>
-  <si>
-    <t>Acto Inaugural
-Oración
-Grupo de Danza Foloklórica Maguaré</t>
-  </si>
-  <si>
-    <t>Ecoeducación Sonora de la Licenciatura en Ciencias Naturales y Educación Ambiental
-Carlos Pacheco</t>
-  </si>
-  <si>
-    <t>Auditorio C204</t>
-  </si>
-  <si>
-    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
-Andrés Camilo Pérez Rodríguez, Cristian Camilo Ladino Marín</t>
-  </si>
-  <si>
-    <t>Iniciativas de IA para la protección del Medio Ambiente 
-María José Villa Moreno, Danna Valentina Rincon Loaiza</t>
-  </si>
-  <si>
-    <t>El desarrollo humano desde el acondicionamiento físico y el bienestar
-Invitado: Diego Fernando Villamizar Gómez
-Moderadora: Dalis Nury Molina Bustamante</t>
-  </si>
-  <si>
     <t>Sobre convivencia escolar y la prevención del acoso escolar
 José Argenis Mendoza Suárez
 CEMID</t>
   </si>
   <si>
-    <t>AlgaeX Lab: Huerta Escolar Inteligente.
-1. Lauren Fiallo Mendoza
-2. Sara Valentina Velez Mena
-3. María José Zambrano García
-4. Juliana Ramírez Angulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App de las emociones
-1. - Samuel Alejandro García Cuervo 
-2. Nikol Mariana Buitrago Jaramillo 
-3. Laura Sofia Tobar García 
-4. Mariana Quiroga Sánchez </t>
+    <t>Narrativas de infancias para el reconocimiento intercultural
+Edgar Zambrano, Diana Reyes, Ángel Téllez y David Garzón)</t>
+  </si>
+  <si>
+    <t>Educomunicación, pensamiento crítico y lenguaje desde las experiencias audiovisuales en la CEMID
+Valerie Sophia Prado Velásquez -Evolet Blue Pabón Gómez</t>
+  </si>
+  <si>
+    <t>PensArte
+Javier Maury (CoordAcadémico) - Katherine Rojas (DGC)
+Rodríguez Ruíz Isabella
+Jiménez Castillo Sara Michell
+Fonseca Chávez Ana Sofía
+Rodríguez Perilla Ana María</t>
+  </si>
+  <si>
+    <t>Investigación Cualitativa 
+Prof. Miguel Valdivia Pinto
+Universidad César Vallejo. Perú. (virtual)</t>
+  </si>
+  <si>
+    <t>Ecología de la retención estudiantil en la Educación Superior. 
+Profesora Asociada, Pilar Mendoza
+Universidad de Missouri y Directora CIIDE</t>
+  </si>
+  <si>
+    <t>Modelo de implementación STEM - MD
+Diana Marcela Valencia
+CEMID</t>
+  </si>
+  <si>
+    <t>Innovando desde la primera capa hasta el núcleo
+Nelson Orellano Llinás
+CEMID</t>
+  </si>
+  <si>
+    <t>9:!5</t>
   </si>
   <si>
     <t xml:space="preserve">Arquitectura autosostenible
@@ -961,7 +760,61 @@
 </t>
   </si>
   <si>
-    <t>9:!5</t>
+    <t>Poster Expandido</t>
+  </si>
+  <si>
+    <t>AlgaeX Lab: Huerta Escolar Inteligente.
+1. Lauren Fiallo Mendoza
+2. Sara Valentina Velez Mena
+3. María José Zambrano García
+4. Juliana Ramírez Angulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App de las emociones
+1. - Samuel Alejandro García Cuervo 
+2. Nikol Mariana Buitrago Jaramillo 
+3. Laura Sofia Tobar García 
+4. Mariana Quiroga Sánchez </t>
+  </si>
+  <si>
+    <t>Taller Vendaje Neuro Muscular y Kinesiotype
+Brayan García</t>
+  </si>
+  <si>
+    <t>CEMID - El Cuerpo que nos Une
+William Martínez Lievano
+Eric Guerra Charris</t>
+  </si>
+  <si>
+    <t>Desafiar Para Pensar: Experiencias Formativas para Desarrollar el Pensamiento Computacional
+Daniela Paola Urrea Diaz ,Liced Katerin Gómez Vega, Sandra Milena Bermúdez Bermúdez ,Miguel Alexander Vergara Mendoza y Nelson Enrique Orellano Llínas</t>
+  </si>
+  <si>
+    <t>Conversatorio Escenario Pedagógico Pensamiento de la Educación Física
+Anderson David Garzón Sichaca</t>
+  </si>
+  <si>
+    <t>Salòn C508</t>
+  </si>
+  <si>
+    <t>Técnicas de Rehabilitación y Recuperación Muscular
+Stiff García</t>
+  </si>
+  <si>
+    <t>Encuentro de Estudiantes
+IDRM-REDDI
+ Universidad Autonoma del Estado de Mexico, Universidad popular  del cesar de Colombia,  Universidad Atlantico y UniminutO</t>
+  </si>
+  <si>
+    <t>Conversatorio Docentes Educación Física-SENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EcoFinanzas
+Natalia Martínez - Johana Rodríguez </t>
+  </si>
+  <si>
+    <t>Taller de Graffiti
+Daniel Núñez, UNIARTES</t>
   </si>
   <si>
     <t>Arqueología de la confianza: recuperar el pasado para innovar en educación
@@ -971,13 +824,166 @@
     <t>¿Cómo se construyen las nociones de violencia en la infancia? Una experiencia de investigación en educación
 Invitado: John Jairo García Díaz
 Moderadora: Nadia Johanna Hernández Ordoñez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentación investigación LILEX Madrid
+Ana María Rocha Tamayo, Marisela Niño Monsalve, Norma Clemencia Rodríguez Arroyave, Claudia Alejandra Pineda Silva.
+Link de conexión: https://teams.microsoft.com/meet/241575852914896?p=8CM4487YPTL7uBv9Q5   </t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGISTRO </t>
+  </si>
+  <si>
+    <t>Zipaquirá</t>
+  </si>
+  <si>
+    <t>Charla con invitado paralimpico</t>
+  </si>
+  <si>
+    <t>Muévete sin Barreras: Unplugged Pedagógico por la Inclusión</t>
+  </si>
+  <si>
+    <t>Mural de la experiencia</t>
+  </si>
+  <si>
+    <t>Teaching English in Colombia: Paradigms, People &amp; Practice
+Alejandro Tabares
+CU- Girardot</t>
+  </si>
+  <si>
+    <t>Girardot</t>
+  </si>
+  <si>
+    <t>Diálogos científicos
+Virtual
+Carlos Pacheco</t>
+  </si>
+  <si>
+    <t>Cuidado Integral de la Persona Mayor: Experiencias en el Contexto Australiano
+Lina María Sierra (Australia)</t>
+  </si>
+  <si>
+    <t>Cuidado Integral de las Personas con Discapacidad: Experiencias en el Contexto Australiano
+Virtual sincrónico
+Yara De Jesus Correia E Silva (Australia)</t>
+  </si>
+  <si>
+    <t>MINDEPORTES - Juegos Ancestrales y Tradicionales en los Territorios de Colombia
+Cristian Castellanos 
+(Presencial- virtual )</t>
+  </si>
+  <si>
+    <t>Más allá de los subtítulos: cómo el cine nos ayuda a aprender lenguas y cruzar fronteras 
+Andrea Carolina Rodríguez Salazar 
+LLEI Madrid</t>
+  </si>
+  <si>
+    <t>La literatura una ventana al mundo y una herramienta para la inclusión global  
+Laura Viviana Sechagua Sechagua 
+LLEI Madrid</t>
+  </si>
+  <si>
+    <t>El desafío de enseñar tecnología aplicada al arte en la era de la inteligencia artificial
+Emiliano Causa, Universidad Nacional de La Plata y Universidad Nacional del Arte
+Argentina</t>
+  </si>
+  <si>
+    <t>Sabio Mutis Inmersion  proposal workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aventura gamificada en el living lab
+Master Daniel Diaz
+Licenciatura en Lenguas Extranjeras Bogota Presencial
+Red de multilinguismo y pensamiento glocal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Viaje de Nogai: Guardianes de la Diversidad
+Living Lab UNIMINUTO  360, Andrés Rico, Maryuri Agudelo y Zaily García </t>
+  </si>
+  <si>
+    <t>Conversatorio Pensamiento de la Educación Física
+Omar Cantor &amp; Jorge Rodríguez</t>
+  </si>
+  <si>
+    <t>CRAII 3 Piso</t>
+  </si>
+  <si>
+    <t>Perdomo</t>
+  </si>
+  <si>
+    <t>Proyecto de Investigación Creación
+Las Formas del Vacío - Artes  Expandidas: Circo, Danza, Audiovisual, Música, Tecnología.
+Diego Felipe Gaitán, Alejandro Andrade</t>
+  </si>
+  <si>
+    <t>Centro Nacional de las Artes - Delia Zapata</t>
+  </si>
+  <si>
+    <t>Cl. 11 #5 - 60, Bogotá</t>
+  </si>
+  <si>
+    <t>Inclusive meeting for the design of Educational materials
+Karina Garcia
+LLEID</t>
+  </si>
+  <si>
+    <t>Cabina de sonido y
+plazoleta primer piso (edificio A)</t>
+  </si>
+  <si>
+    <t>Unplugged Pedagógico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujeres en la Cima 
+Egnan Yesid Alvarez Cruz
+Dalis Nury Molina Bustamante
+</t>
+  </si>
+  <si>
+    <t>Por Confirmar</t>
+  </si>
+  <si>
+    <t>Two languages, one voice: Sign language and English
+PhD Jhon Farfan</t>
+  </si>
+  <si>
+    <t>Aprendiendo a través del lenguaje visual vernaculo 
+Christian Briceño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movimiento que incluye, infancias que transforman 
+CU Madrid- instalaciones Zoraida Cadavid de Sierra 
+Carlos Fuentes Rios, José David Peralta, Claudia Alejandra Pineda </t>
+  </si>
+  <si>
+    <t>"Movimiento que incluye, infancias que transforman 
+CU Madrid- instalaciones Zoraida Cadavid de Sierra 
+Carlos Fuentes Rios, José David Peralta, Claudia Alejandra Pineda</t>
+  </si>
+  <si>
+    <t>Taller Arte, inclusión y sensibilidad</t>
+  </si>
+  <si>
+    <t>Pistacho Talk - Ideas que transforman (1. Dra. Yohana González Bohórquez) 2. Dra. Martha González Castañeda 3. Mg. Martha Muñoz Gutierrez   Ciclo de Investigación potenciado  a través de la IA:  Retos, métodos y  herramientas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flipped Talk - Construcción colaborativa </t>
+  </si>
+  <si>
+    <t>Fire Pitch -  Innovación en acción: 7 Cuatrimestre (3 grupos) 8 Cuatrimestre (2 grupos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Pitch -  Innovación en acción: 9 Cuatrimestre (2 grupos)  - 10 Cuatrimestre  (2 grupos) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1020,7 +1026,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1043,11 +1049,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1108,6 +1125,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1443,44 +1463,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5702EEFC-39B3-4645-A79D-C3F97D1BC546}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="5" customWidth="1"/>
-    <col min="2" max="3" width="13.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="63.33203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="13.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="63.375" customWidth="1"/>
+    <col min="5" max="5" width="30.875" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="66.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17.100000000000001">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="51">
       <c r="A2" s="5">
         <v>46314</v>
       </c>
@@ -1491,22 +1515,22 @@
         <v>0.375</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="33.950000000000003">
       <c r="A3" s="5">
         <v>46314</v>
       </c>
@@ -1517,22 +1541,22 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="84.95">
       <c r="A4" s="5">
         <v>46314</v>
       </c>
@@ -1543,22 +1567,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="84.95">
       <c r="A5" s="5">
         <v>46314</v>
       </c>
@@ -1569,22 +1593,22 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="5">
         <v>46314</v>
       </c>
@@ -1595,16 +1619,16 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="33.950000000000003">
       <c r="A7" s="5">
         <v>46314</v>
       </c>
@@ -1615,22 +1639,22 @@
         <v>0.46875</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="33.950000000000003">
       <c r="A8" s="5">
         <v>46314</v>
       </c>
@@ -1641,22 +1665,22 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="84.95">
       <c r="A9" s="5">
         <v>46314</v>
       </c>
@@ -1667,22 +1691,22 @@
         <v>0.52777777777777779</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="33.950000000000003">
       <c r="A10" s="5">
         <v>46314</v>
       </c>
@@ -1693,23 +1717,26 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="D13" s="1"/>
+    </row>
+    <row r="29" spans="9:9">
+      <c r="I29" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1720,43 +1747,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0435A0A-E8EE-B24A-B2EA-F66A17D967D3}">
   <dimension ref="A1:I48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="12" customWidth="1"/>
-    <col min="2" max="3" width="13.6640625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="63.33203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="12" customWidth="1"/>
+    <col min="2" max="3" width="13.625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="63.375" customWidth="1"/>
+    <col min="5" max="5" width="30.875" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="75.375" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17.100000000000001">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="84.95">
       <c r="A2" s="12">
         <v>46315</v>
       </c>
@@ -1767,22 +1798,22 @@
         <v>0.34375</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="68.099999999999994">
       <c r="A3" s="12">
         <v>46315</v>
       </c>
@@ -1793,22 +1824,22 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="84.95">
       <c r="A4" s="12">
         <v>46315</v>
       </c>
@@ -1819,23 +1850,23 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="17.100000000000001">
       <c r="A5" s="12">
         <v>46315</v>
       </c>
@@ -1846,10 +1877,10 @@
         <v>0.4375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17.100000000000001">
       <c r="A6" s="12">
         <v>46315</v>
       </c>
@@ -1860,22 +1891,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.100000000000001">
       <c r="A7" s="12">
         <v>46315</v>
       </c>
@@ -1886,10 +1917,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="84.95">
       <c r="A8" s="12">
         <v>46315</v>
       </c>
@@ -1900,22 +1931,22 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="68.099999999999994">
       <c r="A9" s="12">
         <v>46315</v>
       </c>
@@ -1926,22 +1957,22 @@
         <v>0.625</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="84.95">
       <c r="A10" s="12">
         <v>46315</v>
       </c>
@@ -1952,22 +1983,22 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="84.95">
       <c r="A11" s="12">
         <v>46315</v>
       </c>
@@ -1978,22 +2009,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="68.099999999999994">
       <c r="A12" s="12">
         <v>46315</v>
       </c>
@@ -2004,22 +2035,22 @@
         <v>0.6875</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="68.099999999999994">
       <c r="A13" s="12">
         <v>46315</v>
       </c>
@@ -2030,22 +2061,22 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="68.099999999999994">
       <c r="A14" s="12">
         <v>46315</v>
       </c>
@@ -2056,19 +2087,19 @@
         <v>0.8125</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="33.950000000000003">
       <c r="A15" s="12">
         <v>46315</v>
       </c>
@@ -2079,22 +2110,22 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="51">
       <c r="A16" s="12">
         <v>46315</v>
       </c>
@@ -2105,22 +2136,22 @@
         <v>0.375</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="51">
       <c r="A17" s="12">
         <v>46315</v>
       </c>
@@ -2131,22 +2162,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="84.95">
       <c r="A18" s="12">
         <v>46315</v>
       </c>
@@ -2157,22 +2188,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="84.95">
       <c r="A19" s="12">
         <v>46315</v>
       </c>
@@ -2183,22 +2214,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="33.950000000000003">
       <c r="A20" s="12">
         <v>46315</v>
       </c>
@@ -2209,22 +2240,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="68.099999999999994">
       <c r="A21" s="12">
         <v>46315</v>
       </c>
@@ -2235,22 +2266,22 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="68.099999999999994">
       <c r="A22" s="12">
         <v>46315</v>
       </c>
@@ -2261,22 +2292,22 @@
         <v>0.625</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>166</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="51">
       <c r="A23" s="12">
         <v>46315</v>
       </c>
@@ -2287,22 +2318,22 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="72.95" customHeight="1">
       <c r="A24" s="12">
         <v>46315</v>
       </c>
@@ -2313,22 +2344,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="68.099999999999994">
       <c r="A25" s="12">
         <v>46315</v>
       </c>
@@ -2339,22 +2370,22 @@
         <v>0.6875</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>169</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="68.099999999999994">
       <c r="A26" s="12">
         <v>46315</v>
       </c>
@@ -2365,22 +2396,22 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>170</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="102">
       <c r="A27" s="12">
         <v>46315</v>
       </c>
@@ -2391,22 +2422,22 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>195</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="H27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="119" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="119.1">
       <c r="A28" s="12">
         <v>46315</v>
       </c>
@@ -2417,22 +2448,22 @@
         <v>0.375</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F28" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="35" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="35.1">
       <c r="A29" s="12">
         <v>46315</v>
       </c>
@@ -2443,23 +2474,23 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H29" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="I29" s="14"/>
     </row>
-    <row r="30" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="51">
       <c r="A30" s="12">
         <v>46315</v>
       </c>
@@ -2470,22 +2501,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="51">
       <c r="A31" s="12">
         <v>46315</v>
       </c>
@@ -2496,22 +2527,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="51">
       <c r="A32" s="12">
         <v>46315</v>
       </c>
@@ -2522,22 +2553,22 @@
         <v>0.375</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="51">
       <c r="A33" s="12">
         <v>46315</v>
       </c>
@@ -2548,22 +2579,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F33" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="51">
       <c r="A34" s="12">
         <v>46315</v>
       </c>
@@ -2574,22 +2605,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="33.950000000000003">
       <c r="A35" s="12">
         <v>46315</v>
       </c>
@@ -2600,22 +2631,22 @@
         <v>0.5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F35" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17.100000000000001">
       <c r="A36" s="12">
         <v>46315</v>
       </c>
@@ -2626,22 +2657,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F36" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="51">
       <c r="A37" s="12">
         <v>46315</v>
       </c>
@@ -2652,23 +2683,23 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F37" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H37" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="84.95">
       <c r="A38" s="12">
         <v>46315</v>
       </c>
@@ -2679,22 +2710,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F38" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="102">
       <c r="A39" s="12">
         <v>46315</v>
       </c>
@@ -2705,22 +2736,22 @@
         <v>0.5</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F39" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="33.950000000000003">
       <c r="A40" s="12">
         <v>46315</v>
       </c>
@@ -2731,27 +2762,27 @@
         <v>0.375</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
       <c r="D41" s="1"/>
     </row>
-    <row r="42" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="68.099999999999994">
       <c r="A42" s="12">
         <v>46315</v>
       </c>
@@ -2762,22 +2793,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H42" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="102">
       <c r="A43" s="12">
         <v>46315</v>
       </c>
@@ -2788,22 +2819,22 @@
         <v>0.5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="51">
       <c r="A44" s="12">
         <v>46315</v>
       </c>
@@ -2814,22 +2845,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="E44" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F44" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17.100000000000001">
       <c r="A45" s="12">
         <v>46315</v>
       </c>
@@ -2840,22 +2871,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E45" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F45" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17.100000000000001">
       <c r="A46" s="12">
         <v>46315</v>
       </c>
@@ -2866,22 +2897,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E46" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F46" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17.100000000000001">
       <c r="A47" s="12">
         <v>46315</v>
       </c>
@@ -2892,22 +2923,22 @@
         <v>0.5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E47" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F47" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H47" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="17.100000000000001">
       <c r="A48" s="12">
         <v>46315</v>
       </c>
@@ -2918,19 +2949,19 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E48" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F48" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H48" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2940,46 +2971,50 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED20595-F46C-C040-90EA-99C2F2DEBE61}">
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="15.625" style="12" customWidth="1"/>
     <col min="2" max="2" width="16.5" style="9" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="14.875" style="9" customWidth="1"/>
     <col min="4" max="4" width="51" customWidth="1"/>
     <col min="5" max="5" width="27.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.1640625" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.125" customWidth="1"/>
+    <col min="9" max="9" width="78.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17.100000000000001">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="119.1">
       <c r="A2" s="12">
         <v>46316</v>
       </c>
@@ -2990,22 +3025,22 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="84.95">
       <c r="A3" s="12">
         <v>46316</v>
       </c>
@@ -3016,22 +3051,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>201</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.100000000000001">
       <c r="A4" s="12">
         <v>46316</v>
       </c>
@@ -3042,10 +3077,10 @@
         <v>0.4375</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="68.099999999999994">
       <c r="A5" s="12">
         <v>46316</v>
       </c>
@@ -3056,22 +3091,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" t="s">
         <v>47</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="51">
       <c r="A6" s="12">
         <v>46316</v>
       </c>
@@ -3082,22 +3117,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.100000000000001">
       <c r="A7" s="12">
         <v>46316</v>
       </c>
@@ -3108,10 +3143,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="51">
       <c r="A8" s="12">
         <v>46316</v>
       </c>
@@ -3122,22 +3157,22 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>193</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="68.099999999999994">
       <c r="A9" s="12">
         <v>46316</v>
       </c>
@@ -3148,22 +3183,22 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="84.95">
       <c r="A10" s="12">
         <v>46316</v>
       </c>
@@ -3174,22 +3209,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="84.95">
       <c r="A11" s="12">
         <v>46316</v>
       </c>
@@ -3200,22 +3235,22 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="102">
       <c r="A12" s="12">
         <v>46316</v>
       </c>
@@ -3226,22 +3261,22 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="33.950000000000003">
       <c r="A13" s="12">
         <v>46316</v>
       </c>
@@ -3252,22 +3287,22 @@
         <v>0.375</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="61.5">
       <c r="A14" s="12">
         <v>46316</v>
       </c>
@@ -3278,22 +3313,22 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="72.75" customHeight="1">
       <c r="A15" s="12">
         <v>46316</v>
       </c>
@@ -3304,22 +3339,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="72.75" customHeight="1">
       <c r="A16" s="12">
         <v>46316</v>
       </c>
@@ -3330,22 +3365,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="51">
       <c r="A17" s="12">
         <v>46316</v>
       </c>
@@ -3356,22 +3391,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="84.95">
       <c r="A18" s="12">
         <v>46316</v>
       </c>
@@ -3382,22 +3417,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F18" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="102">
       <c r="A19" s="12">
         <v>46316</v>
       </c>
@@ -3408,22 +3443,22 @@
         <v>0.375</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="102">
       <c r="A20" s="12">
         <v>46316</v>
       </c>
@@ -3434,22 +3469,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="33.950000000000003">
       <c r="A21" s="12">
         <v>46316</v>
       </c>
@@ -3460,22 +3495,22 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="33.950000000000003">
       <c r="A22" s="12">
         <v>46316</v>
       </c>
@@ -3486,22 +3521,22 @@
         <v>0.46875</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="102">
       <c r="A23" s="12">
         <v>46316</v>
       </c>
@@ -3512,22 +3547,22 @@
         <v>0.5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="102">
       <c r="A24" s="12">
         <v>46316</v>
       </c>
@@ -3538,22 +3573,22 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="84.95">
       <c r="A25" s="12">
         <v>46316</v>
       </c>
@@ -3564,22 +3599,22 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="84.95">
       <c r="A26" s="12">
         <v>46316</v>
       </c>
@@ -3590,22 +3625,22 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="119.1">
       <c r="A27" s="12">
         <v>46316</v>
       </c>
@@ -3616,22 +3651,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H27" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="68.099999999999994">
       <c r="A28" s="12">
         <v>46316</v>
       </c>
@@ -3642,22 +3677,22 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H28" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="68.099999999999994">
       <c r="A29" s="12">
         <v>46316</v>
       </c>
@@ -3668,22 +3703,22 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="51">
       <c r="A30" s="12">
         <v>46316</v>
       </c>
@@ -3694,22 +3729,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="51">
       <c r="A31" s="12">
         <v>46316</v>
       </c>
@@ -3720,22 +3755,22 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="33.950000000000003">
       <c r="A32" s="12">
         <v>46316</v>
       </c>
@@ -3746,22 +3781,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="84.95">
       <c r="A33" s="12">
         <v>46316</v>
       </c>
@@ -3772,22 +3807,22 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F33" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="204" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="204">
       <c r="A34" s="12">
         <v>46316</v>
       </c>
@@ -3798,22 +3833,22 @@
         <v>0.625</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="136" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="135.94999999999999">
       <c r="A35" s="12">
         <v>46316</v>
       </c>
@@ -3824,22 +3859,22 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F35" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="102">
       <c r="A36" s="12">
         <v>46316</v>
       </c>
@@ -3850,22 +3885,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="102">
       <c r="A37" s="12">
         <v>46316</v>
       </c>
@@ -3876,22 +3911,22 @@
         <v>0.6875</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F37" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="136" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="135.94999999999999">
       <c r="A38" s="12">
         <v>46316</v>
       </c>
@@ -3902,22 +3937,22 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>189</v>
+        <v>121</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F38" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="68.099999999999994">
       <c r="A39" s="12">
         <v>46316</v>
       </c>
@@ -3928,19 +3963,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="E39" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="153">
       <c r="A40" s="12">
         <v>46316</v>
       </c>
@@ -3951,19 +3986,19 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="68.099999999999994">
       <c r="A41" s="12">
         <v>46316</v>
       </c>
@@ -3974,22 +4009,22 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="51">
       <c r="A42" s="12">
         <v>46316</v>
       </c>
@@ -4000,22 +4035,22 @@
         <v>0.375</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F42" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="119.1">
       <c r="A43" s="12">
         <v>46316</v>
       </c>
@@ -4026,22 +4061,22 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="E43" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F43" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="84.95">
       <c r="A44" s="12">
         <v>46316</v>
       </c>
@@ -4052,22 +4087,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="E44" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="33.950000000000003">
       <c r="A45" s="12">
         <v>46316</v>
       </c>
@@ -4078,22 +4113,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F45" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="68.099999999999994">
       <c r="A46" s="12">
         <v>46316</v>
       </c>
@@ -4104,22 +4139,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F46" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H46" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="33.950000000000003">
       <c r="A47" s="12">
         <v>46316</v>
       </c>
@@ -4130,22 +4165,22 @@
         <v>0.375</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="F47" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="33.950000000000003">
       <c r="A48" s="12">
         <v>46316</v>
       </c>
@@ -4156,22 +4191,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F48" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="33.950000000000003">
       <c r="A49" s="12">
         <v>46316</v>
       </c>
@@ -4182,24 +4217,24 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F49" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="E52" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E52" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -4209,46 +4244,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{610C11C2-B771-9D44-A689-56619F68B052}">
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="12"/>
+    <col min="1" max="1" width="10.875" style="12"/>
     <col min="2" max="2" width="13" style="9" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="68.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="68.875" customWidth="1"/>
     <col min="5" max="5" width="20.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="9" width="63.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17.100000000000001">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="33.950000000000003">
       <c r="A2" s="12">
         <v>46317</v>
       </c>
@@ -4259,22 +4298,22 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="33.950000000000003">
       <c r="A3" s="12">
         <v>46317</v>
       </c>
@@ -4285,22 +4324,22 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="51">
       <c r="A4" s="12">
         <v>46317</v>
       </c>
@@ -4311,22 +4350,22 @@
         <v>0.40625</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="33.950000000000003">
       <c r="A5" s="12">
         <v>46317</v>
       </c>
@@ -4337,22 +4376,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17.100000000000001">
       <c r="A6" s="12">
         <v>46317</v>
       </c>
@@ -4363,10 +4402,10 @@
         <v>0.4375</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="33.950000000000003">
       <c r="A7" s="12">
         <v>46317</v>
       </c>
@@ -4377,22 +4416,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="51">
       <c r="A8" s="12">
         <v>46317</v>
       </c>
@@ -4403,22 +4442,22 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="51">
       <c r="A9" s="12">
         <v>46317</v>
       </c>
@@ -4429,22 +4468,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.100000000000001">
       <c r="A10" s="12">
         <v>46317</v>
       </c>
@@ -4455,10 +4494,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="33.950000000000003">
       <c r="A11" s="12">
         <v>46317</v>
       </c>
@@ -4469,22 +4508,22 @@
         <v>0.625</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="68.099999999999994">
       <c r="A12" s="12">
         <v>46317</v>
       </c>
@@ -4495,22 +4534,22 @@
         <v>0.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="68.099999999999994">
       <c r="A13" s="12">
         <v>46317</v>
       </c>
@@ -4521,22 +4560,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="51">
       <c r="A14" s="12">
         <v>46317</v>
       </c>
@@ -4547,22 +4586,22 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="33.950000000000003">
       <c r="A15" s="12">
         <v>46317</v>
       </c>
@@ -4573,22 +4612,22 @@
         <v>0.375</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="51">
       <c r="A16" s="12">
         <v>46317</v>
       </c>
@@ -4599,22 +4638,22 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="102">
       <c r="A17" s="12">
         <v>46317</v>
       </c>
@@ -4625,22 +4664,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="51">
       <c r="A18" s="12">
         <v>46317</v>
       </c>
@@ -4651,22 +4690,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="51">
       <c r="A19" s="12">
         <v>46317</v>
       </c>
@@ -4677,22 +4716,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="51">
       <c r="A20" s="12">
         <v>46317</v>
       </c>
@@ -4703,22 +4742,22 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="51">
       <c r="A21" s="12">
         <v>46317</v>
       </c>
@@ -4729,22 +4768,22 @@
         <v>0.375</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="119.1">
       <c r="A22" s="12">
         <v>46317</v>
       </c>
@@ -4752,25 +4791,25 @@
         <v>0.375</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="84.95">
       <c r="A23" s="12">
         <v>46317</v>
       </c>
@@ -4781,22 +4820,22 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F23" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="84.95">
       <c r="A24" s="12">
         <v>46317</v>
       </c>
@@ -4807,22 +4846,22 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33.950000000000003">
       <c r="A25" s="12">
         <v>46317</v>
       </c>
@@ -4833,22 +4872,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="H25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="51">
       <c r="A26" s="12">
         <v>46317</v>
       </c>
@@ -4859,22 +4898,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="68.099999999999994">
       <c r="A27" s="12">
         <v>46317</v>
       </c>
@@ -4885,22 +4924,22 @@
         <v>0.375</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F27" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="33.950000000000003">
       <c r="A28" s="12">
         <v>46317</v>
       </c>
@@ -4911,22 +4950,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="F28" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="33.950000000000003">
       <c r="A29" s="12">
         <v>46317</v>
       </c>
@@ -4937,22 +4976,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F29" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="68.099999999999994">
       <c r="A30" s="12">
         <v>46317</v>
       </c>
@@ -4963,22 +5002,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="F30" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.100000000000001">
       <c r="A31" s="12">
         <v>46317</v>
       </c>
@@ -4989,22 +5028,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="F31" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="33.950000000000003">
       <c r="A32" s="12">
         <v>46317</v>
       </c>
@@ -5015,22 +5054,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="F32" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="33.950000000000003">
       <c r="A33" s="12">
         <v>46317</v>
       </c>
@@ -5041,22 +5080,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="33.950000000000003">
       <c r="A34" s="12">
         <v>46317</v>
       </c>
@@ -5067,22 +5106,22 @@
         <v>0.5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F34" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="68.099999999999994">
       <c r="A35" s="12">
         <v>46317</v>
       </c>
@@ -5093,19 +5132,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="84.95">
       <c r="A36" s="12">
         <v>46317</v>
       </c>
@@ -5116,22 +5155,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="17.100000000000001">
       <c r="A37" s="12">
         <v>46317</v>
       </c>
@@ -5142,16 +5181,16 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="17.100000000000001">
       <c r="A38" s="12">
         <v>46317</v>
       </c>
@@ -5162,22 +5201,22 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="33.950000000000003">
       <c r="A39" s="12">
         <v>46317</v>
       </c>
@@ -5188,22 +5227,22 @@
         <v>0.1875</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H39" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="17.100000000000001">
       <c r="A40" s="12">
         <v>46317</v>
       </c>
@@ -5214,19 +5253,19 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H40" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -5236,44 +5275,49 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED2B231-C2FE-4148-8243-856EEE7BB0A8}">
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="12"/>
-    <col min="2" max="3" width="10.83203125" style="9"/>
+    <col min="1" max="1" width="10.875" style="12"/>
+    <col min="2" max="3" width="10.875" style="9"/>
     <col min="4" max="4" width="54.5" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.625" customWidth="1"/>
     <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.875" customWidth="1"/>
+    <col min="9" max="9" width="40.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17.100000000000001">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="51">
       <c r="A2" s="12">
         <v>46318</v>
       </c>
@@ -5284,22 +5328,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="51">
       <c r="A3" s="12">
         <v>46318</v>
       </c>
@@ -5310,19 +5354,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="51">
       <c r="A4" s="12">
         <v>46318</v>
       </c>
@@ -5333,22 +5377,22 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="68.099999999999994">
       <c r="A5" s="12">
         <v>46318</v>
       </c>
@@ -5359,22 +5403,22 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="68.099999999999994">
       <c r="A6" s="12">
         <v>46318</v>
       </c>
@@ -5385,22 +5429,22 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>107</v>
+        <v>185</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="68.099999999999994">
       <c r="A7" s="12">
         <v>46318</v>
       </c>
@@ -5411,22 +5455,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="68.099999999999994">
       <c r="A8" s="12">
         <v>46318</v>
       </c>
@@ -5437,22 +5481,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="84.95">
       <c r="A9" s="12">
         <v>46318</v>
       </c>
@@ -5463,19 +5507,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.100000000000001">
       <c r="A10" s="12">
         <v>46318</v>
       </c>
@@ -5486,22 +5530,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="68.099999999999994">
       <c r="A11" s="12">
         <v>46318</v>
       </c>
@@ -5512,22 +5556,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="51">
       <c r="A12" s="12">
         <v>46318</v>
       </c>
@@ -5538,22 +5582,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="51">
       <c r="A13" s="12">
         <v>46318</v>
       </c>
@@ -5564,22 +5608,22 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="51">
       <c r="A14" s="12">
         <v>46318</v>
       </c>
@@ -5590,22 +5634,22 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="33.950000000000003">
       <c r="A15" s="12">
         <v>46318</v>
       </c>
@@ -5616,22 +5660,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="F15" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="68.099999999999994">
       <c r="A16" s="12">
         <v>46318</v>
       </c>
@@ -5642,22 +5686,22 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17.100000000000001">
       <c r="A17" s="12">
         <v>46318</v>
       </c>
@@ -5668,10 +5712,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17.100000000000001">
       <c r="A18" s="12">
         <v>46318</v>
       </c>
@@ -5682,7 +5726,7 @@
         <v>0.4375</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5692,45 +5736,49 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20AF3EDE-6580-ED48-9EFC-D8F9F19716A1}">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="12"/>
+    <col min="1" max="1" width="10.875" style="12"/>
     <col min="2" max="3" width="11.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.1640625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="9"/>
+    <col min="4" max="4" width="41.125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="25.875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="9"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="16.125" customWidth="1"/>
+    <col min="9" max="9" width="63.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17.100000000000001">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="68.099999999999994">
       <c r="A2" s="12">
         <v>46319</v>
       </c>
@@ -5741,22 +5789,22 @@
         <v>0.75</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="68.099999999999994">
       <c r="A3" s="12">
         <v>46319</v>
       </c>
@@ -5767,22 +5815,22 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="51">
       <c r="A4" s="12">
         <v>46319</v>
       </c>
@@ -5793,22 +5841,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>121</v>
+        <v>203</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17.100000000000001">
       <c r="A5" s="12">
         <v>46319</v>
       </c>
@@ -5819,12 +5867,12 @@
         <v>0.4375</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="51">
       <c r="A6" s="12">
         <v>46319</v>
       </c>
@@ -5835,22 +5883,22 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="102">
       <c r="A7" s="12">
         <v>46319</v>
       </c>
@@ -5861,22 +5909,22 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="102">
       <c r="A8" s="12">
         <v>46319</v>
       </c>
@@ -5887,22 +5935,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="102">
       <c r="A9" s="12">
         <v>46319</v>
       </c>
@@ -5913,22 +5961,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="102" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="102">
       <c r="A10" s="12">
         <v>46319</v>
       </c>
@@ -5939,22 +5987,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="33.950000000000003">
       <c r="A11" s="12">
         <v>46319</v>
       </c>
@@ -5965,22 +6013,22 @@
         <v>0.375</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="84.95">
       <c r="A12" s="12">
         <v>46319</v>
       </c>
@@ -5991,22 +6039,22 @@
         <v>0.40625</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.100000000000001">
       <c r="A13" s="12">
         <v>46319</v>
       </c>
@@ -6017,22 +6065,22 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>125</v>
+        <v>209</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="51">
       <c r="A14" s="12">
         <v>46319</v>
       </c>
@@ -6043,22 +6091,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="51">
       <c r="A15" s="12">
         <v>46319</v>
       </c>
@@ -6069,22 +6117,22 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="68.099999999999994">
       <c r="A16" s="12">
         <v>46319</v>
       </c>
@@ -6095,22 +6143,22 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17.100000000000001">
       <c r="A17" s="12">
         <v>46319</v>
       </c>
@@ -6121,7 +6169,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61CB33F7-557D-489E-A545-1079DBA8762B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94AC9587-E96E-48EA-B985-AA49519EEB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="2" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="3" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="212">
   <si>
     <t>DÍA</t>
   </si>
@@ -451,8 +451,8 @@
 John Edwin Valencia Moreno y Oscar Javier Quintero  - Secretaria de Educación Bogotá</t>
   </si>
   <si>
-    <t>Habitar el miedo y la incertidumbre en la práctica educativa 
-Laura Hurtado</t>
+    <t>"Voces del barrio
+Daniel Núñez"</t>
   </si>
   <si>
     <t>Auditorio C205</t>
@@ -653,8 +653,8 @@
 Óscar Andrés Mosquera</t>
   </si>
   <si>
-    <t>Voces del barrio
-Daniel Núñez</t>
+    <t>Habitar el miedo y la incertidumbre en la práctica educativa 
+Laura Hurtado</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -818,7 +818,7 @@
   </si>
   <si>
     <t>Arqueología de la confianza: recuperar el pasado para innovar en educación
-James Ricardo Zorro Monroy, Frendy González y Sandra Patricia Pachón Monsalve</t>
+James Ricardo Zorro Monrroy, Frendy González y Sandra Patricia Pachón Monsalve</t>
   </si>
   <si>
     <t>¿Cómo se construyen las nociones de violencia en la infancia? Una experiencia de investigación en educación
@@ -3276,7 +3276,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="33.950000000000003">
+    <row r="13" spans="1:9" ht="30.75">
       <c r="A13" s="12">
         <v>46316</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="33.950000000000003">
+    <row r="49" spans="1:8" ht="30.75">
       <c r="A49" s="12">
         <v>46316</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="33.950000000000003">
+    <row r="34" spans="1:8" ht="30.75">
       <c r="A34" s="12">
         <v>46317</v>
       </c>
@@ -5576,10 +5576,10 @@
         <v>46318</v>
       </c>
       <c r="B12" s="18">
-        <v>0.4375</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C12" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>191</v>
@@ -5602,10 +5602,10 @@
         <v>46318</v>
       </c>
       <c r="B13" s="18">
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="C13" s="18">
-        <v>0.64583333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>191</v>
@@ -5623,82 +5623,70 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="51">
+    <row r="14" spans="1:9" ht="33.950000000000003">
       <c r="A14" s="12">
         <v>46318</v>
       </c>
       <c r="B14" s="18">
-        <v>0.75</v>
+        <v>0.4375</v>
       </c>
       <c r="C14" s="18">
-        <v>0.83333333333333337</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="33.950000000000003">
+    <row r="15" spans="1:9" ht="68.099999999999994">
       <c r="A15" s="12">
         <v>46318</v>
       </c>
       <c r="B15" s="18">
-        <v>0.4375</v>
+        <v>0.8125</v>
       </c>
       <c r="C15" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E15" t="s">
-        <v>193</v>
-      </c>
-      <c r="F15" t="s">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="68.099999999999994">
+        <v>12</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17.100000000000001">
       <c r="A16" s="12">
         <v>46318</v>
       </c>
       <c r="B16" s="18">
-        <v>0.8125</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="C16" s="18">
-        <v>0.85416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.100000000000001">
@@ -5706,29 +5694,16 @@
         <v>46318</v>
       </c>
       <c r="B17" s="18">
-        <v>0.52083333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C17" s="18">
-        <v>0.58333333333333337</v>
+        <v>0.4375</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17.100000000000001">
-      <c r="A18" s="12">
-        <v>46318</v>
-      </c>
-      <c r="B18" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C18" s="18">
-        <v>0.4375</v>
-      </c>
-      <c r="D18" s="1" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="18" spans="1:4" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94AC9587-E96E-48EA-B985-AA49519EEB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6CCA7D1-27A9-484C-BF01-2EB05B7DAB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="3" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="5" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="234">
   <si>
     <t>DÍA</t>
   </si>
@@ -166,6 +166,9 @@
     <t>Híbrido</t>
   </si>
   <si>
+    <t>https://teams.microsoft.com/meet/238014813785739?p=QO1Vk1a0ta3XTUDEXx</t>
+  </si>
+  <si>
     <t>Coffee Break &amp; Networiking</t>
   </si>
   <si>
@@ -183,6 +186,9 @@
 Yammir López Brito (España), Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
   </si>
   <si>
+    <t>https://teams.microsoft.com/meet/236360195720129?p=CbI3UObtPLPgIgMogm</t>
+  </si>
+  <si>
     <t>CONGRESO IDRM -REDDI EDUFISICA 
 Actividad física adaptada: Educación para la salud y prescripción del ejercicio físico. 
  Luciana Brito - Argentina</t>
@@ -229,6 +235,9 @@
   </si>
   <si>
     <t>Auditorio B205</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/meet/2631746659935957?p=QMTrrbgFlJKmQq9koj</t>
   </si>
   <si>
     <t>Co-crear lo común: Wikimedia, laboratorios ciudadanos y apropiacion social del conocimiento.
@@ -312,6 +321,9 @@
 SINGIT TECH - Argentina</t>
   </si>
   <si>
+    <t>https://teams.microsoft.com/l/meetup-join/19%3ameeting_OGQ0YmRkNjUtYjk2NC00NGYyLWFmMDQtNWQzMmMzYzk5OTg0%40thread.v2/0?context=%7b%22Tid%22%3a%22b1ba85eb-a253-4467-9ee8-d4f8ed4df300%22%2c%22Oid%22%3a%2256e1af7f-4b42-4e80-8671-8a89b73c660c%22%7d</t>
+  </si>
+  <si>
     <t>Integración humana y social de las TIC en la educación: un análisis en instituciones rurales y urbanas
 Maira Alejandra Pulgarín Rodríguez</t>
   </si>
@@ -366,6 +378,13 @@
  Vásquez Casallas, Johan Samuel</t>
   </si>
   <si>
+    <t>Exigencia académica y desarrollo integral: una mirada a la experiencia de los estudiantes del Bachillerato Internacional 
+Andrés Camilo Hernández Hernández</t>
+  </si>
+  <si>
+    <t>Unplugged pedagógico</t>
+  </si>
+  <si>
     <t xml:space="preserve">Presentación Artes Escénicas 
 Fredy Torres, </t>
   </si>
@@ -384,7 +403,8 @@
     <t>Soacha</t>
   </si>
   <si>
-    <t>FISIOLAB, una estrategia didáctica interdisciplinar fundamentada en el enfoque STEAM
+    <t>FISIOLAB: Científicos del Cuerpo. Una estrategia didáctica interdisciplinar fundamentada en el enfoque STEM
+Nathalie Rodriguez Caucali
 Jhon Alexander Serna García
 Lili Vélez Cante
 Yuli Andriana Navarrete Vaca
@@ -430,6 +450,9 @@
 Alexander Ospina Bolaños - Presidente PAMESCO - Colombia</t>
   </si>
   <si>
+    <t>https://teams.microsoft.com/meet/268438955130536?p=kBLTrRHKhHpZeWejhh</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
  Presentación Libro Evaluación y Capacidades Físicas Básicas: Una visión desde la interdisciplinariedad
 Eliana Sofía Monroy Muñoz(Colombia) </t>
@@ -463,7 +486,7 @@
 UNAD</t>
   </si>
   <si>
-    <t>El sonido de lo sagrado: Interpretaciones iconográficas y acústicas de los objetos sonoros Tairona
+    <t>Decolonización de la escucha en la academia
 Luisa Fernanda Arias
 UNAD</t>
   </si>
@@ -483,14 +506,23 @@
 UCV - Lima Perú </t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/e28bcf5e-cb1c-482a-b355-0d6bc86621b1@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taller vivencial: "Leer con el cuerpo y la voz", una experiencia práctica orientada a docentes y agentes educativos sobre lectura en voz alta, narración corporal y mediación afectiva como estrategias de literacidad emergente en la primera infancia.
 Dra. Dora Tamariz  UCV - Lima  - Perú  </t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/1bfeda94-aae3-4289-8bdd-981be1c192b6@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
   </si>
   <si>
     <t>Uso de la Inteligencia Artificial en el Aprendizaje  de niños y niñas en los colegios (Alfabetización para la docencia escolar)
 Profesor asociado Sam Von Guillern
 Universidad de Missouri
 CIIDE</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/1fbb508b-25fc-4f5e-adec-c336215a025f@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t>Ciudadanía digital en los Colegios Minuto de Dios
@@ -597,6 +629,9 @@
 Moderadora: Dalis Nury Molina Bustamante</t>
   </si>
   <si>
+    <t>https://teams.microsoft.com/meet/272197321964862?p=3ZUvVjw3nhTuhT295I</t>
+  </si>
+  <si>
     <t>Del prompt a la experiencia de aprendizaje: inteligencia artificial y diseño instruccional con sentido pedagógico 
 Karla Beatriz Gómez Santana
 Kenia Viridiana Ocampo Vera, 
@@ -666,11 +701,14 @@
     <t>Conferencia Performática</t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/2068695d-2af6-4d74-93f3-31c3ce33fd14@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xeropan - Effective and fun language learning for the dedicated. 
 Ákos Huszár- Budapest, Hungary  </t>
   </si>
   <si>
-    <t>Unplugged pedagógico</t>
+    <t>https://events.teams.microsoft.com/event/09066365-2f89-4b9d-9e25-e8407d3d7d7a@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t xml:space="preserve">Pais Invitado: Mexico Singit
@@ -678,7 +716,13 @@
 Guillermo Nuchowich </t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/0c9dcb5c-f55b-409d-a4be-03da0e10b81f@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pearson education: international English exams </t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/ce04c0e9-1211-4d19-ad29-6a55543786ba@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t xml:space="preserve">Oiga Profe Venga le Cuento....La Ruta del Reto 
@@ -734,11 +778,17 @@
 Universidad César Vallejo. Perú. (virtual)</t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/22665374-cbde-4501-87a6-8973bf4dccbd@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t>Ecología de la retención estudiantil en la Educación Superior. 
 Profesora Asociada, Pilar Mendoza
 Universidad de Missouri y Directora CIIDE</t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/89538298-daed-473c-b6cb-b558dd6c6ceb@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
+  </si>
+  <si>
     <t>Modelo de implementación STEM - MD
 Diana Marcela Valencia
 CEMID</t>
@@ -747,9 +797,6 @@
     <t>Innovando desde la primera capa hasta el núcleo
 Nelson Orellano Llinás
 CEMID</t>
-  </si>
-  <si>
-    <t>9:!5</t>
   </si>
   <si>
     <t xml:space="preserve">Arquitectura autosostenible
@@ -834,6 +881,9 @@
     <t>Madrid</t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/0f23b575-a34b-460e-b018-e6742f4905b8@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t xml:space="preserve">REGISTRO </t>
   </si>
   <si>
@@ -857,6 +907,9 @@
     <t>Girardot</t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/e6b42d56-5a74-4486-b8b1-cb00a9d6fa8e@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t>Diálogos científicos
 Virtual
 Carlos Pacheco</t>
@@ -876,6 +929,9 @@
 (Presencial- virtual )</t>
   </si>
   <si>
+    <t>https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.youtube.com%2Flive%2Fesp7PURwXVw%3Fsi%3Dsj4hy4V6H6qsgsCH&amp;data=05%7C02%7Canderson.garzon.s%40uniminuto.edu%7C8c40ee5cc1b4465bf10a08df2a0d6ea2%7Cb1ba85eba25344679ee8d4f8ed4df300%7C1%7C0%7C639275909426166060%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=vLjWfGSRgHp4LJ6pY3I83XdSpAYEt0XuJi4BfC3%2FFvA%3D&amp;reserved=0</t>
+  </si>
+  <si>
     <t>Más allá de los subtítulos: cómo el cine nos ayuda a aprender lenguas y cruzar fronteras 
 Andrea Carolina Rodríguez Salazar 
 LLEI Madrid</t>
@@ -892,6 +948,9 @@
   </si>
   <si>
     <t>Sabio Mutis Inmersion  proposal workshop</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/9ee29b05-dd04-4282-871c-53fe9ce5082e@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t xml:space="preserve">Aventura gamificada en el living lab
@@ -937,17 +996,26 @@
     <t>Unplugged Pedagógico</t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/9dd92c1c-b09f-4bc3-95f5-97a572615a61@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mujeres en la Cima 
 Egnan Yesid Alvarez Cruz
 Dalis Nury Molina Bustamante
 </t>
   </si>
   <si>
-    <t>Por Confirmar</t>
+    <t>Aula Combinada Piso 2</t>
   </si>
   <si>
     <t>Two languages, one voice: Sign language and English
 PhD Jhon Farfan</t>
+  </si>
+  <si>
+    <t>Por Confirmar</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/16af2921-a318-40da-8795-6e3dd2992e61@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t>Aprendiendo a través del lenguaje visual vernaculo 
@@ -967,23 +1035,23 @@
     <t>Taller Arte, inclusión y sensibilidad</t>
   </si>
   <si>
-    <t>Pistacho Talk - Ideas que transforman (1. Dra. Yohana González Bohórquez) 2. Dra. Martha González Castañeda 3. Mg. Martha Muñoz Gutierrez   Ciclo de Investigación potenciado  a través de la IA:  Retos, métodos y  herramientas.</t>
+    <t>Ideas que transforman (1. Dra. Yohana González Bohórquez) 2. Dra. Martha González Castañeda 3. Mg. Martha Muñoz Gutierrez   Ciclo de Investigación potenciado  a través de la IA:  Retos, métodos y  herramientas.</t>
   </si>
   <si>
     <t xml:space="preserve">Flipped Talk - Construcción colaborativa </t>
   </si>
   <si>
-    <t>Fire Pitch -  Innovación en acción: 7 Cuatrimestre (3 grupos) 8 Cuatrimestre (2 grupos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Pitch -  Innovación en acción: 9 Cuatrimestre (2 grupos)  - 10 Cuatrimestre  (2 grupos) </t>
+    <t>Innovación en acción: 7 Cuatrimestre (3 grupos) 8 Cuatrimestre (2 grupos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovación en acción: 9 Cuatrimestre (2 grupos)  - 10 Cuatrimestre  (2 grupos) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1013,6 +1081,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1061,10 +1137,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1129,8 +1206,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1746,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0435A0A-E8EE-B24A-B2EA-F66A17D967D3}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="10.625" style="12" customWidth="1"/>
@@ -1839,7 +1924,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="84.95">
+    <row r="4" spans="1:9" ht="77.25">
       <c r="A4" s="12">
         <v>46315</v>
       </c>
@@ -1864,7 +1949,9 @@
       <c r="H4" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="25" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="17.100000000000001">
       <c r="A5" s="12">
@@ -1877,7 +1964,7 @@
         <v>0.4375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.100000000000001">
@@ -1891,7 +1978,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -1900,13 +1987,13 @@
         <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.100000000000001">
+    <row r="7" spans="1:9" ht="15.75">
       <c r="A7" s="12">
         <v>46315</v>
       </c>
@@ -1917,10 +2004,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="84.95">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="84.95" customHeight="1">
       <c r="A8" s="12">
         <v>46315</v>
       </c>
@@ -1931,7 +2018,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -1945,8 +2032,11 @@
       <c r="H8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="68.099999999999994">
+      <c r="I8" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A9" s="12">
         <v>46315</v>
       </c>
@@ -1957,7 +2047,7 @@
         <v>0.625</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -1971,8 +2061,9 @@
       <c r="H9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="84.95">
+      <c r="I9" s="26"/>
+    </row>
+    <row r="10" spans="1:9" ht="84.95" customHeight="1">
       <c r="A10" s="12">
         <v>46315</v>
       </c>
@@ -1983,7 +2074,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -1997,8 +2088,9 @@
       <c r="H10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="84.95">
+      <c r="I10" s="26"/>
+    </row>
+    <row r="11" spans="1:9" ht="84.95" customHeight="1">
       <c r="A11" s="12">
         <v>46315</v>
       </c>
@@ -2009,7 +2101,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
         <v>27</v>
@@ -2023,8 +2115,9 @@
       <c r="H11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="68.099999999999994">
+      <c r="I11" s="26"/>
+    </row>
+    <row r="12" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A12" s="12">
         <v>46315</v>
       </c>
@@ -2035,7 +2128,7 @@
         <v>0.6875</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -2049,8 +2142,9 @@
       <c r="H12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="68.099999999999994">
+      <c r="I12" s="26"/>
+    </row>
+    <row r="13" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A13" s="12">
         <v>46315</v>
       </c>
@@ -2061,7 +2155,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -2075,8 +2169,9 @@
       <c r="H13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="68.099999999999994">
+      <c r="I13" s="26"/>
+    </row>
+    <row r="14" spans="1:9" ht="46.5">
       <c r="A14" s="12">
         <v>46315</v>
       </c>
@@ -2087,10 +2182,10 @@
         <v>0.8125</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -2110,22 +2205,22 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="51">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="46.5">
       <c r="A16" s="12">
         <v>46315</v>
       </c>
@@ -2136,10 +2231,10 @@
         <v>0.375</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -2149,6 +2244,9 @@
       </c>
       <c r="H16" t="s">
         <v>31</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="51">
@@ -2162,10 +2260,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -2188,10 +2286,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
         <v>49</v>
-      </c>
-      <c r="E18" t="s">
-        <v>47</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -2214,10 +2312,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -2240,10 +2338,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -2266,10 +2364,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
@@ -2292,10 +2390,10 @@
         <v>0.625</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
@@ -2318,10 +2416,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -2344,10 +2442,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
@@ -2370,10 +2468,10 @@
         <v>0.6875</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
@@ -2396,10 +2494,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -2422,16 +2520,16 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -2448,10 +2546,10 @@
         <v>0.375</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -2474,10 +2572,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" t="s">
         <v>62</v>
-      </c>
-      <c r="E29" t="s">
-        <v>59</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -2490,7 +2588,7 @@
       </c>
       <c r="I29" s="14"/>
     </row>
-    <row r="30" spans="1:9" ht="51">
+    <row r="30" spans="1:9" ht="77.25">
       <c r="A30" s="12">
         <v>46315</v>
       </c>
@@ -2501,10 +2599,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
@@ -2514,6 +2612,9 @@
       </c>
       <c r="H30" t="s">
         <v>13</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="51">
@@ -2527,10 +2628,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
@@ -2553,10 +2654,10 @@
         <v>0.375</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -2579,10 +2680,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -2605,10 +2706,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -2631,10 +2732,10 @@
         <v>0.5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -2657,10 +2758,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -2680,19 +2781,19 @@
         <v>0.4375</v>
       </c>
       <c r="C37" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E37" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -2704,22 +2805,22 @@
         <v>46315</v>
       </c>
       <c r="B38" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="C38" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H38" t="s">
         <v>31</v>
@@ -2730,16 +2831,16 @@
         <v>46315</v>
       </c>
       <c r="B39" s="18">
-        <v>0.47916666666666669</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="C39" s="18">
-        <v>0.5</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" t="s">
         <v>75</v>
-      </c>
-      <c r="E39" t="s">
-        <v>71</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -2751,81 +2852,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="33.950000000000003">
+    <row r="40" spans="1:9" ht="46.5">
       <c r="A40" s="12">
         <v>46315</v>
       </c>
       <c r="B40" s="18">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="C40" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="33.950000000000003">
+      <c r="A41" s="12">
+        <v>46315</v>
+      </c>
+      <c r="B41" s="18">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C41" s="18">
         <v>0.375</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="D41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" ht="68.099999999999994">
-      <c r="A42" s="12">
-        <v>46315</v>
-      </c>
-      <c r="B42" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C42" s="18">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" t="s">
-        <v>79</v>
-      </c>
-      <c r="F42" t="s">
-        <v>80</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="102">
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" ht="68.099999999999994">
       <c r="A43" s="12">
         <v>46315</v>
       </c>
       <c r="B43" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C43" s="18">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C43" s="18">
-        <v>0.5</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>23</v>
@@ -2834,53 +2935,53 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="51">
+    <row r="44" spans="1:9" ht="118.5" customHeight="1">
       <c r="A44" s="12">
         <v>46315</v>
       </c>
       <c r="B44" s="18">
-        <v>0.375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C44" s="18">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E44" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17.100000000000001">
+    <row r="45" spans="1:9" ht="51">
       <c r="A45" s="12">
         <v>46315</v>
       </c>
       <c r="B45" s="18">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="C45" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E45" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
@@ -2891,22 +2992,22 @@
         <v>46315</v>
       </c>
       <c r="B46" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="C46" s="18">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C46" s="18">
-        <v>0.47916666666666669</v>
-      </c>
       <c r="D46" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
@@ -2917,22 +3018,22 @@
         <v>46315</v>
       </c>
       <c r="B47" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C47" s="18">
         <v>0.47916666666666669</v>
       </c>
-      <c r="C47" s="18">
-        <v>0.5</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
@@ -2943,28 +3044,63 @@
         <v>46315</v>
       </c>
       <c r="B48" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C48" s="18">
         <v>0.5</v>
       </c>
-      <c r="C48" s="18">
+      <c r="D48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="17.100000000000001">
+      <c r="A49" s="12">
+        <v>46315</v>
+      </c>
+      <c r="B49" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="C49" s="18">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E48" t="s">
-        <v>83</v>
-      </c>
-      <c r="F48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="D49" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H49" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I8:I13"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I4" r:id="rId1" xr:uid="{F8B24EBD-6CF5-4ABE-981A-C1DF5FBA39FF}"/>
+    <hyperlink ref="I8:I13" r:id="rId2" display="https://teams.microsoft.com/meet/236360195720129?p=CbI3UObtPLPgIgMogm" xr:uid="{F463185E-E386-4CAA-996A-FC8EF321124E}"/>
+    <hyperlink ref="I16" r:id="rId3" xr:uid="{5C651494-3780-400E-9464-C8933F12A297}"/>
+    <hyperlink ref="I30" r:id="rId4" xr:uid="{4D6938B4-EABA-47AD-BB77-571B03D4FC4B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3025,10 +3161,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -3051,10 +3187,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -3077,7 +3213,7 @@
         <v>0.4375</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="68.099999999999994">
@@ -3091,16 +3227,16 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
@@ -3117,10 +3253,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -3132,7 +3268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.100000000000001">
+    <row r="7" spans="1:9" ht="15.75">
       <c r="A7" s="12">
         <v>46316</v>
       </c>
@@ -3143,10 +3279,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="51">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="46.5">
       <c r="A8" s="12">
         <v>46316</v>
       </c>
@@ -3157,10 +3293,10 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -3171,8 +3307,11 @@
       <c r="H8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="68.099999999999994">
+      <c r="I8" s="26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A9" s="12">
         <v>46316</v>
       </c>
@@ -3183,10 +3322,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -3197,8 +3336,9 @@
       <c r="H9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="84.95">
+      <c r="I9" s="26"/>
+    </row>
+    <row r="10" spans="1:9" ht="84.95" customHeight="1">
       <c r="A10" s="12">
         <v>46316</v>
       </c>
@@ -3209,10 +3349,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -3223,8 +3363,9 @@
       <c r="H10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="84.95">
+      <c r="I10" s="26"/>
+    </row>
+    <row r="11" spans="1:9" ht="84.95" customHeight="1">
       <c r="A11" s="12">
         <v>46316</v>
       </c>
@@ -3235,10 +3376,10 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -3249,8 +3390,9 @@
       <c r="H11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="102">
+      <c r="I11" s="26"/>
+    </row>
+    <row r="12" spans="1:9" ht="102" customHeight="1">
       <c r="A12" s="12">
         <v>46316</v>
       </c>
@@ -3261,10 +3403,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -3275,6 +3417,7 @@
       <c r="H12" t="s">
         <v>13</v>
       </c>
+      <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:9" ht="30.75">
       <c r="A13" s="12">
@@ -3287,16 +3430,16 @@
         <v>0.375</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
@@ -3313,10 +3456,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -3339,10 +3482,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -3365,10 +3508,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -3380,7 +3523,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="51">
+    <row r="17" spans="1:9" ht="51">
       <c r="A17" s="12">
         <v>46316</v>
       </c>
@@ -3391,10 +3534,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -3406,7 +3549,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="84.95">
+    <row r="18" spans="1:9" ht="77.25">
       <c r="A18" s="12">
         <v>46316</v>
       </c>
@@ -3417,10 +3560,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -3431,8 +3574,11 @@
       <c r="H18" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="102">
+      <c r="I18" s="24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="105.75" customHeight="1">
       <c r="A19" s="12">
         <v>46316</v>
       </c>
@@ -3443,7 +3589,7 @@
         <v>0.375</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -3452,13 +3598,16 @@
         <v>11</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="102">
+      <c r="I19" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="89.25" customHeight="1">
       <c r="A20" s="12">
         <v>46316</v>
       </c>
@@ -3469,7 +3618,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -3483,8 +3632,11 @@
       <c r="H20" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="33.950000000000003">
+      <c r="I20" s="24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="33.950000000000003">
       <c r="A21" s="12">
         <v>46316</v>
       </c>
@@ -3495,7 +3647,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -3504,13 +3656,13 @@
         <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="33.950000000000003">
+    <row r="22" spans="1:9" ht="33.950000000000003">
       <c r="A22" s="12">
         <v>46316</v>
       </c>
@@ -3521,7 +3673,7 @@
         <v>0.46875</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -3530,13 +3682,13 @@
         <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="102">
+    <row r="23" spans="1:9" ht="102">
       <c r="A23" s="12">
         <v>46316</v>
       </c>
@@ -3547,7 +3699,7 @@
         <v>0.5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -3556,13 +3708,13 @@
         <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="102">
+    <row r="24" spans="1:9" ht="102">
       <c r="A24" s="12">
         <v>46316</v>
       </c>
@@ -3573,7 +3725,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -3588,7 +3740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="84.95">
+    <row r="25" spans="1:9" ht="84.95">
       <c r="A25" s="12">
         <v>46316</v>
       </c>
@@ -3599,7 +3751,7 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -3614,7 +3766,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="84.95">
+    <row r="26" spans="1:9" ht="84.95">
       <c r="A26" s="12">
         <v>46316</v>
       </c>
@@ -3625,7 +3777,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -3640,7 +3792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="119.1">
+    <row r="27" spans="1:9" ht="119.1">
       <c r="A27" s="12">
         <v>46316</v>
       </c>
@@ -3651,7 +3803,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -3666,7 +3818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="68.099999999999994">
+    <row r="28" spans="1:9" ht="68.099999999999994">
       <c r="A28" s="12">
         <v>46316</v>
       </c>
@@ -3677,7 +3829,7 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -3692,7 +3844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="68.099999999999994">
+    <row r="29" spans="1:9" ht="68.099999999999994">
       <c r="A29" s="12">
         <v>46316</v>
       </c>
@@ -3703,7 +3855,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -3718,7 +3870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="51">
+    <row r="30" spans="1:9" ht="51">
       <c r="A30" s="12">
         <v>46316</v>
       </c>
@@ -3729,22 +3881,22 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="51">
+    <row r="31" spans="1:9" ht="51">
       <c r="A31" s="12">
         <v>46316</v>
       </c>
@@ -3755,22 +3907,22 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="33.950000000000003">
+    <row r="32" spans="1:9" ht="33.950000000000003">
       <c r="A32" s="12">
         <v>46316</v>
       </c>
@@ -3781,10 +3933,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -3796,7 +3948,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="84.95">
+    <row r="33" spans="1:9" ht="84.95">
       <c r="A33" s="12">
         <v>46316</v>
       </c>
@@ -3807,10 +3959,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -3822,7 +3974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="204">
+    <row r="34" spans="1:9" ht="204">
       <c r="A34" s="12">
         <v>46316</v>
       </c>
@@ -3833,10 +3985,10 @@
         <v>0.625</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -3848,7 +4000,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="135.94999999999999">
+    <row r="35" spans="1:9" ht="135.94999999999999">
       <c r="A35" s="12">
         <v>46316</v>
       </c>
@@ -3859,10 +4011,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -3874,7 +4026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="102">
+    <row r="36" spans="1:9" ht="102">
       <c r="A36" s="12">
         <v>46316</v>
       </c>
@@ -3885,10 +4037,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -3900,7 +4052,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="102">
+    <row r="37" spans="1:9" ht="102">
       <c r="A37" s="12">
         <v>46316</v>
       </c>
@@ -3911,10 +4063,10 @@
         <v>0.6875</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -3926,7 +4078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="135.94999999999999">
+    <row r="38" spans="1:9" ht="135.94999999999999">
       <c r="A38" s="12">
         <v>46316</v>
       </c>
@@ -3937,10 +4089,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
@@ -3952,7 +4104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="68.099999999999994">
+    <row r="39" spans="1:9" ht="61.5">
       <c r="A39" s="12">
         <v>46316</v>
       </c>
@@ -3963,19 +4115,22 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="153">
+        <v>47</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="153">
       <c r="A40" s="12">
         <v>46316</v>
       </c>
@@ -3986,19 +4141,19 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H40" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="68.099999999999994">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="68.099999999999994">
       <c r="A41" s="12">
         <v>46316</v>
       </c>
@@ -4009,10 +4164,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -4024,7 +4179,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="51">
+    <row r="42" spans="1:9" ht="51">
       <c r="A42" s="12">
         <v>46316</v>
       </c>
@@ -4035,10 +4190,10 @@
         <v>0.375</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -4050,7 +4205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="119.1">
+    <row r="43" spans="1:9" ht="119.1">
       <c r="A43" s="12">
         <v>46316</v>
       </c>
@@ -4061,10 +4216,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E43" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
@@ -4076,7 +4231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="84.95">
+    <row r="44" spans="1:9" ht="84.95">
       <c r="A44" s="12">
         <v>46316</v>
       </c>
@@ -4087,10 +4242,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E44" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
@@ -4102,7 +4257,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="33.950000000000003">
+    <row r="45" spans="1:9" ht="33.950000000000003">
       <c r="A45" s="12">
         <v>46316</v>
       </c>
@@ -4113,22 +4268,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="68.099999999999994">
+    <row r="46" spans="1:9" ht="68.099999999999994">
       <c r="A46" s="12">
         <v>46316</v>
       </c>
@@ -4139,10 +4294,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
@@ -4154,7 +4309,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="33.950000000000003">
+    <row r="47" spans="1:9" ht="33.950000000000003">
       <c r="A47" s="12">
         <v>46316</v>
       </c>
@@ -4165,13 +4320,13 @@
         <v>0.375</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E47" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F47" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>19</v>
@@ -4180,7 +4335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="33.950000000000003">
+    <row r="48" spans="1:9" ht="33.950000000000003">
       <c r="A48" s="12">
         <v>46316</v>
       </c>
@@ -4191,13 +4346,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F48" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>23</v>
@@ -4217,10 +4372,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -4234,10 +4389,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="E52" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I8:I12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I20" r:id="rId1" xr:uid="{FC32B617-59E4-4C06-859F-4AAAE4EFE882}"/>
+    <hyperlink ref="I8" r:id="rId2" xr:uid="{2819DA45-DB42-4A92-B450-16230ECD7459}"/>
+    <hyperlink ref="I39" r:id="rId3" xr:uid="{D24D438E-2CF8-42B8-9DE7-67A20A75DF1A}"/>
+    <hyperlink ref="I19" r:id="rId4" xr:uid="{CCCD8BFB-0939-D149-BD09-CE29918D8AAB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4287,7 +4451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="33.950000000000003">
+    <row r="2" spans="1:9" ht="46.5">
       <c r="A2" s="12">
         <v>46317</v>
       </c>
@@ -4298,22 +4462,25 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="33.950000000000003">
+      <c r="I2" s="25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="46.5">
       <c r="A3" s="12">
         <v>46317</v>
       </c>
@@ -4324,22 +4491,25 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="51">
+      <c r="I3" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="46.5">
       <c r="A4" s="12">
         <v>46317</v>
       </c>
@@ -4350,22 +4520,25 @@
         <v>0.40625</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="33.950000000000003">
+      <c r="I4" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="46.5">
       <c r="A5" s="12">
         <v>46317</v>
       </c>
@@ -4376,19 +4549,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s">
         <v>31</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.100000000000001">
@@ -4402,7 +4578,7 @@
         <v>0.4375</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="33.950000000000003">
@@ -4416,10 +4592,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -4442,10 +4618,10 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -4468,10 +4644,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -4494,7 +4670,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="33.950000000000003">
@@ -4508,10 +4684,10 @@
         <v>0.625</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -4534,10 +4710,10 @@
         <v>0.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -4560,10 +4736,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -4586,7 +4762,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>27</v>
@@ -4612,7 +4788,7 @@
         <v>0.375</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>27</v>
@@ -4638,7 +4814,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>27</v>
@@ -4653,7 +4829,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="102">
+    <row r="17" spans="1:9" ht="102">
       <c r="A17" s="12">
         <v>46317</v>
       </c>
@@ -4664,7 +4840,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E17" s="21" t="s">
         <v>27</v>
@@ -4679,7 +4855,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="51">
+    <row r="18" spans="1:9" ht="46.5">
       <c r="A18" s="12">
         <v>46317</v>
       </c>
@@ -4690,7 +4866,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>27</v>
@@ -4704,8 +4880,11 @@
       <c r="H18" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="51">
+      <c r="I18" s="24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="46.5">
       <c r="A19" s="12">
         <v>46317</v>
       </c>
@@ -4716,7 +4895,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>27</v>
@@ -4730,8 +4909,11 @@
       <c r="H19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="51">
+      <c r="I19" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="51">
       <c r="A20" s="12">
         <v>46317</v>
       </c>
@@ -4742,10 +4924,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4757,7 +4939,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="51">
+    <row r="21" spans="1:9" ht="51">
       <c r="A21" s="12">
         <v>46317</v>
       </c>
@@ -4768,48 +4950,48 @@
         <v>0.375</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="119.1">
+    <row r="22" spans="1:9" ht="108">
       <c r="A22" s="12">
         <v>46317</v>
       </c>
       <c r="B22" s="18">
         <v>0.375</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>156</v>
+      <c r="C22" s="18">
+        <v>0.38541666666666669</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="84.95">
+    <row r="23" spans="1:9" ht="77.25">
       <c r="A23" s="12">
         <v>46317</v>
       </c>
@@ -4820,22 +5002,22 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="84.95">
+    <row r="24" spans="1:9" ht="84.95">
       <c r="A24" s="12">
         <v>46317</v>
       </c>
@@ -4846,22 +5028,22 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.950000000000003">
+    <row r="25" spans="1:9" ht="33.950000000000003">
       <c r="A25" s="12">
         <v>46317</v>
       </c>
@@ -4872,22 +5054,22 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="51">
+    <row r="26" spans="1:9" ht="51">
       <c r="A26" s="12">
         <v>46317</v>
       </c>
@@ -4898,10 +5080,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -4913,7 +5095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="68.099999999999994">
+    <row r="27" spans="1:9" ht="68.099999999999994">
       <c r="A27" s="12">
         <v>46317</v>
       </c>
@@ -4924,10 +5106,10 @@
         <v>0.375</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
@@ -4939,7 +5121,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="33.950000000000003">
+    <row r="28" spans="1:9" ht="33.950000000000003">
       <c r="A28" s="12">
         <v>46317</v>
       </c>
@@ -4950,10 +5132,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -4965,7 +5147,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="33.950000000000003">
+    <row r="29" spans="1:9" ht="33.950000000000003">
       <c r="A29" s="12">
         <v>46317</v>
       </c>
@@ -4976,10 +5158,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -4991,7 +5173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="68.099999999999994">
+    <row r="30" spans="1:9" ht="68.099999999999994">
       <c r="A30" s="12">
         <v>46317</v>
       </c>
@@ -5002,22 +5184,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="17.100000000000001">
+    <row r="31" spans="1:9" ht="17.100000000000001">
       <c r="A31" s="12">
         <v>46317</v>
       </c>
@@ -5028,10 +5210,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
@@ -5043,7 +5225,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="33.950000000000003">
+    <row r="32" spans="1:9" ht="33.950000000000003">
       <c r="A32" s="12">
         <v>46317</v>
       </c>
@@ -5054,10 +5236,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -5069,7 +5251,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="33.950000000000003">
+    <row r="33" spans="1:9" ht="33.950000000000003">
       <c r="A33" s="12">
         <v>46317</v>
       </c>
@@ -5080,22 +5262,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30.75">
+    <row r="34" spans="1:9" ht="30.75">
       <c r="A34" s="12">
         <v>46317</v>
       </c>
@@ -5106,22 +5288,22 @@
         <v>0.5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="68.099999999999994">
+    <row r="35" spans="1:9" ht="68.099999999999994">
       <c r="A35" s="12">
         <v>46317</v>
       </c>
@@ -5132,19 +5314,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="84.95">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="77.25">
       <c r="A36" s="12">
         <v>46317</v>
       </c>
@@ -5155,13 +5337,13 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>23</v>
@@ -5169,8 +5351,11 @@
       <c r="H36" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="17.100000000000001">
+      <c r="I36" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17.100000000000001">
       <c r="A37" s="12">
         <v>46317</v>
       </c>
@@ -5181,16 +5366,16 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="17.100000000000001">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17.100000000000001">
       <c r="A38" s="12">
         <v>46317</v>
       </c>
@@ -5201,13 +5386,13 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="D38" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>23</v>
@@ -5216,7 +5401,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="33.950000000000003">
+    <row r="39" spans="1:9" ht="33.950000000000003">
       <c r="A39" s="12">
         <v>46317</v>
       </c>
@@ -5227,22 +5412,22 @@
         <v>0.1875</v>
       </c>
       <c r="D39" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="17.100000000000001">
+    <row r="40" spans="1:9" ht="17.100000000000001">
       <c r="A40" s="12">
         <v>46317</v>
       </c>
@@ -5253,22 +5438,31 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H40" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I19" r:id="rId1" xr:uid="{45DCC090-C842-47F8-AA21-60089D79061C}"/>
+    <hyperlink ref="I18" r:id="rId2" xr:uid="{CE097CE5-E7A1-4558-BC32-1132D26AFCA7}"/>
+    <hyperlink ref="I2" r:id="rId3" xr:uid="{7A558243-3E31-42AB-AAA1-40F94DB00B20}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{321BBD08-D24F-4FFB-9BAF-4EF3565D6D74}"/>
+    <hyperlink ref="I5" r:id="rId5" xr:uid="{B570705A-A170-4F60-B9EB-C517400AE864}"/>
+    <hyperlink ref="I36" r:id="rId6" xr:uid="{947F3F53-3062-48C4-8F1A-6B21543BB41E}"/>
+    <hyperlink ref="I4" r:id="rId7" xr:uid="{991392A4-E965-4ECF-AB97-B0C42403684A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5317,7 +5511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="51">
+    <row r="2" spans="1:9" ht="77.25">
       <c r="A2" s="12">
         <v>46318</v>
       </c>
@@ -5328,19 +5522,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="51">
@@ -5354,19 +5551,19 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="51">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="46.5">
       <c r="A4" s="12">
         <v>46318</v>
       </c>
@@ -5377,10 +5574,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -5391,8 +5588,11 @@
       <c r="H4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="68.099999999999994">
+      <c r="I4" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="61.5">
       <c r="A5" s="12">
         <v>46318</v>
       </c>
@@ -5403,10 +5603,10 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -5417,8 +5617,11 @@
       <c r="H5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="68.099999999999994">
+      <c r="I5" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="61.5">
       <c r="A6" s="12">
         <v>46318</v>
       </c>
@@ -5429,10 +5632,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -5442,6 +5645,9 @@
       </c>
       <c r="H6" t="s">
         <v>31</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="68.099999999999994">
@@ -5455,10 +5661,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -5481,10 +5687,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -5507,19 +5713,19 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17.100000000000001">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="77.25">
       <c r="A10" s="12">
         <v>46318</v>
       </c>
@@ -5530,7 +5736,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -5539,10 +5745,13 @@
         <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="68.099999999999994">
@@ -5556,16 +5765,16 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
@@ -5582,16 +5791,16 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
@@ -5608,16 +5817,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
@@ -5634,13 +5843,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="E14" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>19</v>
@@ -5660,13 +5869,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>12</v>
@@ -5686,7 +5895,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.100000000000001">
@@ -5700,11 +5909,18 @@
         <v>0.4375</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I4" r:id="rId1" xr:uid="{C9493442-D043-4F0C-87C2-48D7691A2D28}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{9EEC6AE0-738A-4A01-A567-DEBBDF2C5FBB}"/>
+    <hyperlink ref="I6" r:id="rId3" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.youtube.com%2Flive%2Fesp7PURwXVw%3Fsi%3Dsj4hy4V6H6qsgsCH&amp;data=05%7C02%7Canderson.garzon.s%40uniminuto.edu%7C8c40ee5cc1b4465bf10a08df2a0d6ea2%7Cb1ba85eba25344679ee8d4f8ed4df300%7C1%7C0%7C639275909426166060%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=vLjWfGSRgHp4LJ6pY3I83XdSpAYEt0XuJi4BfC3%2FFvA%3D&amp;reserved=0" xr:uid="{8191B0B2-0D8D-467E-8B9E-829DDC0876A2}"/>
+    <hyperlink ref="I2" r:id="rId4" xr:uid="{8E47C14B-12C8-44DD-B099-1CCDAF1D329E}"/>
+    <hyperlink ref="I10" r:id="rId5" xr:uid="{A870712A-1A07-4428-AE09-413B7AD8BBDB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5753,7 +5969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="68.099999999999994">
+    <row r="2" spans="1:9" ht="61.5">
       <c r="A2" s="12">
         <v>46319</v>
       </c>
@@ -5764,19 +5980,22 @@
         <v>0.75</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68.099999999999994">
@@ -5790,13 +6009,13 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>23</v>
@@ -5805,7 +6024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="51">
+    <row r="4" spans="1:9" ht="46.5">
       <c r="A4" s="12">
         <v>46319</v>
       </c>
@@ -5816,19 +6035,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.100000000000001">
@@ -5842,7 +6064,7 @@
         <v>0.4375</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="3"/>
@@ -5858,16 +6080,16 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
@@ -5884,13 +6106,13 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
@@ -5910,13 +6132,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>23</v>
@@ -5936,13 +6158,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -5962,13 +6184,13 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>23</v>
@@ -5988,13 +6210,13 @@
         <v>0.375</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>30</v>
@@ -6003,7 +6225,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="84.95">
+    <row r="12" spans="1:9" ht="77.25">
       <c r="A12" s="12">
         <v>46319</v>
       </c>
@@ -6014,13 +6236,13 @@
         <v>0.40625</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>23</v>
@@ -6040,13 +6262,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>23</v>
@@ -6055,7 +6277,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="51">
+    <row r="14" spans="1:9" ht="30.75">
       <c r="A14" s="12">
         <v>46319</v>
       </c>
@@ -6066,13 +6288,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>15</v>
@@ -6081,7 +6303,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="51">
+    <row r="15" spans="1:9" ht="30.75">
       <c r="A15" s="12">
         <v>46319</v>
       </c>
@@ -6092,13 +6314,13 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>15</v>
@@ -6107,7 +6329,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="68.099999999999994">
+    <row r="16" spans="1:9" ht="61.5">
       <c r="A16" s="12">
         <v>46319</v>
       </c>
@@ -6118,13 +6340,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>12</v>
@@ -6144,10 +6366,14 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{ED6291B3-F19A-4735-AB07-07D4F75A7948}"/>
+    <hyperlink ref="I4" r:id="rId2" xr:uid="{75E2C9A4-9B4E-46C2-B3F4-863E434C8B76}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6CCA7D1-27A9-484C-BF01-2EB05B7DAB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11C8482D-E5DD-4CC8-B003-6AD13C6CAA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="5" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="2" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="238">
   <si>
     <t>DÍA</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>Auditorio C204</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/d9c245be-f2ab-4820-8b4b-6772959b2259@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t>CHARLAS WEBINAR MAFB-LFDD
@@ -370,6 +373,9 @@
  Karen Liliana Patiño Cruz </t>
   </si>
   <si>
+    <t>https://events.teams.microsoft.com/event/4a0deab1-a5c3-42d5-b4f9-d32806966699@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t>Energías Renovables enfocadas en la energía nuclear 
 Javier Maury (Coordinador Académico) - Katherine Rojas (DGC)
  Escobar Carrillo, Juan Daniel  
@@ -539,6 +545,9 @@
 2. Cristian Andrés Cabezas Justinico
 3. Edisson Israel Cruz Varón
 4. Diego Alejandro Saray Moreno  </t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/46f4a92d-a5b9-4ffd-98a5-c05f9da97a74@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
@@ -635,8 +644,10 @@
     <t>Del prompt a la experiencia de aprendizaje: inteligencia artificial y diseño instruccional con sentido pedagógico 
 Karla Beatriz Gómez Santana
 Kenia Viridiana Ocampo Vera, 
-Universidad de Guadalajara
-Enlace: https://teams.microsoft.com/meet/277921384618913?p=RKSqlSnDTLi83MwWvY</t>
+Universidad de Guadalajara</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/36eb2a1a-32d6-48f9-ab67-ba99d2dc807f@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t>Estrategia tejer calidad 
@@ -1765,7 +1776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="84.95">
+    <row r="9" spans="1:9" ht="61.5">
       <c r="A9" s="5">
         <v>46314</v>
       </c>
@@ -2193,6 +2204,12 @@
       <c r="G14" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="33.950000000000003">
       <c r="A15" s="12">
@@ -2205,19 +2222,19 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="46.5">
@@ -2231,10 +2248,10 @@
         <v>0.375</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -2246,7 +2263,7 @@
         <v>31</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="51">
@@ -2260,10 +2277,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -2286,10 +2303,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -2312,10 +2329,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -2338,10 +2355,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -2364,10 +2381,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
@@ -2390,10 +2407,10 @@
         <v>0.625</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
@@ -2416,10 +2433,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -2442,10 +2459,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
@@ -2468,10 +2485,10 @@
         <v>0.6875</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
@@ -2494,10 +2511,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -2520,16 +2537,16 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -2546,10 +2563,10 @@
         <v>0.375</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -2572,10 +2589,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -2599,10 +2616,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
@@ -2614,7 +2631,7 @@
         <v>13</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="51">
@@ -2628,10 +2645,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
@@ -2654,10 +2671,10 @@
         <v>0.375</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -2680,10 +2697,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" t="s">
         <v>71</v>
-      </c>
-      <c r="E33" t="s">
-        <v>70</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -2706,10 +2723,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -2732,10 +2749,10 @@
         <v>0.5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -2758,10 +2775,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -2784,46 +2801,49 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" t="s">
         <v>76</v>
       </c>
-      <c r="E37" t="s">
-        <v>75</v>
-      </c>
       <c r="F37" t="s">
         <v>11</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:9" ht="84.95">
+    <row r="38" spans="1:9" ht="77.25">
       <c r="A38" s="12">
         <v>46315</v>
       </c>
       <c r="B38" s="18">
-        <v>0.49305555555555558</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="C38" s="18">
         <v>0.47222222222222221</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H38" t="s">
         <v>31</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="102">
@@ -2837,10 +2857,10 @@
         <v>0.4826388888888889</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -2863,16 +2883,16 @@
         <v>0.5</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
@@ -2889,10 +2909,10 @@
         <v>0.375</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -2920,13 +2940,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>23</v>
@@ -2946,13 +2966,13 @@
         <v>0.5</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" t="s">
         <v>87</v>
       </c>
-      <c r="E44" t="s">
-        <v>85</v>
-      </c>
       <c r="F44" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>23</v>
@@ -2972,10 +2992,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -2998,16 +3018,16 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
@@ -3024,16 +3044,16 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E47" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
@@ -3050,16 +3070,16 @@
         <v>0.5</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E48" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
@@ -3076,16 +3096,16 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E49" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
@@ -3100,6 +3120,7 @@
     <hyperlink ref="I8:I13" r:id="rId2" display="https://teams.microsoft.com/meet/236360195720129?p=CbI3UObtPLPgIgMogm" xr:uid="{F463185E-E386-4CAA-996A-FC8EF321124E}"/>
     <hyperlink ref="I16" r:id="rId3" xr:uid="{5C651494-3780-400E-9464-C8933F12A297}"/>
     <hyperlink ref="I30" r:id="rId4" xr:uid="{4D6938B4-EABA-47AD-BB77-571B03D4FC4B}"/>
+    <hyperlink ref="I38" r:id="rId5" xr:uid="{8E6A0EE6-7014-4188-AC92-14F5BD6368F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3161,10 +3182,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -3187,10 +3208,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -3227,16 +3248,16 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
@@ -3253,10 +3274,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -3293,10 +3314,10 @@
         <v>0.625</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -3308,7 +3329,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
@@ -3322,10 +3343,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -3349,10 +3370,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -3376,10 +3397,10 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -3403,10 +3424,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -3430,16 +3451,16 @@
         <v>0.375</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
@@ -3456,10 +3477,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -3482,10 +3503,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
         <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>103</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -3508,10 +3529,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -3534,10 +3555,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -3560,10 +3581,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -3575,7 +3596,7 @@
         <v>31</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="105.75" customHeight="1">
@@ -3589,7 +3610,7 @@
         <v>0.375</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -3598,13 +3619,13 @@
         <v>11</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H19" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="89.25" customHeight="1">
@@ -3618,7 +3639,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -3633,7 +3654,7 @@
         <v>31</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="33.950000000000003">
@@ -3647,7 +3668,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -3656,7 +3677,7 @@
         <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -3673,7 +3694,7 @@
         <v>0.46875</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -3682,13 +3703,13 @@
         <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="102">
+    <row r="23" spans="1:9" ht="92.25">
       <c r="A23" s="12">
         <v>46316</v>
       </c>
@@ -3699,7 +3720,7 @@
         <v>0.5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -3708,10 +3729,13 @@
         <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H23" t="s">
         <v>31</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="102">
@@ -3725,7 +3749,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -3751,7 +3775,7 @@
         <v>0.625</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -3777,7 +3801,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -3803,7 +3827,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -3829,7 +3853,7 @@
         <v>0.6875</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -3855,7 +3879,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -3881,16 +3905,16 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -3907,16 +3931,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -3933,10 +3957,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -3959,10 +3983,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -3985,10 +4009,10 @@
         <v>0.625</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -4011,10 +4035,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -4037,10 +4061,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -4063,10 +4087,10 @@
         <v>0.6875</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -4089,10 +4113,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
@@ -4115,22 +4139,22 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="153">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="77.25">
       <c r="A40" s="12">
         <v>46316</v>
       </c>
@@ -4141,16 +4165,19 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H40" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="68.099999999999994">
@@ -4164,10 +4191,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -4190,10 +4217,10 @@
         <v>0.375</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -4216,10 +4243,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
@@ -4242,10 +4269,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
@@ -4268,16 +4295,16 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
@@ -4294,10 +4321,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
@@ -4320,13 +4347,13 @@
         <v>0.375</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>19</v>
@@ -4346,13 +4373,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F48" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>23</v>
@@ -4366,16 +4393,16 @@
         <v>46316</v>
       </c>
       <c r="B49" s="18">
-        <v>0.4375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C49" s="18">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -4389,7 +4416,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="E52" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4401,6 +4428,8 @@
     <hyperlink ref="I8" r:id="rId2" xr:uid="{2819DA45-DB42-4A92-B450-16230ECD7459}"/>
     <hyperlink ref="I39" r:id="rId3" xr:uid="{D24D438E-2CF8-42B8-9DE7-67A20A75DF1A}"/>
     <hyperlink ref="I19" r:id="rId4" xr:uid="{CCCD8BFB-0939-D149-BD09-CE29918D8AAB}"/>
+    <hyperlink ref="I40" r:id="rId5" xr:uid="{91101E1E-D27C-43AD-95D4-9F7F27CA2CFD}"/>
+    <hyperlink ref="I23" r:id="rId6" xr:uid="{8ED477E0-57DD-4243-95BA-7B749553D740}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4462,22 +4491,22 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="46.5">
@@ -4491,22 +4520,22 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="46.5">
@@ -4520,22 +4549,22 @@
         <v>0.40625</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="46.5">
@@ -4549,22 +4578,22 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.100000000000001">
@@ -4592,10 +4621,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -4618,10 +4647,10 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -4644,10 +4673,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -4684,10 +4713,10 @@
         <v>0.625</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -4710,10 +4739,10 @@
         <v>0.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -4736,10 +4765,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -4762,7 +4791,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>27</v>
@@ -4788,7 +4817,7 @@
         <v>0.375</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>27</v>
@@ -4814,7 +4843,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>27</v>
@@ -4840,7 +4869,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E17" s="21" t="s">
         <v>27</v>
@@ -4866,7 +4895,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>27</v>
@@ -4881,7 +4910,7 @@
         <v>31</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="46.5">
@@ -4895,7 +4924,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>27</v>
@@ -4910,7 +4939,7 @@
         <v>31</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="51">
@@ -4924,10 +4953,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4950,16 +4979,16 @@
         <v>0.375</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -4976,16 +5005,16 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
@@ -5002,16 +5031,16 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
@@ -5028,16 +5057,16 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
@@ -5054,16 +5083,16 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -5080,10 +5109,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -5106,10 +5135,10 @@
         <v>0.375</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
@@ -5132,10 +5161,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -5158,10 +5187,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -5184,16 +5213,16 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -5210,10 +5239,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
@@ -5236,10 +5265,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" s="21" t="s">
         <v>184</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>180</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -5262,16 +5291,16 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -5288,16 +5317,16 @@
         <v>0.5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -5314,16 +5343,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="77.25">
@@ -5337,13 +5366,13 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>23</v>
@@ -5352,7 +5381,7 @@
         <v>31</v>
       </c>
       <c r="I36" s="25" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="17.100000000000001">
@@ -5366,13 +5395,13 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="D37" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="17.100000000000001">
@@ -5386,13 +5415,13 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="D38" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>23</v>
@@ -5412,16 +5441,16 @@
         <v>0.1875</v>
       </c>
       <c r="D39" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s">
         <v>31</v>
@@ -5438,16 +5467,16 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="D40" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F40" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H40" t="s">
         <v>31</v>
@@ -5522,22 +5551,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="51">
@@ -5551,16 +5580,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="46.5">
@@ -5574,10 +5603,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -5589,7 +5618,7 @@
         <v>31</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="61.5">
@@ -5603,10 +5632,10 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -5618,7 +5647,7 @@
         <v>31</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="61.5">
@@ -5632,10 +5661,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -5647,7 +5676,7 @@
         <v>31</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="68.099999999999994">
@@ -5661,10 +5690,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -5687,10 +5716,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -5713,16 +5742,16 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="77.25">
@@ -5736,7 +5765,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -5745,13 +5774,13 @@
         <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="68.099999999999994">
@@ -5765,16 +5794,16 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
@@ -5791,16 +5820,16 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
@@ -5817,16 +5846,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
@@ -5843,13 +5872,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>19</v>
@@ -5869,13 +5898,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>12</v>
@@ -5980,22 +6009,22 @@
         <v>0.75</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68.099999999999994">
@@ -6009,13 +6038,13 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>23</v>
@@ -6035,13 +6064,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>23</v>
@@ -6050,7 +6079,7 @@
         <v>13</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.100000000000001">
@@ -6080,16 +6109,16 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>222</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
@@ -6106,13 +6135,13 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
@@ -6132,13 +6161,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>23</v>
@@ -6158,13 +6187,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>224</v>
-      </c>
       <c r="F9" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -6184,13 +6213,13 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>23</v>
@@ -6210,13 +6239,13 @@
         <v>0.375</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>30</v>
@@ -6236,13 +6265,13 @@
         <v>0.40625</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>23</v>
@@ -6262,13 +6291,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>23</v>
@@ -6288,13 +6317,13 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>15</v>
@@ -6314,13 +6343,13 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>15</v>
@@ -6340,13 +6369,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>12</v>

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA6BA21F-B18C-422A-AF6D-4352522A9D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7447F4E0-1FF2-41BF-8362-7FC031A3BA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="2" activeTab="2" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="1" activeTab="3" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,11 @@
     <sheet name="Viernes 23 de octubre" sheetId="7" r:id="rId5"/>
     <sheet name="Sabado 24 de octubre" sheetId="8" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jueves 22 de octubre'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Miércoles 21 de octubre'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Martes 20 de octubre'!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="242">
   <si>
     <t>DÍA</t>
   </si>
@@ -139,21 +144,6 @@
 Presentación musical CEMID</t>
   </si>
   <si>
-    <t>Educación para todos desde la perspectiva de garantía de derechos y la educación para todos.  
-CEMID 
-Slendy Caterin Malpica Orjuela 
-Kathery Yessenia Mendoza Vargas</t>
-  </si>
-  <si>
-    <t>Auditorio B206</t>
-  </si>
-  <si>
-    <t>El DUA desde la neurociencia.
-CEMID 
-Judy Andrea Rueda Gómez 
-Lina María Castañeda Cisneros</t>
-  </si>
-  <si>
     <t xml:space="preserve">Batukids  – ATS
 Ibagué Virtual
 Adriana Balaguera Balaguera
@@ -161,6 +151,9 @@
 Briyith Tatiana Ramírez Villanueva </t>
   </si>
   <si>
+    <t>Auditorio B206</t>
+  </si>
+  <si>
     <t>Conferencia performática</t>
   </si>
   <si>
@@ -170,16 +163,88 @@
     <t>https://teams.microsoft.com/meet/238014813785739?p=QO1Vk1a0ta3XTUDEXx</t>
   </si>
   <si>
-    <t>Coffee Break &amp; Networiking</t>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Diagnóstico morfofuncional del perfil de fuerza-velocidad horizontal en el contexto del deporte escolar regional
+Yohandis Abad Camejo, Francisco Freyre Vazquez, Abel Emilio Campaña Garzon - Cuba</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/meet/236360195720129?p=CbI3UObtPLPgIgMogm</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Caracterización de la fuerza en miembros inferiores en futbolistas prejuveniles de la Escuela Nueva Era de Sogamoso como apoyo a la educación física escolar.
+Nataly Alejandra Velandia Naranjo</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Implementación de la Plataforma de Educación física (PEF)
+Pablo Paúl Almeyda Torres, Susana Elizabeth Saravia Tasayco, Jimmy Alexandre Vergara Blas. Perú</t>
+  </si>
+  <si>
+    <t>Retos y posibilidades de la inteligencia artificial en la formación de docentes
+Saúl Antonio Reyes
+Celebración renovación alta calidad Lic. Informática</t>
+  </si>
+  <si>
+    <t>Auditorio C204</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/d9c245be-f2ab-4820-8b4b-6772959b2259@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Old dogs, new tricks: Life long learning through exercise for older adults"
+Virtual sincrónico
+Miranda Foyster </t>
+  </si>
+  <si>
+    <t>Auditorio B205</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/meet/2631746659935957?p=QMTrrbgFlJKmQq9koj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+Evaluar el proceso y no solo el producto: el portafolio digital en la formación del profesorado de Educación Física 
+Josep Campos-Rius </t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA 
+Diagnóstico de competencias genéricas en estudiantes universitarios como base para una estrategia con LEGO Serious Play                         
+Melissa Andrea Laiton Garnica(Colombia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyecto ATS - Todos juntos - Ibagué - virtual
+CEMID: José Argenis Mendoza
+ Magerlly Beltrán Acosta 
+ Maryory Jaramillo Carvajal 
+ Karen Liliana Patiño Cruz </t>
+  </si>
+  <si>
+    <t>Salón C508</t>
+  </si>
+  <si>
+    <t>Kids Untalk</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/4a0deab1-a5c3-42d5-b4f9-d32806966699@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
+    <t>Educación para todos desde la perspectiva de garantía de derechos y la educación para todos.  
+CEMID 
+Slendy Caterin Malpica Orjuela 
+Kathery Yessenia Mendoza Vargas</t>
+  </si>
+  <si>
+    <t>El DUA desde la neurociencia.
+CEMID 
+Judy Andrea Rueda Gómez 
+Lina María Castañeda Cisneros</t>
   </si>
   <si>
     <t>Diálogos de Semilleros Ciprés</t>
   </si>
   <si>
     <t>Poster expandido</t>
-  </si>
-  <si>
-    <t>Almuerzo</t>
   </si>
   <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
@@ -187,61 +252,14 @@
 Yammir López Brito (España), Óscar Nazario García Rivera, Edi Luis Alejandro Gómez Pérez(México- virtual ) </t>
   </si>
   <si>
-    <t>https://teams.microsoft.com/meet/236360195720129?p=CbI3UObtPLPgIgMogm</t>
-  </si>
-  <si>
     <t>CONGRESO IDRM -REDDI EDUFISICA 
 Actividad física adaptada: Educación para la salud y prescripción del ejercicio físico. 
  Luciana Brito - Argentina</t>
   </si>
   <si>
     <t>CONGRESO IDRM -REDDI EDUFISICA
-Diagnóstico morfofuncional del perfil de fuerza-velocidad horizontal en el contexto del deporte escolar regional
-Yohandis Abad Camejo, Francisco Freyre Vazquez, Abel Emilio Campaña Garzon - Cuba</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Caracterización de la fuerza en miembros inferiores en futbolistas prejuveniles de la Escuela Nueva Era de Sogamoso como apoyo a la educación física escolar.
-Nataly Alejandra Velandia Naranjo</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Implementación de la Plataforma de Educación física (PEF)
-Pablo Paúl Almeyda Torres, Susana Elizabeth Saravia Tasayco, Jimmy Alexandre Vergara Blas. Perú</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
 Educación Física, deporte y enseñanza: un análisis de la política curricular de Educación Física en Argentina
 Emiliozzi M. Valeria, Tocco Cecilia, Goldsworthy Jeremías Jesús</t>
-  </si>
-  <si>
-    <t>Retos y posibilidades de la inteligencia artificial en la formación de docentes
-Saúl Antonio Reyes
-Celebración renovación alta calidad Lic. Informática</t>
-  </si>
-  <si>
-    <t>Auditorio C204</t>
-  </si>
-  <si>
-    <t>https://events.teams.microsoft.com/event/d9c245be-f2ab-4820-8b4b-6772959b2259@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
-  </si>
-  <si>
-    <t>CHARLAS WEBINAR MAFB-LFDD
-Dalis Molina</t>
-  </si>
-  <si>
-    <t>Virtual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Old dogs, new tricks: Life long learning through exercise for older adults"
-Virtual sincrónico
-Miranda Foyster </t>
-  </si>
-  <si>
-    <t>Auditorio B205</t>
-  </si>
-  <si>
-    <t>https://teams.microsoft.com/meet/2631746659935957?p=QMTrrbgFlJKmQq9koj</t>
   </si>
   <si>
     <t>Co-crear lo común: Wikimedia, laboratorios ciudadanos y apropiacion social del conocimiento.
@@ -269,11 +287,6 @@
   </si>
   <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
-Evaluar el proceso y no solo el producto: el portafolio digital en la formación del profesorado de Educación Física 
-Josep Campos-Rius </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
  El Aprendizaje Servicio y Formación Docente en Educación Física
 Miguel Aquilino Diaz Barboza (Perú) </t>
   </si>
@@ -281,11 +294,6 @@
     <t>CONGRESO IDRM -REDDI EDUFISICA
 Gerencia curricular dialógica pentadimensional y formación de competencias investigativas en educación física universitaria: revisión integrativa.                                          
 Jorge Daniel Miranda Guzmán(Colombia)</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA 
-Diagnóstico de competencias genéricas en estudiantes universitarios como base para una estrategia con LEGO Serious Play                         
-Melissa Andrea Laiton Garnica(Colombia)</t>
   </si>
   <si>
     <t>CONGRESO IDRM -REDDI EDUFISICA
@@ -302,9 +310,6 @@
   </si>
   <si>
     <t>Living Lab B201</t>
-  </si>
-  <si>
-    <t>Kids Untalk</t>
   </si>
   <si>
     <t>Semillero de investigación Phobos, proyecto Belt Vision
@@ -348,25 +353,12 @@
     <t xml:space="preserve">Relacionamiento de redes   docentes CONGRESO IDRM -REDDI EDUFISICA </t>
   </si>
   <si>
-    <t>Salón C508</t>
-  </si>
-  <si>
     <t>Impacto de la IA en la escuela – Docentes y Estudiantes
 Paul Cubillos + 1 Estudinate
 CEMID</t>
   </si>
   <si>
     <t>Pistacho Talk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proyecto ATS - Todos juntos - Ibagué - virtual
-CEMID: José Argenis Mendoza
- Magerlly Beltrán Acosta 
- Maryory Jaramillo Carvajal 
- Karen Liliana Patiño Cruz </t>
-  </si>
-  <si>
-    <t>https://events.teams.microsoft.com/event/4a0deab1-a5c3-42d5-b4f9-d32806966699@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
     <t>Energías Renovables enfocadas en la energía nuclear 
@@ -391,6 +383,19 @@
     <t>Plazoleta Rafael García Herreros</t>
   </si>
   <si>
+    <t>CHARLAS WEBINAR MAFB-LFDD
+Dalis Molina</t>
+  </si>
+  <si>
+    <t>Virtual</t>
+  </si>
+  <si>
+    <t>Coffee Break &amp; Networiking</t>
+  </si>
+  <si>
+    <t>Almuerzo</t>
+  </si>
+  <si>
     <t>Estrategias pedagógicas para la enseñanza de niños y niñas con discapacidad
 Ana María Abella Perdomo
 Invitada por confirmar</t>
@@ -421,95 +426,22 @@
     <t>Encuentro de Prácticas Pedagógicas Emergentes y Creativas</t>
   </si>
   <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA  
-Gerente Gonzalo Amaya 8:00 a 8:30am
-Estrategia Cundinamarca deporte incluyente
-Danny Quiñones
- </t>
-  </si>
-  <si>
-    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
-Andrés Camilo Pérez Rodríguez, Cristian Camilo Ladino Marín</t>
-  </si>
-  <si>
-    <t>Taller Experiencial con presentación de Caso:Educación con Propósito: Laboratorio de Innovacón Pedagogíca para Transformar Comunidades 
-EDULAB</t>
-  </si>
-  <si>
-    <t>Taller</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA 
-RUTA STEM EN EDUCACIÓN FÍSICA  
-Pedro Nel Urrea Roa</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Juegos Electrónicos
-Alexander Ospina Bolaños - Presidente PAMESCO - Colombia</t>
-  </si>
-  <si>
-    <t>https://teams.microsoft.com/meet/268438955130536?p=kBLTrRHKhHpZeWejhh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
- Presentación Libro Evaluación y Capacidades Físicas Básicas: Una visión desde la interdisciplinariedad
-Eliana Sofía Monroy Muñoz(Colombia) </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Actividad física y regulación emocional en estudiantes universitarios 
-Deiby Alexander Lara Garzón &amp; Nayelly Tatiana Barragán Cañón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
-Desarrollo de Habilidades Blandas en Educación Básica y Media
-Luis Uriel Méndez Solano - IED Alfonso Reyes Echandía. 
- </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Cuerpos que piensan, mentes que juegan: Estrategias sociomotrices para la formación de sujetos críticos en el siglo XXI.
-John Edwin Valencia Moreno y Oscar Javier Quintero  - Secretaria de Educación Bogotá</t>
-  </si>
-  <si>
-    <t>"Voces del barrio
-Daniel Núñez"</t>
-  </si>
-  <si>
-    <t>Auditorio C205</t>
-  </si>
-  <si>
-    <t>Más allá del clic: Cómo medir la calidad pedagógica real de un RED musical
-Jorge Alvarado 
-UNAD</t>
-  </si>
-  <si>
-    <t>Decolonización de la escucha en la academia
-Luisa Fernanda Arias
-UNAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Enfoques y metodologías actuales para la formación Universitaria en entrenamiento auditivo y solfeo
-Ana María Moreno 
-Universidad de Cundinamarca</t>
-  </si>
-  <si>
-    <t>Divulgación social del conocimiento: posibilidades de participación académica
-Jonathan Caicedo Girón</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conferencia Magistral: "Apego y desarrollo del lenguaje en la primera infancia", abordando el apego como componente biológico y neurológico.
 Dr. Fernando Eli Ledesma Pérez
 UCV - Lima Perú </t>
   </si>
   <si>
+    <t>Auditorio C205</t>
+  </si>
+  <si>
     <t>https://events.teams.microsoft.com/event/e28bcf5e-cb1c-482a-b355-0d6bc86621b1@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
   </si>
   <si>
     <t xml:space="preserve">Taller vivencial: "Leer con el cuerpo y la voz", una experiencia práctica orientada a docentes y agentes educativos sobre lectura en voz alta, narración corporal y mediación afectiva como estrategias de literacidad emergente en la primera infancia.
 Dra. Dora Tamariz  UCV - Lima  - Perú  </t>
+  </si>
+  <si>
+    <t>Taller</t>
   </si>
   <si>
     <t>https://events.teams.microsoft.com/event/1bfeda94-aae3-4289-8bdd-981be1c192b6@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
@@ -522,14 +454,6 @@
   </si>
   <si>
     <t>https://events.teams.microsoft.com/event/1fbb508b-25fc-4f5e-adec-c336215a025f@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
-  </si>
-  <si>
-    <t>Ciudadanía digital en los Colegios Minuto de Dios
-José Argenis Mendoza</t>
-  </si>
-  <si>
-    <t>Iniciativas de IA para la protección del Medio Ambiente 
-María José Villa Moreno, Danna Valentina Rincon Loaiza</t>
   </si>
   <si>
     <t xml:space="preserve">Proyecto ATS ECO - Ibagué
@@ -543,34 +467,125 @@
     <t>https://events.teams.microsoft.com/event/46f4a92d-a5b9-4ffd-98a5-c05f9da97a74@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
   </si>
   <si>
-    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
-Neffar Abdul Arboleda Ortega, Joseph David Fiquitiva Carrillo,Jeisson Miguel Urrego Gonzales  UPN EstudiantesTitulo : Estrategias de motivación extrínseca y retroalimentación en el aprendizaje del drive en jóvenes tenistas: estudio cualitativo longitudinal </t>
-  </si>
-  <si>
     <t>CONGRESO IDRM -REDDI EDUFISICA 
 Política, pedagogía y currículum: una trama discursiva en la enseñanza de la Educación Física en contexto de encierro
 Claudia Rosa Romero
 Ariel Maximiliano Berrondo(Argentina- Virtual)</t>
   </si>
   <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Sendero Ambiental Otium: Un espacio para disfrutar de la actividad física y recreación con la naturaleza con integrantes del proyecto de proyección social "Caminemos por la vida" de la Universidad Surcolombiana
+Angel Miller Roa Cruz, Yibi Salazar Parra, Nicolas Díaz (Colombia)</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA 
+Aleli Torres Ceja y Yammir López Brito
+ Experiencias sobre autonomía en educación física con enfoque freireano: México-Cuba</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Educación física como alternativa para mejorar la calidad de vida de los jóvenes de malambo Atlántico
+José Francisco Mora Núñez</t>
+  </si>
+  <si>
+    <t>Semillero Café sentipensante 
+Juan Esteban Carreño González
+Isaac David Fuentes Durán 
+Linda Saray Martinez Ortiz
+Melany Sareth Rueda Lea</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/ff3d7f14-315f-45c6-bc92-03115e071edb@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA  
+Gerente Gonzalo Amaya 8:00 a 8:30am
+Estrategia Cundinamarca deporte incluyente
+Danny Quiñones
+ </t>
+  </si>
+  <si>
+    <t>Espacio sobre Inteligencia Artificial aplicada a la educación articulado con las Licenciaturas en Informática, Ciencias Naturales y Educación Infantil
+Andrés Camilo Pérez Rodríguez, Cristian Camilo Ladino Marín</t>
+  </si>
+  <si>
+    <t>Taller Experiencial con presentación de Caso:Educación con Propósito: Laboratorio de Innovacón Pedagogíca para Transformar Comunidades 
+EDULAB</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA 
+RUTA STEM EN EDUCACIÓN FÍSICA  
+Pedro Nel Urrea Roa</t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Juegos Electrónicos
+Alexander Ospina Bolaños - Presidente PAMESCO - Colombia</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/meet/268438955130536?p=kBLTrRHKhHpZeWejhh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+ Presentación Libro Evaluación y Capacidades Físicas Básicas: Una visión desde la interdisciplinariedad
+Eliana Sofía Monroy Muñoz(Colombia) </t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Actividad física y regulación emocional en estudiantes universitarios 
+Deiby Alexander Lara Garzón &amp; Nayelly Tatiana Barragán Cañón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+Desarrollo de Habilidades Blandas en Educación Básica y Media
+Luis Uriel Méndez Solano - IED Alfonso Reyes Echandía. 
+ </t>
+  </si>
+  <si>
+    <t>CONGRESO IDRM -REDDI EDUFISICA
+Cuerpos que piensan, mentes que juegan: Estrategias sociomotrices para la formación de sujetos críticos en el siglo XXI.
+John Edwin Valencia Moreno y Oscar Javier Quintero  - Secretaria de Educación Bogotá</t>
+  </si>
+  <si>
+    <t>"Voces del barrio
+Daniel Núñez"</t>
+  </si>
+  <si>
+    <t>Más allá del clic: Cómo medir la calidad pedagógica real de un RED musical
+Jorge Alvarado 
+UNAD</t>
+  </si>
+  <si>
+    <t>Decolonización de la escucha en la academia
+Luisa Fernanda Arias
+UNAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Enfoques y metodologías actuales para la formación Universitaria en entrenamiento auditivo y solfeo
+Ana María Moreno 
+Universidad de Cundinamarca</t>
+  </si>
+  <si>
+    <t>Divulgación social del conocimiento: posibilidades de participación académica
+Jonathan Caicedo Girón</t>
+  </si>
+  <si>
+    <t>Ciudadanía digital en los Colegios Minuto de Dios
+José Argenis Mendoza</t>
+  </si>
+  <si>
+    <t>Iniciativas de IA para la protección del Medio Ambiente 
+María José Villa Moreno, Danna Valentina Rincon Loaiza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
+Neffar Abdul Arboleda Ortega, Joseph David Fiquitiva Carrillo,Jeisson Miguel Urrego Gonzales  UPN EstudiantesTitulo : Estrategias de motivación extrínseca y retroalimentación en el aprendizaje del drive en jóvenes tenistas: estudio cualitativo longitudinal </t>
+  </si>
+  <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA 
 Actividad fisica y habilidades socioemocionales en adolescentes de la fundación ZUA 
 Lizeth Gabriela González Anzola - Deyber Gerardo Mora Velásquez </t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Sendero Ambiental Otium: Un espacio para disfrutar de la actividad física y recreación con la naturaleza con integrantes del proyecto de proyección social "Caminemos por la vida" de la Universidad Surcolombiana
-Angel Miller Roa Cruz, Yibi Salazar Parra, Nicolas Díaz (Colombia)</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA 
-Aleli Torres Ceja y Yammir López Brito
- Experiencias sobre autonomía en educación física con enfoque freireano: México-Cuba</t>
-  </si>
-  <si>
-    <t>CONGRESO IDRM -REDDI EDUFISICA
-Educación física como alternativa para mejorar la calidad de vida de los jóvenes de malambo Atlántico
-José Francisco Mora Núñez</t>
   </si>
   <si>
     <t xml:space="preserve">El Viaje de Nogai: Guardianes de la Diversidad
@@ -626,23 +641,6 @@
 Tutor Juan Pablo Reyes</t>
   </si>
   <si>
-    <t>El desarrollo humano desde el acondicionamiento físico y el bienestar
-Invitado: Diego Fernando Villamizar Gómez
-Moderadora: Dalis Nury Molina Bustamante</t>
-  </si>
-  <si>
-    <t>https://teams.microsoft.com/meet/272197321964862?p=3ZUvVjw3nhTuhT295I</t>
-  </si>
-  <si>
-    <t>Del prompt a la experiencia de aprendizaje: inteligencia artificial y diseño instruccional con sentido pedagógico 
-Karla Beatriz Gómez Santana
-Kenia Viridiana Ocampo Vera, 
-Universidad de Guadalajara</t>
-  </si>
-  <si>
-    <t>https://events.teams.microsoft.com/event/36eb2a1a-32d6-48f9-ab67-ba99d2dc807f@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
-  </si>
-  <si>
     <t>Estrategia tejer calidad 
 Paul Brayan Cubillos Cabrera
 José Luis Gaitán Mendoza 
@@ -661,16 +659,6 @@
 Samuel López Jiménez, </t>
   </si>
   <si>
-    <t>Semillero Café sentipensante 
-Juan Esteban Carreño González
-Isaac David Fuentes Durán 
-Linda Saray Martinez Ortiz
-Melany Sareth Rueda Lea</t>
-  </si>
-  <si>
-    <t>https://events.teams.microsoft.com/event/ff3d7f14-315f-45c6-bc92-03115e071edb@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
-  </si>
-  <si>
     <t>Taller  "Inventario de pérdidas"
 Juliana Jaramillo Pabón</t>
   </si>
@@ -703,20 +691,84 @@
 Daniela Lemus Ruíz</t>
   </si>
   <si>
+    <t>El desarrollo humano desde el acondicionamiento físico y el bienestar
+Invitado: Diego Fernando Villamizar Gómez, Sindy Vannesa Castellanos González
+Moderadora: Dalis Nury Molina Bustamante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://teams.microsoft.com/meet/298637062877603?p=dqbKJf0l4CkPQsjs8a </t>
+  </si>
+  <si>
+    <t>Del prompt a la experiencia de aprendizaje: inteligencia artificial y diseño instruccional con sentido pedagógico 
+Karla Beatriz Gómez Santana
+Kenia Viridiana Ocampo Vera, 
+Universidad de Guadalajara</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/36eb2a1a-32d6-48f9-ab67-ba99d2dc807f@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Performance British Culture and Literature: Shakespeare in Love</t>
-  </si>
-  <si>
-    <t>Conferencia Performática</t>
-  </si>
-  <si>
-    <t>https://teams.microsoft.com/l/meetup-join/19%3ameeting_OThmMWJlMzgtODMyMy00MTkzLTgwMjQtNDY3NjkyMDVhNWRi%40thread.v2/0?context=%7b%22Tid%22%3a%22b1ba85eb-a253-4467-9ee8-d4f8ed4df300%22%2c%22Oid%22%3a%22106d225c-bde9-4ba6-8ecd-49c82573139e%22%7d</t>
   </si>
   <si>
     <t xml:space="preserve">Xeropan - Effective and fun language learning for the dedicated. 
 Ákos Huszár- Budapest, Hungary  </t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/l/meetup-join/19%3ameeting_OThmMWJlMzgtODMyMy00MTkzLTgwMjQtNDY3NjkyMDVhNWRi%40thread.v2/0?context=%7b%22Tid%22%3a%22b1ba85eb-a253-4467-9ee8-d4f8ed4df300%22%2c%22Oid%22%3a%22106d225c-bde9-4ba6-8ecd-49c82573139e%22%7d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pearson education: international English exams </t>
+  </si>
+  <si>
+    <t>Construcción de la identidad en la primera infancia a través de prácticas pedagógicas  basadas en el juego, la participación y la diversidad en el aula
+Briyeth Michelle Mogollón Ascanio y Karen Daniela Álvarez Carranza 
+Semillero Educación Infantil</t>
+  </si>
+  <si>
+    <t>Investigación Cualitativa 
+Prof. Miguel Valdivia Pinto
+Universidad César Vallejo. Perú. (virtual)</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/22665374-cbde-4501-87a6-8973bf4dccbd@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
+    <t>Ecología de la retención estudiantil en la Educación Superior. 
+Profesora Asociada, Pilar Mendoza
+Universidad de Missouri y Directora CIIDE</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/89538298-daed-473c-b6cb-b558dd6c6ceb@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentación investigación LILEX Madrid
+Ana María Rocha Tamayo, Marisela Niño Monsalve, Norma Clemencia Rodríguez Arroyave, Claudia Alejandra Pineda Silva.
+Link de conexión: https://teams.microsoft.com/meet/241575852914896?p=8CM4487YPTL7uBv9Q5   </t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/0f23b575-a34b-460e-b018-e6742f4905b8@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+  </si>
+  <si>
+    <t>Charla con invitado paralimpico</t>
+  </si>
+  <si>
+    <t>Zipaquirá</t>
+  </si>
+  <si>
+    <t>Muévete sin Barreras: Unplugged Pedagógico por la Inclusión</t>
+  </si>
+  <si>
+    <t>Mural de la experiencia</t>
+  </si>
+  <si>
+    <t>Performance British Culture and Literature: Shakespeare in Love</t>
+  </si>
+  <si>
+    <t>Conferencia Performática</t>
   </si>
   <si>
     <t>Innovacion educativa: Learning English through songs
@@ -727,9 +779,6 @@
     <t>https://teams.microsoft.com/l/meetup-join/19%3ameeting_OGQ0YmRkNjUtYjk2NC00NGYyLWFmMDQtNWQzMmMzYzk5OTg0%40thread.v2/0?context=%7b%22Tid%22%3a%22b1ba85eb-a253-4467-9ee8-d4f8ed4df300%22%2c%22Oid%22%3a%2256e1af7f-4b42-4e80-8671-8a89b73c660c%22%7d</t>
   </si>
   <si>
-    <t xml:space="preserve">Pearson education: international English exams </t>
-  </si>
-  <si>
     <t xml:space="preserve">Oiga Profe Venga le Cuento....La Ruta del Reto 
 Claudia Avila-Edgar Zambrano </t>
   </si>
@@ -744,11 +793,6 @@
   <si>
     <t>Lanzamientos editoriales 
 Licenciatura en Humanidades y lengua Castellana</t>
-  </si>
-  <si>
-    <t>Construcción de la identidad en la primera infancia a través de prácticas pedagógicas  basadas en el juego, la participación y la diversidad en el aula
-Briyeth Michelle Mogollón Ascanio y Karen Daniela Álvarez Carranza 
-Semillero Educación Infantil</t>
   </si>
   <si>
     <t xml:space="preserve">CONGRESO IDRM -REDDI EDUFISICA
@@ -778,22 +822,6 @@
 Rodríguez Perilla Ana María</t>
   </si>
   <si>
-    <t>Investigación Cualitativa 
-Prof. Miguel Valdivia Pinto
-Universidad César Vallejo. Perú. (virtual)</t>
-  </si>
-  <si>
-    <t>https://events.teams.microsoft.com/event/22665374-cbde-4501-87a6-8973bf4dccbd@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
-  </si>
-  <si>
-    <t>Ecología de la retención estudiantil en la Educación Superior. 
-Profesora Asociada, Pilar Mendoza
-Universidad de Missouri y Directora CIIDE</t>
-  </si>
-  <si>
-    <t>https://events.teams.microsoft.com/event/89538298-daed-473c-b6cb-b558dd6c6ceb@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
-  </si>
-  <si>
     <t>Modelo de implementación STEM - MD
 Diana Marcela Valencia
 CEMID</t>
@@ -873,35 +901,15 @@
 James Ricardo Zorro Monrroy, Frendy González y Sandra Patricia Pachón Monsalve</t>
   </si>
   <si>
-    <t>¿Cómo se construyen las nociones de violencia en la infancia? Una experiencia de investigación en educación
-Invitado: John Jairo García Díaz
-Moderadora: Nadia Johanna Hernández Ordoñez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presentación investigación LILEX Madrid
-Ana María Rocha Tamayo, Marisela Niño Monsalve, Norma Clemencia Rodríguez Arroyave, Claudia Alejandra Pineda Silva.
-Link de conexión: https://teams.microsoft.com/meet/241575852914896?p=8CM4487YPTL7uBv9Q5   </t>
-  </si>
-  <si>
-    <t>Madrid</t>
-  </si>
-  <si>
-    <t>https://events.teams.microsoft.com/event/0f23b575-a34b-460e-b018-e6742f4905b8@b1ba85eb-a253-4467-9ee8-d4f8ed4df300?source=copyLinkOneEventsShareDialog</t>
+    <t>Educación expandida: articulaciones de las pedagogías y la investigación educativa para mejorar las prácticas pedagógicas
+Dr. Miguel Escamilla Rocaldy - México
+Moderador: Ferney Rodriguez López</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/meet/298637062877603?p=dqbKJf0l4CkPQsjs8a</t>
   </si>
   <si>
     <t xml:space="preserve">REGISTRO </t>
-  </si>
-  <si>
-    <t>Zipaquirá</t>
-  </si>
-  <si>
-    <t>Charla con invitado paralimpico</t>
-  </si>
-  <si>
-    <t>Muévete sin Barreras: Unplugged Pedagógico por la Inclusión</t>
-  </si>
-  <si>
-    <t>Mural de la experiencia</t>
   </si>
   <si>
     <t>Teaching English in Colombia: Paradigms, People &amp; Practice
@@ -922,6 +930,9 @@
   <si>
     <t>Cuidado Integral de la Persona Mayor: Experiencias en el Contexto Australiano
 Lina María Sierra (Australia)</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/meet/272197321964862?p=3ZUvVjw3nhTuhT295I</t>
   </si>
   <si>
     <t>Cuidado Integral de las Personas con Discapacidad: Experiencias en el Contexto Australiano
@@ -987,6 +998,11 @@
   </si>
   <si>
     <t>Cl. 11 #5 - 60, Bogotá</t>
+  </si>
+  <si>
+    <t>¿Cómo se construyen las nociones de violencia en la infancia? Una experiencia de investigación en educación
+Invitado: John Jairo García Díaz
+Moderadora: Nadia Johanna Hernández Ordoñez</t>
   </si>
   <si>
     <t>Inclusive meeting for the design of Educational materials
@@ -1130,7 +1146,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1179,12 +1195,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1262,9 +1291,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1286,9 +1312,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1303,6 +1326,41 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1966,7 +2024,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="32" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
@@ -1978,10 +2036,10 @@
         <v>46315</v>
       </c>
       <c r="B2" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C2" s="21">
-        <v>0.34375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>26</v>
@@ -1993,25 +2051,27 @@
         <v>11</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="90.75" customHeight="1">
       <c r="A3" s="20">
         <v>46315</v>
       </c>
       <c r="B3" s="21">
-        <v>0.34375</v>
+        <v>0.625</v>
       </c>
       <c r="C3" s="21">
-        <v>0.375</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>27</v>
@@ -2020,25 +2080,27 @@
         <v>11</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="77.25">
       <c r="A4" s="20">
         <v>46315</v>
       </c>
       <c r="B4" s="21">
-        <v>0.375</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C4" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>27</v>
@@ -2047,12 +2109,12 @@
         <v>11</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2061,81 +2123,103 @@
         <v>46315</v>
       </c>
       <c r="B5" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C5" s="21">
-        <v>0.4375</v>
+        <v>0.6875</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75">
+        <v>34</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="46.5">
       <c r="A6" s="20">
         <v>46315</v>
       </c>
       <c r="B6" s="21">
-        <v>0.4375</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="C6" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.8125</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75">
+        <v>29</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="46.5">
       <c r="A7" s="20">
         <v>46315</v>
       </c>
       <c r="B7" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C7" s="21">
-        <v>0.58333333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="12"/>
+        <v>38</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="84.95" customHeight="1">
       <c r="A8" s="20">
         <v>46315</v>
       </c>
       <c r="B8" s="21">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C8" s="21">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>11</v>
@@ -2144,28 +2228,26 @@
         <v>23</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>38</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A9" s="20">
         <v>46315</v>
       </c>
       <c r="B9" s="21">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C9" s="21">
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="D9" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>27</v>
-      </c>
       <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
@@ -2173,39 +2255,37 @@
         <v>23</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>38</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="84.95" customHeight="1">
       <c r="A10" s="20">
         <v>46315</v>
       </c>
       <c r="B10" s="21">
-        <v>0.625</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="C10" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="84.95" customHeight="1">
@@ -2213,13 +2293,13 @@
         <v>46315</v>
       </c>
       <c r="B11" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C11" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.34375</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>27</v>
@@ -2228,27 +2308,25 @@
         <v>11</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>38</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A12" s="20">
         <v>46315</v>
       </c>
       <c r="B12" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.34375</v>
       </c>
       <c r="C12" s="21">
-        <v>0.6875</v>
+        <v>0.375</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>27</v>
@@ -2257,27 +2335,25 @@
         <v>11</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>38</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A13" s="20">
         <v>46315</v>
       </c>
       <c r="B13" s="21">
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
       <c r="C13" s="21">
-        <v>0.70833333333333337</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>27</v>
@@ -2286,98 +2362,98 @@
         <v>11</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="30" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="46.5">
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:9" ht="77.25">
       <c r="A14" s="20">
         <v>46315</v>
       </c>
       <c r="B14" s="21">
-        <v>0.77083333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C14" s="21">
-        <v>0.8125</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="30.75">
+        <v>13</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="61.5">
       <c r="A15" s="20">
         <v>46315</v>
       </c>
       <c r="B15" s="21">
-        <v>0.79166666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C15" s="21">
-        <v>0.83333333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:9" ht="46.5">
+        <v>13</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="61.5">
       <c r="A16" s="20">
         <v>46315</v>
       </c>
       <c r="B16" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.6875</v>
       </c>
       <c r="C16" s="21">
-        <v>0.375</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>51</v>
+        <v>13</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="46.5">
@@ -2391,10 +2467,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>11</v>
@@ -2418,10 +2494,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>11</v>
@@ -2445,10 +2521,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>11</v>
@@ -2472,10 +2548,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>11</v>
@@ -2499,10 +2575,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>11</v>
@@ -2515,21 +2591,21 @@
       </c>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="68.099999999999994">
+    <row r="22" spans="1:9" ht="46.5">
       <c r="A22" s="20">
         <v>46315</v>
       </c>
       <c r="B22" s="21">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="C22" s="21">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>11</v>
@@ -2538,25 +2614,25 @@
         <v>23</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="51">
+    <row r="23" spans="1:9" ht="61.5">
       <c r="A23" s="20">
         <v>46315</v>
       </c>
       <c r="B23" s="21">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C23" s="21">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>58</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>11</v>
@@ -2574,16 +2650,16 @@
         <v>46315</v>
       </c>
       <c r="B24" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="C24" s="21">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>59</v>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>11</v>
@@ -2596,72 +2672,72 @@
       </c>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="68.099999999999994">
+    <row r="25" spans="1:9" ht="92.25">
       <c r="A25" s="20">
         <v>46315</v>
       </c>
       <c r="B25" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C25" s="21">
-        <v>0.6875</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="68.099999999999994">
+    <row r="26" spans="1:9" ht="108">
       <c r="A26" s="20">
         <v>46315</v>
       </c>
       <c r="B26" s="21">
-        <v>0.6875</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C26" s="21">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H26" s="23" t="s">
         <v>13</v>
       </c>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="92.25">
+    <row r="27" spans="1:9" ht="30.75">
       <c r="A27" s="20">
         <v>46315</v>
       </c>
       <c r="B27" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C27" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>63</v>
@@ -2670,25 +2746,25 @@
         <v>11</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="H27" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="I27" s="12"/>
-    </row>
-    <row r="28" spans="1:9" ht="108">
+      <c r="I27" s="30"/>
+    </row>
+    <row r="28" spans="1:9" ht="46.5">
       <c r="A28" s="20">
         <v>46315</v>
       </c>
       <c r="B28" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C28" s="21">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>63</v>
@@ -2697,55 +2773,55 @@
         <v>11</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H28" s="23" t="s">
         <v>13</v>
       </c>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="30.75">
+    <row r="29" spans="1:9" ht="46.5">
       <c r="A29" s="20">
         <v>46315</v>
       </c>
       <c r="B29" s="21">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C29" s="21">
         <v>0.375</v>
       </c>
-      <c r="C29" s="21">
-        <v>0.41666666666666669</v>
-      </c>
       <c r="D29" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H29" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="I29" s="31"/>
+      <c r="I29" s="12"/>
     </row>
     <row r="30" spans="1:9" ht="46.5">
       <c r="A30" s="20">
         <v>46315</v>
       </c>
       <c r="B30" s="21">
-        <v>0.45833333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C30" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>11</v>
@@ -2763,22 +2839,22 @@
         <v>46315</v>
       </c>
       <c r="B31" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C31" s="21">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="F31" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H31" s="23" t="s">
         <v>13</v>
@@ -2790,16 +2866,16 @@
         <v>46315</v>
       </c>
       <c r="B32" s="21">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C32" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>11</v>
@@ -2817,22 +2893,22 @@
         <v>46315</v>
       </c>
       <c r="B33" s="21">
-        <v>0.4375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C33" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H33" s="23" t="s">
         <v>13</v>
@@ -2844,49 +2920,49 @@
         <v>46315</v>
       </c>
       <c r="B34" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="C34" s="21">
-        <v>0.5</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H34" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="I34" s="12"/>
-    </row>
-    <row r="35" spans="1:9" ht="15.75">
+      <c r="I34" s="31"/>
+    </row>
+    <row r="35" spans="1:9" ht="92.25">
       <c r="A35" s="20">
         <v>46315</v>
       </c>
       <c r="B35" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="C35" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H35" s="23" t="s">
         <v>13</v>
@@ -2898,136 +2974,118 @@
         <v>46315</v>
       </c>
       <c r="B36" s="21">
-        <v>0.4375</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="C36" s="21">
-        <v>0.4513888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H36" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="I36" s="32"/>
-    </row>
-    <row r="37" spans="1:9" ht="77.25">
+      <c r="I36" s="12"/>
+    </row>
+    <row r="37" spans="1:9" ht="30.75">
       <c r="A37" s="20">
         <v>46315</v>
       </c>
       <c r="B37" s="21">
-        <v>0.4513888888888889</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C37" s="21">
-        <v>0.47222222222222221</v>
+        <v>0.375</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>78</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I37" s="12"/>
     </row>
     <row r="38" spans="1:9" ht="102" customHeight="1">
       <c r="A38" s="20">
         <v>46315</v>
       </c>
       <c r="B38" s="21">
-        <v>0.47222222222222221</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C38" s="21">
-        <v>0.4826388888888889</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="I38" s="12"/>
     </row>
-    <row r="39" spans="1:9" ht="46.5">
+    <row r="39" spans="1:9" ht="15.75">
       <c r="A39" s="20">
         <v>46315</v>
       </c>
       <c r="B39" s="21">
-        <v>0.4826388888888889</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C39" s="21">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>13</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="23"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="30.75">
+    <row r="40" spans="1:9" ht="15.75">
       <c r="A40" s="20">
         <v>46315</v>
       </c>
       <c r="B40" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="C40" s="21">
-        <v>0.375</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F40" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" s="23" t="s">
-        <v>13</v>
-      </c>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="23"/>
       <c r="I40" s="12"/>
     </row>
     <row r="41" spans="1:9" ht="15.75">
@@ -3142,7 +3200,7 @@
         <v>11</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H45" s="23" t="s">
         <v>13</v>
@@ -3169,7 +3227,7 @@
         <v>11</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H46" s="23" t="s">
         <v>13</v>
@@ -3196,7 +3254,7 @@
         <v>11</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H47" s="23" t="s">
         <v>13</v>
@@ -3223,7 +3281,7 @@
         <v>11</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H48" s="23" t="s">
         <v>13</v>
@@ -3233,11 +3291,12 @@
     <row r="49" ht="15.75"/>
     <row r="50" ht="15.75"/>
   </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{E0435A0A-E8EE-B24A-B2EA-F66A17D967D3}"/>
   <hyperlinks>
-    <hyperlink ref="I4" r:id="rId1" xr:uid="{F8B24EBD-6CF5-4ABE-981A-C1DF5FBA39FF}"/>
-    <hyperlink ref="I16" r:id="rId2" xr:uid="{5C651494-3780-400E-9464-C8933F12A297}"/>
-    <hyperlink ref="I37" r:id="rId3" xr:uid="{8E6A0EE6-7014-4188-AC92-14F5BD6368F1}"/>
-    <hyperlink ref="I14" r:id="rId4" xr:uid="{3961131D-2959-47F6-84B8-F9F61FA105B1}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{F8B24EBD-6CF5-4ABE-981A-C1DF5FBA39FF}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{5C651494-3780-400E-9464-C8933F12A297}"/>
+    <hyperlink ref="I10" r:id="rId3" xr:uid="{8E6A0EE6-7014-4188-AC92-14F5BD6368F1}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{3961131D-2959-47F6-84B8-F9F61FA105B1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3288,121 +3347,137 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="108">
+    <row r="2" spans="1:9" ht="77.25">
       <c r="A2" s="20">
         <v>46316</v>
       </c>
       <c r="B2" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C2" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>91</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="84.95" customHeight="1">
       <c r="A3" s="20">
         <v>46316</v>
       </c>
       <c r="B3" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C3" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="17.100000000000001" customHeight="1">
       <c r="A4" s="20">
         <v>46316</v>
       </c>
       <c r="B4" s="21">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C4" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C4" s="21">
-        <v>0.4375</v>
-      </c>
       <c r="D4" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+        <v>97</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A5" s="20">
         <v>46316</v>
       </c>
       <c r="B5" s="21">
-        <v>0.4375</v>
+        <v>0.46875</v>
       </c>
       <c r="C5" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="51" customHeight="1">
       <c r="A6" s="20">
         <v>46316</v>
       </c>
       <c r="B6" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C6" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>11</v>
@@ -3411,44 +3486,52 @@
         <v>23</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75">
+    <row r="7" spans="1:9" ht="108">
       <c r="A7" s="20">
         <v>46316</v>
       </c>
       <c r="B7" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C7" s="21">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="12"/>
+        <v>102</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:9" ht="46.5">
+    <row r="8" spans="1:9" ht="61.5">
       <c r="A8" s="20">
         <v>46316</v>
       </c>
       <c r="B8" s="21">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C8" s="21">
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>11</v>
@@ -3457,27 +3540,25 @@
         <v>23</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="39" t="s">
-        <v>97</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I8" s="56"/>
     </row>
     <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A9" s="20">
         <v>46316</v>
       </c>
       <c r="B9" s="21">
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="C9" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>11</v>
@@ -3486,52 +3567,54 @@
         <v>23</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="I9" s="56"/>
     </row>
     <row r="10" spans="1:9" ht="84.95" customHeight="1">
       <c r="A10" s="20">
         <v>46316</v>
       </c>
       <c r="B10" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="C10" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="84.95" customHeight="1">
       <c r="A11" s="20">
         <v>46316</v>
       </c>
       <c r="B11" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C11" s="21">
-        <v>0.6875</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>11</v>
@@ -3542,77 +3625,77 @@
       <c r="H11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="39"/>
+      <c r="I11" s="56"/>
     </row>
     <row r="12" spans="1:9" ht="102" customHeight="1">
       <c r="A12" s="20">
         <v>46316</v>
       </c>
       <c r="B12" s="21">
-        <v>0.6875</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="C12" s="21">
-        <v>0.70833333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" spans="1:9" ht="30.75">
+      <c r="I12" s="56"/>
+    </row>
+    <row r="13" spans="1:9" ht="61.5">
       <c r="A13" s="20">
         <v>46316</v>
       </c>
       <c r="B13" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C13" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:9" ht="61.5">
+    <row r="14" spans="1:9" ht="46.5">
       <c r="A14" s="20">
         <v>46316</v>
       </c>
       <c r="B14" s="21">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C14" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>11</v>
@@ -3630,16 +3713,16 @@
         <v>46316</v>
       </c>
       <c r="B15" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C15" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>11</v>
@@ -3650,23 +3733,25 @@
       <c r="H15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I15" s="12"/>
+      <c r="I15" s="44" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="72.75" customHeight="1">
       <c r="A16" s="20">
         <v>46316</v>
       </c>
       <c r="B16" s="21">
-        <v>0.4375</v>
+        <v>0.625</v>
       </c>
       <c r="C16" s="21">
-        <v>0.45833333333333331</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>11</v>
@@ -3677,23 +3762,23 @@
       <c r="H16" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I16" s="12"/>
+      <c r="I16" s="44"/>
     </row>
     <row r="17" spans="1:9" ht="51" customHeight="1">
       <c r="A17" s="20">
         <v>46316</v>
       </c>
       <c r="B17" s="21">
-        <v>0.45833333333333331</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C17" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>11</v>
@@ -3704,116 +3789,110 @@
       <c r="H17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:9" ht="77.25">
+      <c r="I17" s="44"/>
+    </row>
+    <row r="18" spans="1:9" ht="92.25">
       <c r="A18" s="20">
         <v>46316</v>
       </c>
       <c r="B18" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C18" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>109</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" ht="105.75" customHeight="1">
       <c r="A19" s="20">
         <v>46316</v>
       </c>
       <c r="B19" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.6875</v>
       </c>
       <c r="C19" s="21">
-        <v>0.375</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>111</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="89.25" customHeight="1">
       <c r="A20" s="20">
         <v>46316</v>
       </c>
       <c r="B20" s="21">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C20" s="21">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C20" s="21">
-        <v>0.41666666666666669</v>
-      </c>
       <c r="D20" s="16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>113</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9" ht="33.950000000000003" customHeight="1">
       <c r="A21" s="20">
         <v>46316</v>
       </c>
       <c r="B21" s="21">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="C21" s="21">
-        <v>0.44791666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>13</v>
@@ -3825,72 +3904,70 @@
         <v>46316</v>
       </c>
       <c r="B22" s="21">
-        <v>0.44791666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="C22" s="21">
-        <v>0.46875</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="92.25">
+    <row r="23" spans="1:9" ht="77.25">
       <c r="A23" s="20">
         <v>46316</v>
       </c>
       <c r="B23" s="21">
-        <v>0.46875</v>
+        <v>0.4375</v>
       </c>
       <c r="C23" s="21">
-        <v>0.5</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="92.25">
+        <v>13</v>
+      </c>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:9" ht="46.5">
       <c r="A24" s="20">
         <v>46316</v>
       </c>
       <c r="B24" s="21">
-        <v>0.58333333333333337</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C24" s="21">
-        <v>0.60416666666666663</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>11</v>
@@ -3903,18 +3980,18 @@
       </c>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="84.95">
+    <row r="25" spans="1:9" ht="30.75">
       <c r="A25" s="20">
         <v>46316</v>
       </c>
       <c r="B25" s="21">
-        <v>0.60416666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="C25" s="21">
-        <v>0.625</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>27</v>
@@ -3923,25 +4000,25 @@
         <v>11</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="84.95">
+    <row r="26" spans="1:9" ht="30.75">
       <c r="A26" s="20">
         <v>46316</v>
       </c>
       <c r="B26" s="21">
-        <v>0.625</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="C26" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.46875</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>27</v>
@@ -3950,25 +4027,25 @@
         <v>11</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="119.1">
+    <row r="27" spans="1:9" ht="92.25">
       <c r="A27" s="20">
         <v>46316</v>
       </c>
       <c r="B27" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C27" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>27</v>
@@ -3980,22 +4057,22 @@
         <v>23</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="68.099999999999994">
+    <row r="28" spans="1:9" ht="77.25">
       <c r="A28" s="20">
         <v>46316</v>
       </c>
       <c r="B28" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="C28" s="21">
-        <v>0.6875</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>27</v>
@@ -4007,34 +4084,34 @@
         <v>23</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="68.099999999999994">
+    <row r="29" spans="1:9" ht="46.5">
       <c r="A29" s="20">
         <v>46316</v>
       </c>
       <c r="B29" s="21">
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
       <c r="C29" s="21">
-        <v>0.70833333333333337</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I29" s="12"/>
     </row>
@@ -4043,13 +4120,13 @@
         <v>46316</v>
       </c>
       <c r="B30" s="21">
-        <v>0.4375</v>
+        <v>0.75</v>
       </c>
       <c r="C30" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>63</v>
@@ -4058,82 +4135,82 @@
         <v>11</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="51">
+    <row r="31" spans="1:9" ht="30.75">
       <c r="A31" s="20">
         <v>46316</v>
       </c>
       <c r="B31" s="21">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C31" s="21">
-        <v>0.85416666666666663</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="33.950000000000003">
+    <row r="32" spans="1:9" ht="77.25">
       <c r="A32" s="20">
         <v>46316</v>
       </c>
       <c r="B32" s="21">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C32" s="21">
-        <v>0.54166666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="84.95">
+    <row r="33" spans="1:9" ht="184.5">
       <c r="A33" s="20">
         <v>46316</v>
       </c>
       <c r="B33" s="21">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C33" s="21">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>11</v>
@@ -4146,21 +4223,21 @@
       </c>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="204">
+    <row r="34" spans="1:9" ht="123">
       <c r="A34" s="20">
         <v>46316</v>
       </c>
       <c r="B34" s="21">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="C34" s="21">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>11</v>
@@ -4173,21 +4250,21 @@
       </c>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="135.94999999999999">
+    <row r="35" spans="1:9" ht="92.25">
       <c r="A35" s="20">
         <v>46316</v>
       </c>
       <c r="B35" s="21">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C35" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>11</v>
@@ -4200,21 +4277,21 @@
       </c>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="102">
+    <row r="36" spans="1:9" ht="92.25">
       <c r="A36" s="20">
         <v>46316</v>
       </c>
       <c r="B36" s="21">
-        <v>0.64583333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C36" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>11</v>
@@ -4227,21 +4304,21 @@
       </c>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="102">
+    <row r="37" spans="1:9" ht="123">
       <c r="A37" s="20">
         <v>46316</v>
       </c>
       <c r="B37" s="21">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="C37" s="21">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>11</v>
@@ -4254,108 +4331,108 @@
       </c>
       <c r="I37" s="12"/>
     </row>
-    <row r="38" spans="1:9" ht="135.94999999999999">
+    <row r="38" spans="1:9" ht="61.5">
       <c r="A38" s="20">
         <v>46316</v>
       </c>
       <c r="B38" s="21">
-        <v>0.6875</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C38" s="21">
-        <v>0.70833333333333337</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I38" s="12"/>
     </row>
-    <row r="39" spans="1:9" ht="61.5">
+    <row r="39" spans="1:9" ht="107.25" customHeight="1">
       <c r="A39" s="20">
         <v>46316</v>
       </c>
       <c r="B39" s="21">
-        <v>0.8125</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C39" s="21">
-        <v>0.85416666666666663</v>
+        <v>0.375</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" s="12"/>
+        <v>44</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="G39" s="16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="77.25">
+        <v>13</v>
+      </c>
+      <c r="I39" s="12"/>
+    </row>
+    <row r="40" spans="1:9" ht="100.5" customHeight="1">
       <c r="A40" s="20">
         <v>46316</v>
       </c>
       <c r="B40" s="21">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="C40" s="21">
-        <v>0.79166666666666663</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="12"/>
+        <v>44</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="G40" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I40" s="26" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="61.5">
+        <v>13</v>
+      </c>
+      <c r="I40" s="12"/>
+    </row>
+    <row r="41" spans="1:9" ht="30.75">
       <c r="A41" s="20">
         <v>46316</v>
       </c>
       <c r="B41" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C41" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>13</v>
@@ -4367,22 +4444,22 @@
         <v>46316</v>
       </c>
       <c r="B42" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C42" s="21">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>13</v>
@@ -4394,22 +4471,22 @@
         <v>46316</v>
       </c>
       <c r="B43" s="21">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C43" s="21">
         <v>0.375</v>
       </c>
-      <c r="C43" s="21">
-        <v>0.39583333333333331</v>
-      </c>
       <c r="D43" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>11</v>
+        <v>142</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>13</v>
@@ -4421,194 +4498,176 @@
         <v>46316</v>
       </c>
       <c r="B44" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C44" s="21">
         <v>0.41666666666666669</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="25" t="s">
-        <v>141</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I44" s="12"/>
     </row>
     <row r="45" spans="1:9" ht="33.950000000000003" customHeight="1">
       <c r="A45" s="20">
         <v>46316</v>
       </c>
       <c r="B45" s="21">
-        <v>0.4375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C45" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="61.5">
+    <row r="46" spans="1:9" ht="43.5">
       <c r="A46" s="20">
         <v>46316</v>
       </c>
       <c r="B46" s="21">
-        <v>0.45833333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C46" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>143</v>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>145</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I46" s="12"/>
     </row>
-    <row r="47" spans="1:9" ht="33.950000000000003">
+    <row r="47" spans="1:9" ht="104.25" customHeight="1">
       <c r="A47" s="20">
         <v>46316</v>
       </c>
       <c r="B47" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.8125</v>
       </c>
       <c r="C47" s="21">
-        <v>0.375</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>146</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F47" s="12"/>
       <c r="G47" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="12"/>
-    </row>
-    <row r="48" spans="1:9" ht="33.950000000000003">
+        <v>81</v>
+      </c>
+      <c r="I47" s="25" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="77.25">
       <c r="A48" s="20">
         <v>46316</v>
       </c>
       <c r="B48" s="21">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="C48" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>86</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F48" s="12"/>
       <c r="G48" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="12"/>
-    </row>
-    <row r="49" spans="1:9" ht="30.75">
+        <v>81</v>
+      </c>
+      <c r="I48" s="26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15.75">
       <c r="A49" s="20">
         <v>46316</v>
       </c>
-      <c r="B49" s="43">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C49" s="43">
-        <v>0.375</v>
-      </c>
-      <c r="D49" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="E49" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="F49" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="I49" s="45"/>
-    </row>
-    <row r="50" spans="1:9" ht="43.5">
-      <c r="A50" s="42">
+      <c r="B49" s="41">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C49" s="41">
+        <v>0.4375</v>
+      </c>
+      <c r="D49" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+    </row>
+    <row r="50" spans="1:9" ht="15.75">
+      <c r="A50" s="40">
         <v>46316</v>
       </c>
       <c r="B50" s="21">
-        <v>0.375</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="C50" s="21">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>13</v>
-      </c>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="12"/>
       <c r="I50" s="12"/>
     </row>
     <row r="51" spans="1:9" ht="15.75">
-      <c r="D51" s="40"/>
+      <c r="D51" s="38"/>
     </row>
     <row r="52" spans="1:9">
       <c r="E52" t="s">
@@ -4616,17 +4675,22 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{BED20595-F46C-C040-90EA-99C2F2DEBE61}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I50">
+      <sortCondition ref="H1"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="I8:I12"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="I20" r:id="rId1" xr:uid="{FC32B617-59E4-4C06-859F-4AAAE4EFE882}"/>
-    <hyperlink ref="I8" r:id="rId2" xr:uid="{2819DA45-DB42-4A92-B450-16230ECD7459}"/>
-    <hyperlink ref="I39" r:id="rId3" xr:uid="{D24D438E-2CF8-42B8-9DE7-67A20A75DF1A}"/>
-    <hyperlink ref="I19" r:id="rId4" xr:uid="{CCCD8BFB-0939-D149-BD09-CE29918D8AAB}"/>
-    <hyperlink ref="I40" r:id="rId5" xr:uid="{91101E1E-D27C-43AD-95D4-9F7F27CA2CFD}"/>
-    <hyperlink ref="I23" r:id="rId6" xr:uid="{8ED477E0-57DD-4243-95BA-7B749553D740}"/>
-    <hyperlink ref="I44" r:id="rId7" xr:uid="{3AFBD4C4-632A-458A-86D7-5274C6D84679}"/>
+    <hyperlink ref="I4" r:id="rId1" xr:uid="{FC32B617-59E4-4C06-859F-4AAAE4EFE882}"/>
+    <hyperlink ref="I15" r:id="rId2" xr:uid="{2819DA45-DB42-4A92-B450-16230ECD7459}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{CCCD8BFB-0939-D149-BD09-CE29918D8AAB}"/>
+    <hyperlink ref="I48" r:id="rId4" xr:uid="{91101E1E-D27C-43AD-95D4-9F7F27CA2CFD}"/>
+    <hyperlink ref="I5" r:id="rId5" xr:uid="{8ED477E0-57DD-4243-95BA-7B749553D740}"/>
+    <hyperlink ref="I10" r:id="rId6" xr:uid="{3AFBD4C4-632A-458A-86D7-5274C6D84679}"/>
+    <hyperlink ref="I47" r:id="rId7" xr:uid="{0BF95494-6269-4F2F-ACEF-E6EBFFAFDF4B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4682,28 +4746,28 @@
         <v>46317</v>
       </c>
       <c r="B2" s="21">
-        <v>0.3125</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="C2" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>151</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="28" t="s">
         <v>152</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="77.25">
@@ -4711,45 +4775,45 @@
         <v>46317</v>
       </c>
       <c r="B3" s="21">
-        <v>0.36458333333333331</v>
+        <v>0.40625</v>
       </c>
       <c r="C3" s="21">
-        <v>0.38194444444444442</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>154</v>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="77.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="61.5">
       <c r="A4" s="20">
         <v>46317</v>
       </c>
       <c r="B4" s="21">
-        <v>0.38194444444444442</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C4" s="21">
-        <v>0.40625</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>11</v>
@@ -4758,60 +4822,66 @@
         <v>23</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="77.25">
+        <v>29</v>
+      </c>
+      <c r="I4" s="23"/>
+    </row>
+    <row r="5" spans="1:9" ht="46.5">
       <c r="A5" s="20">
         <v>46317</v>
       </c>
       <c r="B5" s="21">
-        <v>0.40625</v>
+        <v>0.4375</v>
       </c>
       <c r="C5" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>157</v>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="77.25">
+        <v>29</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="46.5">
       <c r="A6" s="20">
         <v>46317</v>
       </c>
       <c r="B6" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C6" s="21">
-        <v>0.4375</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="28" t="s">
-        <v>153</v>
+        <v>157</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="33.950000000000003" customHeight="1">
@@ -4822,25 +4892,25 @@
         <v>0.4375</v>
       </c>
       <c r="C7" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>50</v>
+        <v>159</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>153</v>
+      <c r="H7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="51" customHeight="1">
@@ -4848,120 +4918,126 @@
         <v>46317</v>
       </c>
       <c r="B8" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="C8" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>50</v>
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>153</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9" ht="51" customHeight="1">
       <c r="A9" s="20">
         <v>46317</v>
       </c>
       <c r="B9" s="21">
-        <v>0.5</v>
+        <v>0.15625</v>
       </c>
       <c r="C9" s="21">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>50</v>
+        <v>0.1875</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>153</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9" ht="15.75">
       <c r="A10" s="20">
         <v>46317</v>
       </c>
       <c r="B10" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.1875</v>
       </c>
       <c r="C10" s="21">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="12"/>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:9" ht="33.950000000000003">
+    <row r="11" spans="1:9" ht="77.25">
       <c r="A11" s="20">
         <v>46317</v>
       </c>
       <c r="B11" s="21">
-        <v>0.58333333333333337</v>
+        <v>0.3125</v>
       </c>
       <c r="C11" s="21">
-        <v>0.625</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" ht="68.099999999999994">
+      <c r="I11" s="46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="77.25">
       <c r="A12" s="20">
         <v>46317</v>
       </c>
       <c r="B12" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="C12" s="21">
-        <v>0.5</v>
+        <v>0.40625</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>11</v>
@@ -4970,25 +5046,27 @@
         <v>23</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" ht="61.5">
+        <v>13</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="77.25">
       <c r="A13" s="20">
         <v>46317</v>
       </c>
       <c r="B13" s="21">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="C13" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>11</v>
@@ -4999,23 +5077,25 @@
       <c r="H13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" ht="46.5">
+      <c r="I13" s="46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="77.25">
       <c r="A14" s="20">
         <v>46317</v>
       </c>
       <c r="B14" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C14" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>11</v>
@@ -5026,23 +5106,25 @@
       <c r="H14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="12"/>
+      <c r="I14" s="46" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="33.950000000000003" customHeight="1">
       <c r="A15" s="20">
         <v>46317</v>
       </c>
       <c r="B15" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="C15" s="21">
-        <v>0.375</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>11</v>
@@ -5053,23 +5135,25 @@
       <c r="H15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I15" s="12"/>
+      <c r="I15" s="46" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="51" customHeight="1">
       <c r="A16" s="20">
         <v>46317</v>
       </c>
       <c r="B16" s="21">
-        <v>0.375</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C16" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>11</v>
@@ -5087,16 +5171,16 @@
         <v>46317</v>
       </c>
       <c r="B17" s="21">
-        <v>0.39583333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="C17" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>11</v>
@@ -5114,13 +5198,13 @@
         <v>46317</v>
       </c>
       <c r="B18" s="21">
-        <v>0.4375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C18" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>27</v>
@@ -5132,24 +5216,22 @@
         <v>23</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="46.5">
+        <v>13</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:9" ht="30.75">
       <c r="A19" s="20">
         <v>46317</v>
       </c>
       <c r="B19" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C19" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>27</v>
@@ -5161,27 +5243,25 @@
         <v>23</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>171</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" spans="1:9" ht="46.5">
       <c r="A20" s="20">
         <v>46317</v>
       </c>
       <c r="B20" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C20" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>11</v>
@@ -5199,40 +5279,40 @@
         <v>46317</v>
       </c>
       <c r="B21" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="C21" s="21">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="108">
+    <row r="22" spans="1:9" ht="46.5">
       <c r="A22" s="20">
         <v>46317</v>
       </c>
       <c r="B22" s="21">
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C22" s="21">
-        <v>0.38541666666666669</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>63</v>
@@ -5241,25 +5321,25 @@
         <v>11</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="77.25">
+    <row r="23" spans="1:9" ht="46.5">
       <c r="A23" s="20">
         <v>46317</v>
       </c>
       <c r="B23" s="21">
-        <v>0.3888888888888889</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C23" s="21">
-        <v>0.39930555555555558</v>
+        <v>0.375</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>63</v>
@@ -5268,7 +5348,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>13</v>
@@ -5280,13 +5360,13 @@
         <v>46317</v>
       </c>
       <c r="B24" s="21">
-        <v>0.40277777777777779</v>
+        <v>0.375</v>
       </c>
       <c r="C24" s="21">
-        <v>0.41319444444444442</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>63</v>
@@ -5295,7 +5375,7 @@
         <v>11</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>13</v>
@@ -5307,13 +5387,13 @@
         <v>46317</v>
       </c>
       <c r="B25" s="21">
-        <v>0.4375</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C25" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.39930555555555558</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>63</v>
@@ -5322,7 +5402,7 @@
         <v>11</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>13</v>
@@ -5334,13 +5414,13 @@
         <v>46317</v>
       </c>
       <c r="B26" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="C26" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>63</v>
@@ -5349,34 +5429,34 @@
         <v>11</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="61.5">
+    <row r="27" spans="1:9" ht="30.75">
       <c r="A27" s="20">
         <v>46317</v>
       </c>
       <c r="B27" s="21">
-        <v>0.35416666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="C27" s="21">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>13</v>
@@ -5388,22 +5468,22 @@
         <v>46317</v>
       </c>
       <c r="B28" s="21">
-        <v>0.375</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="C28" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>13</v>
@@ -5415,16 +5495,16 @@
         <v>46317</v>
       </c>
       <c r="B29" s="21">
-        <v>0.4375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C29" s="21">
-        <v>0.47916666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>11</v>
@@ -5437,34 +5517,34 @@
       </c>
       <c r="I29" s="12"/>
     </row>
-    <row r="30" spans="1:9" ht="61.5">
+    <row r="30" spans="1:9" ht="30.75">
       <c r="A30" s="20">
         <v>46317</v>
       </c>
       <c r="B30" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="C30" s="21">
         <v>0.41666666666666669</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="17.100000000000001">
+    <row r="31" spans="1:9" ht="30.75">
       <c r="A31" s="20">
         <v>46317</v>
       </c>
@@ -5475,43 +5555,43 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="30.75">
+    <row r="32" spans="1:9" ht="61.5">
       <c r="A32" s="20">
         <v>46317</v>
       </c>
       <c r="B32" s="21">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C32" s="21">
-        <v>0.52083333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>13</v>
@@ -5523,22 +5603,22 @@
         <v>46317</v>
       </c>
       <c r="B33" s="21">
-        <v>0.33333333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="C33" s="21">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>13</v>
@@ -5550,194 +5630,186 @@
         <v>46317</v>
       </c>
       <c r="B34" s="21">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="21">
-        <v>0.5</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="61.5">
+    <row r="35" spans="1:9" ht="30.75">
       <c r="A35" s="20">
         <v>46317</v>
       </c>
       <c r="B35" s="21">
-        <v>0.8125</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C35" s="21">
-        <v>0.85416666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" s="12"/>
+        <v>194</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="G35" s="16" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="77.25">
-      <c r="A36" s="20">
+    <row r="36" spans="1:9" ht="30.75">
+      <c r="A36" s="49">
         <v>46317</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="41">
         <v>0.4375</v>
       </c>
-      <c r="C36" s="21">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="25" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="17.100000000000001">
+      <c r="C36" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="43"/>
+    </row>
+    <row r="37" spans="1:9" ht="47.25" customHeight="1">
       <c r="A37" s="20">
         <v>46317</v>
       </c>
       <c r="B37" s="21">
-        <v>8.3333333333333329E-2</v>
+        <v>0.8125</v>
       </c>
       <c r="C37" s="21">
-        <v>0.10416666666666667</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>193</v>
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>196</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G37" s="16"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-    </row>
-    <row r="38" spans="1:9" ht="17.100000000000001">
-      <c r="A38" s="20">
+        <v>81</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="77.25">
+      <c r="A38" s="51">
         <v>46317</v>
       </c>
-      <c r="B38" s="21">
-        <v>0.10416666666666667</v>
-      </c>
-      <c r="C38" s="21">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="12"/>
-    </row>
-    <row r="39" spans="1:9" ht="33.950000000000003">
+      <c r="B38" s="52">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C38" s="52">
+        <v>0.4375</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="55" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.75">
       <c r="A39" s="20">
         <v>46317</v>
       </c>
       <c r="B39" s="21">
-        <v>0.15625</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="C39" s="21">
-        <v>0.1875</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>31</v>
-      </c>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="17.100000000000001">
+    <row r="40" spans="1:9" ht="15.75">
       <c r="A40" s="20">
         <v>46317</v>
       </c>
       <c r="B40" s="21">
-        <v>0.1875</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="C40" s="21">
-        <v>0.20833333333333334</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>85</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>31</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G40" s="16"/>
+      <c r="H40" s="12"/>
       <c r="I40" s="12"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{610C11C2-B771-9D44-A689-56619F68B052}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I40">
+      <sortCondition ref="H1"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="I19" r:id="rId1" xr:uid="{45DCC090-C842-47F8-AA21-60089D79061C}"/>
-    <hyperlink ref="I18" r:id="rId2" xr:uid="{CE097CE5-E7A1-4558-BC32-1132D26AFCA7}"/>
-    <hyperlink ref="I36" r:id="rId3" xr:uid="{947F3F53-3062-48C4-8F1A-6B21543BB41E}"/>
+    <hyperlink ref="I6" r:id="rId1" xr:uid="{45DCC090-C842-47F8-AA21-60089D79061C}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{CE097CE5-E7A1-4558-BC32-1132D26AFCA7}"/>
+    <hyperlink ref="I7" r:id="rId3" xr:uid="{947F3F53-3062-48C4-8F1A-6B21543BB41E}"/>
     <hyperlink ref="I2:I4" r:id="rId4" display="https://teams.microsoft.com/l/meetup-join/19%3ameeting_OThmMWJlMzgtODMyMy00MTkzLTgwMjQtNDY3NjkyMDVhNWRi%40thread.v2/0?context=%7b%22Tid%22%3a%22b1ba85eb-a253-4467-9ee8-d4f8ed4df300%22%2c%22Oid%22%3a%22106d225c-bde9-4ba6-8ecd-49c82573139e%22%7d" xr:uid="{C340DFEB-256D-42DD-828C-BDDE5B88CD6E}"/>
     <hyperlink ref="I3:I9" r:id="rId5" display="https://teams.microsoft.com/l/meetup-join/19%3ameeting_OThmMWJlMzgtODMyMy00MTkzLTgwMjQtNDY3NjkyMDVhNWRi%40thread.v2/0?context=%7b%22Tid%22%3a%22b1ba85eb-a253-4467-9ee8-d4f8ed4df300%22%2c%22Oid%22%3a%22106d225c-bde9-4ba6-8ecd-49c82573139e%22%7d" xr:uid="{54C626D2-69E6-451D-A229-1573F378ECCA}"/>
-    <hyperlink ref="I4" r:id="rId6" xr:uid="{4D6938B4-EABA-47AD-BB77-571B03D4FC4B}"/>
+    <hyperlink ref="I12" r:id="rId6" xr:uid="{4D6938B4-EABA-47AD-BB77-571B03D4FC4B}"/>
+    <hyperlink ref="I37" r:id="rId7" xr:uid="{B6A89901-1CBC-4E53-87D2-CC0BFBACA447}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5798,22 +5870,22 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G2" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="46.5">
@@ -5827,17 +5899,17 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="I3" s="12"/>
     </row>
@@ -5852,10 +5924,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>11</v>
@@ -5864,10 +5936,10 @@
         <v>23</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="61.5">
@@ -5881,10 +5953,10 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>11</v>
@@ -5893,10 +5965,10 @@
         <v>23</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="200.25">
@@ -5910,10 +5982,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>11</v>
@@ -5922,10 +5994,10 @@
         <v>23</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="68.099999999999994" customHeight="1">
@@ -5939,10 +6011,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>11</v>
@@ -5966,10 +6038,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>11</v>
@@ -5993,17 +6065,17 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="I9" s="12"/>
     </row>
@@ -6018,7 +6090,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>27</v>
@@ -6027,13 +6099,13 @@
         <v>11</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="61.5">
@@ -6047,7 +6119,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>63</v>
@@ -6056,7 +6128,7 @@
         <v>11</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>13</v>
@@ -6074,7 +6146,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>63</v>
@@ -6083,7 +6155,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>13</v>
@@ -6101,7 +6173,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>63</v>
@@ -6110,7 +6182,7 @@
         <v>11</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>13</v>
@@ -6128,13 +6200,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>19</v>
@@ -6155,13 +6227,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>12</v>
@@ -6182,10 +6254,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17.100000000000001">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17.100000000000001">
       <c r="A17" s="5">
         <v>46318</v>
       </c>
@@ -6196,10 +6268,36 @@
         <v>0.4375</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="61.5">
+      <c r="A18" s="5">
+        <v>46318</v>
+      </c>
+      <c r="B18" s="21">
+        <v>0.8125</v>
+      </c>
+      <c r="C18" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>197</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I4" r:id="rId1" xr:uid="{C9493442-D043-4F0C-87C2-48D7691A2D28}"/>
@@ -6207,6 +6305,7 @@
     <hyperlink ref="I6" r:id="rId3" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.youtube.com%2Flive%2Fesp7PURwXVw%3Fsi%3Dsj4hy4V6H6qsgsCH&amp;data=05%7C02%7Canderson.garzon.s%40uniminuto.edu%7C8c40ee5cc1b4465bf10a08df2a0d6ea2%7Cb1ba85eba25344679ee8d4f8ed4df300%7C1%7C0%7C639275909426166060%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=vLjWfGSRgHp4LJ6pY3I83XdSpAYEt0XuJi4BfC3%2FFvA%3D&amp;reserved=0" xr:uid="{8191B0B2-0D8D-467E-8B9E-829DDC0876A2}"/>
     <hyperlink ref="I2" r:id="rId4" xr:uid="{8E47C14B-12C8-44DD-B099-1CCDAF1D329E}"/>
     <hyperlink ref="I10" r:id="rId5" xr:uid="{A870712A-1A07-4428-AE09-413B7AD8BBDB}"/>
+    <hyperlink ref="I18" r:id="rId6" xr:uid="{1E7D601A-A3ED-4CC4-9542-344862D130A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6237,7 +6336,7 @@
       <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="19" t="s">
@@ -6266,23 +6365,23 @@
       <c r="C2" s="21">
         <v>0.75</v>
       </c>
-      <c r="D2" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="F2" s="36" t="s">
+      <c r="D2" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="F2" s="35" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68.099999999999994">
@@ -6295,14 +6394,14 @@
       <c r="C3" s="21">
         <v>0.375</v>
       </c>
-      <c r="D3" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>215</v>
+      <c r="D3" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>217</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>23</v>
@@ -6322,14 +6421,14 @@
       <c r="C4" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>215</v>
+      <c r="D4" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>217</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>23</v>
@@ -6338,7 +6437,7 @@
         <v>13</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.100000000000001">
@@ -6351,8 +6450,8 @@
       <c r="C5" s="21">
         <v>0.4375</v>
       </c>
-      <c r="D5" s="37" t="s">
-        <v>33</v>
+      <c r="D5" s="36" t="s">
+        <v>82</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="17"/>
@@ -6370,17 +6469,17 @@
       <c r="C6" s="21">
         <v>0.5</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>215</v>
+      <c r="D6" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>217</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>13</v>
@@ -6397,20 +6496,20 @@
       <c r="C7" s="21">
         <v>0.375</v>
       </c>
-      <c r="D7" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>191</v>
+      <c r="D7" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>160</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I7" s="12"/>
     </row>
@@ -6424,20 +6523,20 @@
       <c r="C8" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D8" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>191</v>
+      <c r="D8" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>160</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I8" s="12"/>
     </row>
@@ -6451,20 +6550,20 @@
       <c r="C9" s="21">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D9" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>191</v>
+      <c r="D9" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>160</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I9" s="12"/>
     </row>
@@ -6478,20 +6577,20 @@
       <c r="C10" s="21">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>191</v>
+      <c r="F10" s="35" t="s">
+        <v>160</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I10" s="12"/>
     </row>
@@ -6505,17 +6604,17 @@
       <c r="C11" s="21">
         <v>0.375</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>194</v>
+      <c r="D11" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>13</v>
@@ -6532,14 +6631,14 @@
       <c r="C12" s="21">
         <v>0.40625</v>
       </c>
-      <c r="D12" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>194</v>
+      <c r="D12" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>23</v>
@@ -6559,14 +6658,14 @@
       <c r="C13" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D13" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>194</v>
+      <c r="D13" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>23</v>
@@ -6586,14 +6685,14 @@
       <c r="C14" s="21">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>194</v>
+      <c r="D14" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>15</v>
@@ -6613,14 +6712,14 @@
       <c r="C15" s="21">
         <v>0.5</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="F15" s="36" t="s">
-        <v>194</v>
+      <c r="D15" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>15</v>
@@ -6641,13 +6740,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>12</v>
@@ -6668,10 +6767,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
+        <v>83</v>
+      </c>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="16"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7447F4E0-1FF2-41BF-8362-7FC031A3BA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BE9C7E-277D-42B7-81BE-5ADC238061EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="1" activeTab="3" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="3" activeTab="4" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="243">
   <si>
     <t>DÍA</t>
   </si>
@@ -961,6 +961,9 @@
     <t>El desafío de enseñar tecnología aplicada al arte en la era de la inteligencia artificial
 Emiliano Causa, Universidad Nacional de La Plata y Universidad Nacional del Arte
 Argentina</t>
+  </si>
+  <si>
+    <t>https://events.teams.microsoft.com/event/68bc64d4-99e0-4520-9044-edaf83d01f06@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
   </si>
   <si>
     <t>Sabio Mutis Inmersion  proposal workshop</t>
@@ -1338,9 +1341,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1359,6 +1359,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -3596,7 +3599,7 @@
       <c r="H10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="48" t="s">
+      <c r="I10" s="55" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5680,7 +5683,7 @@
       <c r="I35" s="12"/>
     </row>
     <row r="36" spans="1:9" ht="30.75">
-      <c r="A36" s="49">
+      <c r="A36" s="48">
         <v>46317</v>
       </c>
       <c r="B36" s="41">
@@ -5692,7 +5695,7 @@
       <c r="D36" s="42" t="s">
         <v>195</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="49" t="s">
         <v>79</v>
       </c>
       <c r="F36" s="43" t="s">
@@ -5734,23 +5737,23 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="77.25">
-      <c r="A38" s="51">
+      <c r="A38" s="50">
         <v>46317</v>
       </c>
-      <c r="B38" s="52">
+      <c r="B38" s="51">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C38" s="52">
+      <c r="C38" s="51">
         <v>0.4375</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="E38" s="53"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="55" t="s">
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="54" t="s">
         <v>152</v>
       </c>
     </row>
@@ -6077,7 +6080,9 @@
       <c r="H9" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="25" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="77.25">
       <c r="A10" s="20">
@@ -6090,7 +6095,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>27</v>
@@ -6105,7 +6110,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="61.5">
@@ -6119,7 +6124,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>63</v>
@@ -6146,7 +6151,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>63</v>
@@ -6173,7 +6178,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>63</v>
@@ -6200,13 +6205,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>19</v>
@@ -6227,13 +6232,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>12</v>
@@ -6282,7 +6287,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>81</v>
@@ -6306,6 +6311,7 @@
     <hyperlink ref="I2" r:id="rId4" xr:uid="{8E47C14B-12C8-44DD-B099-1CCDAF1D329E}"/>
     <hyperlink ref="I10" r:id="rId5" xr:uid="{A870712A-1A07-4428-AE09-413B7AD8BBDB}"/>
     <hyperlink ref="I18" r:id="rId6" xr:uid="{1E7D601A-A3ED-4CC4-9542-344862D130A9}"/>
+    <hyperlink ref="I9" r:id="rId7" xr:uid="{01F6D7F3-1B4A-4EED-AAEC-FD070BD2176B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6366,22 +6372,22 @@
         <v>0.75</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F2" s="35" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="68.099999999999994">
@@ -6395,13 +6401,13 @@
         <v>0.375</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>23</v>
@@ -6422,13 +6428,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>23</v>
@@ -6437,7 +6443,7 @@
         <v>13</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.100000000000001">
@@ -6470,13 +6476,13 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>95</v>
@@ -6497,10 +6503,10 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F7" s="35" t="s">
         <v>160</v>
@@ -6524,10 +6530,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="35" t="s">
         <v>234</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>233</v>
       </c>
       <c r="F8" s="35" t="s">
         <v>160</v>
@@ -6551,10 +6557,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F9" s="35" t="s">
         <v>160</v>
@@ -6578,10 +6584,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F10" s="35" t="s">
         <v>160</v>
@@ -6605,10 +6611,10 @@
         <v>0.375</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F11" s="35" t="s">
         <v>163</v>
@@ -6632,10 +6638,10 @@
         <v>0.40625</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F12" s="35" t="s">
         <v>163</v>
@@ -6659,10 +6665,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F13" s="35" t="s">
         <v>163</v>
@@ -6686,10 +6692,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>163</v>
@@ -6713,10 +6719,10 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F15" s="35" t="s">
         <v>163</v>
@@ -6740,13 +6746,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>12</v>

--- a/data/AgendaPlana.xlsx
+++ b/data/AgendaPlana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpipe/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BE9C7E-277D-42B7-81BE-5ADC238061EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFE0AFBC-C8DF-44CF-B049-5EE81062C978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="3" activeTab="4" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" firstSheet="4" activeTab="4" xr2:uid="{CC828893-5B06-154C-922E-91E8B4C28B8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes 19 de octubre" sheetId="1" r:id="rId1"/>
@@ -963,7 +963,7 @@
 Argentina</t>
   </si>
   <si>
-    <t>https://events.teams.microsoft.com/event/68bc64d4-99e0-4520-9044-edaf83d01f06@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
+    <t>https://events.teams.microsoft.com/event/d327f4e0-58d3-419c-9186-58051c028bf9@b1ba85eb-a253-4467-9ee8-d4f8ed4df300</t>
   </si>
   <si>
     <t>Sabio Mutis Inmersion  proposal workshop</t>
@@ -6311,7 +6311,7 @@
     <hyperlink ref="I2" r:id="rId4" xr:uid="{8E47C14B-12C8-44DD-B099-1CCDAF1D329E}"/>
     <hyperlink ref="I10" r:id="rId5" xr:uid="{A870712A-1A07-4428-AE09-413B7AD8BBDB}"/>
     <hyperlink ref="I18" r:id="rId6" xr:uid="{1E7D601A-A3ED-4CC4-9542-344862D130A9}"/>
-    <hyperlink ref="I9" r:id="rId7" xr:uid="{01F6D7F3-1B4A-4EED-AAEC-FD070BD2176B}"/>
+    <hyperlink ref="I9" r:id="rId7" xr:uid="{1B818DF8-A5FB-4F24-BAFC-452BD8F59B64}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
